--- a/sch/components.xlsx
+++ b/sch/components.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\miha\Desktop\vezje-idp\kicad\sch\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66667DF9-155D-4464-A506-328CD4800B07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F7835F9-2275-499B-89E0-5C8DAB8BD279}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12552" xr2:uid="{6172FD7F-16CD-47D1-A3E4-D63AC8EC044E}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="925" uniqueCount="425">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="929" uniqueCount="428">
   <si>
     <t>ID</t>
   </si>
@@ -1086,9 +1086,6 @@
     <t>S14</t>
   </si>
   <si>
-    <t>C74</t>
-  </si>
-  <si>
     <t>S367</t>
   </si>
   <si>
@@ -1125,9 +1122,6 @@
     <t>33R</t>
   </si>
   <si>
-    <t>LS74</t>
-  </si>
-  <si>
     <t>MC14411</t>
   </si>
   <si>
@@ -1146,24 +1140,12 @@
     <t>4K7</t>
   </si>
   <si>
-    <t>P4?</t>
-  </si>
-  <si>
-    <t>P2?</t>
-  </si>
-  <si>
     <t>P1</t>
   </si>
   <si>
     <t>4.7K</t>
   </si>
   <si>
-    <t>4K7?</t>
-  </si>
-  <si>
-    <t>Z80CTC</t>
-  </si>
-  <si>
     <t>S20</t>
   </si>
   <si>
@@ -1215,9 +1197,6 @@
     <t>S38</t>
   </si>
   <si>
-    <t>S629?</t>
-  </si>
-  <si>
     <t>S393</t>
   </si>
   <si>
@@ -1260,9 +1239,6 @@
     <t>Z80 PIO (MK 3881)</t>
   </si>
   <si>
-    <t>P3 / S04</t>
-  </si>
-  <si>
     <t>2n 2 (?)</t>
   </si>
   <si>
@@ -1300,6 +1276,39 @@
   </si>
   <si>
     <t>390pF</t>
+  </si>
+  <si>
+    <t>P3</t>
+  </si>
+  <si>
+    <t>P2</t>
+  </si>
+  <si>
+    <t>P4</t>
+  </si>
+  <si>
+    <t>S629</t>
+  </si>
+  <si>
+    <t>Z80 CTC</t>
+  </si>
+  <si>
+    <t>LS74 / S74</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>Read as black-brown-red. Most likely it is green-brown-red (5K1).</t>
+  </si>
+  <si>
+    <t>"E75" (pg. 7)</t>
+  </si>
+  <si>
+    <t>Value Ref3</t>
+  </si>
+  <si>
+    <t>MM2716Q (EPROM)</t>
   </si>
 </sst>
 </file>
@@ -1354,11 +1363,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1673,15 +1682,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A507EC0B-FECA-46C5-861D-53A4B99CDA9D}">
-  <dimension ref="A1:G283"/>
+  <dimension ref="A1:I283"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="3" max="3" width="15.83984375" customWidth="1"/>
     <col min="4" max="4" width="15.5234375" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.20703125" customWidth="1"/>
+    <col min="7" max="7" width="31.3125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.15625" customWidth="1"/>
+    <col min="9" max="9" width="53.9453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
         <v>343</v>
       </c>
@@ -1703,8 +1714,14 @@
       <c r="G1" t="s">
         <v>125</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H1" t="s">
+        <v>426</v>
+      </c>
+      <c r="I1" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A2">
         <v>79</v>
       </c>
@@ -1715,7 +1732,7 @@
         <v>77</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>385</v>
+        <v>379</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -1724,11 +1741,11 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A3">
         <v>71</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="3" t="s">
         <v>70</v>
       </c>
       <c r="E3">
@@ -1738,7 +1755,7 @@
         <v>1.6</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A4">
         <v>96</v>
       </c>
@@ -1755,7 +1772,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A5">
         <v>104</v>
       </c>
@@ -1772,7 +1789,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A6">
         <v>199</v>
       </c>
@@ -1789,7 +1806,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A7">
         <v>121</v>
       </c>
@@ -1800,7 +1817,7 @@
         <v>118</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>412</v>
+        <v>404</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -1809,7 +1826,7 @@
         <v>2.4</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A8">
         <v>75</v>
       </c>
@@ -1820,7 +1837,7 @@
         <v>73</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>424</v>
+        <v>416</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -1829,7 +1846,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A9">
         <v>97</v>
       </c>
@@ -1846,7 +1863,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A10">
         <v>83</v>
       </c>
@@ -1857,7 +1874,7 @@
         <v>81</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>413</v>
+        <v>405</v>
       </c>
       <c r="E10">
         <v>1</v>
@@ -1866,7 +1883,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A11">
         <v>98</v>
       </c>
@@ -1883,7 +1900,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A12">
         <v>99</v>
       </c>
@@ -1900,7 +1917,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A13">
         <v>100</v>
       </c>
@@ -1917,7 +1934,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A14">
         <v>101</v>
       </c>
@@ -1934,7 +1951,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A15">
         <v>102</v>
       </c>
@@ -1951,7 +1968,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A16">
         <v>174</v>
       </c>
@@ -1962,7 +1979,7 @@
         <v>168</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>414</v>
+        <v>406</v>
       </c>
       <c r="E16">
         <v>1</v>
@@ -1982,7 +1999,7 @@
         <v>169</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>415</v>
+        <v>407</v>
       </c>
       <c r="E17">
         <v>1</v>
@@ -2012,7 +2029,7 @@
       <c r="A19">
         <v>72</v>
       </c>
-      <c r="B19" s="4" t="s">
+      <c r="B19" s="3" t="s">
         <v>71</v>
       </c>
       <c r="E19">
@@ -2033,7 +2050,7 @@
         <v>239</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>416</v>
+        <v>408</v>
       </c>
       <c r="E20">
         <v>1</v>
@@ -2053,7 +2070,7 @@
         <v>12</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>417</v>
+        <v>409</v>
       </c>
       <c r="E21">
         <v>1</v>
@@ -2076,7 +2093,7 @@
         <v>13</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>417</v>
+        <v>409</v>
       </c>
       <c r="E22">
         <v>1</v>
@@ -2092,7 +2109,7 @@
       <c r="A23">
         <v>61</v>
       </c>
-      <c r="B23" s="4" t="s">
+      <c r="B23" s="3" t="s">
         <v>61</v>
       </c>
       <c r="E23">
@@ -2113,7 +2130,7 @@
         <v>10</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>418</v>
+        <v>410</v>
       </c>
       <c r="E24">
         <v>1</v>
@@ -2136,7 +2153,7 @@
         <v>242</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>419</v>
+        <v>411</v>
       </c>
       <c r="E25">
         <v>1</v>
@@ -2149,7 +2166,7 @@
       <c r="A26">
         <v>62</v>
       </c>
-      <c r="B26" s="4" t="s">
+      <c r="B26" s="3" t="s">
         <v>60</v>
       </c>
       <c r="E26">
@@ -2170,7 +2187,7 @@
         <v>51</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>420</v>
+        <v>412</v>
       </c>
       <c r="E27">
         <v>1</v>
@@ -2190,7 +2207,7 @@
         <v>40</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>420</v>
+        <v>412</v>
       </c>
       <c r="E28">
         <v>1</v>
@@ -2210,7 +2227,7 @@
         <v>38</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>421</v>
+        <v>413</v>
       </c>
       <c r="E29">
         <v>1</v>
@@ -2230,7 +2247,7 @@
         <v>39</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>416</v>
+        <v>408</v>
       </c>
       <c r="E30">
         <v>1</v>
@@ -2260,7 +2277,7 @@
       <c r="A32">
         <v>1</v>
       </c>
-      <c r="B32" s="4" t="s">
+      <c r="B32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="E32">
@@ -2277,7 +2294,7 @@
       <c r="A33">
         <v>15</v>
       </c>
-      <c r="B33" s="4" t="s">
+      <c r="B33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="E33">
@@ -2294,7 +2311,7 @@
       <c r="A34">
         <v>24</v>
       </c>
-      <c r="B34" s="4" t="s">
+      <c r="B34" s="3" t="s">
         <v>3</v>
       </c>
       <c r="E34">
@@ -2311,7 +2328,7 @@
       <c r="A35">
         <v>48</v>
       </c>
-      <c r="B35" s="4" t="s">
+      <c r="B35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="E35">
@@ -2328,7 +2345,7 @@
       <c r="A36">
         <v>74</v>
       </c>
-      <c r="B36" s="4" t="s">
+      <c r="B36" s="3" t="s">
         <v>3</v>
       </c>
       <c r="E36">
@@ -2345,7 +2362,7 @@
       <c r="A37">
         <v>108</v>
       </c>
-      <c r="B37" s="4" t="s">
+      <c r="B37" s="3" t="s">
         <v>3</v>
       </c>
       <c r="E37">
@@ -2362,7 +2379,7 @@
       <c r="A38">
         <v>125</v>
       </c>
-      <c r="B38" s="4" t="s">
+      <c r="B38" s="3" t="s">
         <v>3</v>
       </c>
       <c r="E38">
@@ -2379,7 +2396,7 @@
       <c r="A39">
         <v>130</v>
       </c>
-      <c r="B39" s="4" t="s">
+      <c r="B39" s="3" t="s">
         <v>3</v>
       </c>
       <c r="E39">
@@ -2396,7 +2413,7 @@
       <c r="A40">
         <v>144</v>
       </c>
-      <c r="B40" s="4" t="s">
+      <c r="B40" s="3" t="s">
         <v>3</v>
       </c>
       <c r="E40">
@@ -2413,7 +2430,7 @@
       <c r="A41">
         <v>163</v>
       </c>
-      <c r="B41" s="4" t="s">
+      <c r="B41" s="3" t="s">
         <v>3</v>
       </c>
       <c r="E41">
@@ -2430,7 +2447,7 @@
       <c r="A42">
         <v>186</v>
       </c>
-      <c r="B42" s="4" t="s">
+      <c r="B42" s="3" t="s">
         <v>3</v>
       </c>
       <c r="E42">
@@ -2447,7 +2464,7 @@
       <c r="A43">
         <v>195</v>
       </c>
-      <c r="B43" s="4" t="s">
+      <c r="B43" s="3" t="s">
         <v>3</v>
       </c>
       <c r="E43">
@@ -2464,7 +2481,7 @@
       <c r="A44">
         <v>213</v>
       </c>
-      <c r="B44" s="4" t="s">
+      <c r="B44" s="3" t="s">
         <v>3</v>
       </c>
       <c r="E44">
@@ -2481,7 +2498,7 @@
       <c r="A45">
         <v>221</v>
       </c>
-      <c r="B45" s="4" t="s">
+      <c r="B45" s="3" t="s">
         <v>3</v>
       </c>
       <c r="E45">
@@ -2498,7 +2515,7 @@
       <c r="A46">
         <v>248</v>
       </c>
-      <c r="B46" s="4" t="s">
+      <c r="B46" s="3" t="s">
         <v>3</v>
       </c>
       <c r="E46">
@@ -2515,7 +2532,7 @@
       <c r="A47">
         <v>264</v>
       </c>
-      <c r="B47" s="4" t="s">
+      <c r="B47" s="3" t="s">
         <v>3</v>
       </c>
       <c r="E47">
@@ -2562,7 +2579,7 @@
         <v>6</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>393</v>
+        <v>387</v>
       </c>
       <c r="E49">
         <v>1</v>
@@ -2631,7 +2648,7 @@
         <v>254</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="E52">
         <v>1</v>
@@ -2654,7 +2671,7 @@
         <v>247</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="E53">
         <v>1</v>
@@ -2677,7 +2694,7 @@
         <v>248</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="E54">
         <v>1</v>
@@ -2700,7 +2717,7 @@
         <v>249</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>392</v>
+        <v>386</v>
       </c>
       <c r="E55">
         <v>1</v>
@@ -2723,7 +2740,7 @@
         <v>250</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="E56">
         <v>1</v>
@@ -2746,7 +2763,7 @@
         <v>251</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="E57">
         <v>1</v>
@@ -2769,7 +2786,7 @@
         <v>252</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="E58">
         <v>1</v>
@@ -2792,7 +2809,7 @@
         <v>7</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="E59">
         <v>1</v>
@@ -2815,7 +2832,7 @@
         <v>57</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="E60">
         <v>1</v>
@@ -2838,7 +2855,7 @@
         <v>58</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="E61">
         <v>1</v>
@@ -2861,7 +2878,7 @@
         <v>49</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="E62">
         <v>1</v>
@@ -2884,7 +2901,7 @@
         <v>48</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="E63">
         <v>1</v>
@@ -2907,7 +2924,7 @@
         <v>29</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="E64">
         <v>1</v>
@@ -2930,7 +2947,7 @@
         <v>30</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="E65">
         <v>1</v>
@@ -2953,7 +2970,7 @@
         <v>31</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="E66">
         <v>1</v>
@@ -2976,7 +2993,7 @@
         <v>22</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="E67">
         <v>1</v>
@@ -3022,7 +3039,7 @@
         <v>23</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="E69">
         <v>1</v>
@@ -3045,7 +3062,7 @@
         <v>24</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E70">
         <v>1</v>
@@ -3068,7 +3085,7 @@
         <v>8</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E71">
         <v>1</v>
@@ -3091,7 +3108,7 @@
         <v>9</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="E72">
         <v>1</v>
@@ -3114,7 +3131,7 @@
         <v>15</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="E73">
         <v>1</v>
@@ -3137,7 +3154,7 @@
         <v>16</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="E74">
         <v>1</v>
@@ -3160,7 +3177,7 @@
         <v>120</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>395</v>
+        <v>389</v>
       </c>
       <c r="E75">
         <v>1</v>
@@ -3183,7 +3200,7 @@
         <v>121</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>395</v>
+        <v>389</v>
       </c>
       <c r="E76">
         <v>1</v>
@@ -3206,7 +3223,7 @@
         <v>119</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>395</v>
+        <v>389</v>
       </c>
       <c r="E77">
         <v>1</v>
@@ -3229,7 +3246,7 @@
         <v>110</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="E78">
         <v>1</v>
@@ -3251,8 +3268,8 @@
       <c r="C79" t="s">
         <v>41</v>
       </c>
-      <c r="D79" s="3" t="s">
-        <v>353</v>
+      <c r="D79" s="2" t="s">
+        <v>360</v>
       </c>
       <c r="E79">
         <v>1</v>
@@ -3275,7 +3292,7 @@
         <v>106</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>408</v>
+        <v>401</v>
       </c>
       <c r="E80">
         <v>1</v>
@@ -3298,7 +3315,7 @@
         <v>107</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>408</v>
+        <v>401</v>
       </c>
       <c r="E81">
         <v>1</v>
@@ -3321,7 +3338,7 @@
         <v>108</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>407</v>
+        <v>400</v>
       </c>
       <c r="E82">
         <v>1</v>
@@ -3344,7 +3361,7 @@
         <v>109</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>409</v>
+        <v>402</v>
       </c>
       <c r="E83">
         <v>1</v>
@@ -3367,7 +3384,7 @@
         <v>92</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="E84">
         <v>1</v>
@@ -3390,7 +3407,7 @@
         <v>91</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>380</v>
+        <v>374</v>
       </c>
       <c r="E85">
         <v>1</v>
@@ -3413,7 +3430,7 @@
         <v>74</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E86">
         <v>1</v>
@@ -3436,7 +3453,7 @@
         <v>101</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E87">
         <v>1</v>
@@ -3459,7 +3476,7 @@
         <v>75</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="E88">
         <v>1</v>
@@ -3482,7 +3499,7 @@
         <v>82</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="E89">
         <v>1</v>
@@ -3528,7 +3545,7 @@
         <v>80</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>422</v>
+        <v>414</v>
       </c>
       <c r="E91">
         <v>1</v>
@@ -3551,7 +3568,7 @@
         <v>76</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="E92">
         <v>1</v>
@@ -3652,7 +3669,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A97">
         <v>136</v>
       </c>
@@ -3663,7 +3680,7 @@
         <v>132</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="E97">
         <v>1</v>
@@ -3675,7 +3692,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A98">
         <v>137</v>
       </c>
@@ -3686,7 +3703,7 @@
         <v>133</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="E98">
         <v>1</v>
@@ -3698,7 +3715,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="99" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A99">
         <v>129</v>
       </c>
@@ -3709,7 +3726,7 @@
         <v>126</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>406</v>
+        <v>399</v>
       </c>
       <c r="E99">
         <v>1</v>
@@ -3721,7 +3738,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="100" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A100">
         <v>126</v>
       </c>
@@ -3732,7 +3749,7 @@
         <v>122</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>404</v>
+        <v>397</v>
       </c>
       <c r="E100">
         <v>1</v>
@@ -3744,7 +3761,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="101" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A101">
         <v>26</v>
       </c>
@@ -3755,7 +3772,7 @@
         <v>26</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="E101">
         <v>1</v>
@@ -3767,7 +3784,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="102" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A102">
         <v>127</v>
       </c>
@@ -3777,7 +3794,7 @@
       <c r="C102" t="s">
         <v>123</v>
       </c>
-      <c r="D102" s="2">
+      <c r="D102" s="5">
         <v>2716</v>
       </c>
       <c r="E102">
@@ -3790,7 +3807,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A103">
         <v>128</v>
       </c>
@@ -3800,7 +3817,7 @@
       <c r="C103" t="s">
         <v>124</v>
       </c>
-      <c r="D103" s="2">
+      <c r="D103" s="5">
         <v>2716</v>
       </c>
       <c r="E103">
@@ -3810,10 +3827,13 @@
         <v>3.1</v>
       </c>
       <c r="G103" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+        <v>279</v>
+      </c>
+      <c r="H103" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A104">
         <v>141</v>
       </c>
@@ -3836,7 +3856,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="105" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A105">
         <v>134</v>
       </c>
@@ -3859,7 +3879,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A106">
         <v>133</v>
       </c>
@@ -3870,7 +3890,7 @@
         <v>129</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="E106">
         <v>1</v>
@@ -3882,7 +3902,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="107" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A107">
         <v>132</v>
       </c>
@@ -3893,7 +3913,7 @@
         <v>128</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>379</v>
+        <v>373</v>
       </c>
       <c r="E107">
         <v>1</v>
@@ -3905,7 +3925,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="108" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A108">
         <v>131</v>
       </c>
@@ -3928,7 +3948,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="109" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A109">
         <v>172</v>
       </c>
@@ -3939,7 +3959,7 @@
         <v>166</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>405</v>
+        <v>398</v>
       </c>
       <c r="E109">
         <v>1</v>
@@ -3951,7 +3971,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="110" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A110">
         <v>173</v>
       </c>
@@ -3974,7 +3994,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="111" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A111">
         <v>145</v>
       </c>
@@ -3997,7 +4017,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="112" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A112">
         <v>27</v>
       </c>
@@ -4008,7 +4028,7 @@
         <v>27</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="E112">
         <v>1</v>
@@ -4100,7 +4120,7 @@
         <v>177</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>410</v>
+        <v>403</v>
       </c>
       <c r="E116">
         <v>1</v>
@@ -4123,7 +4143,7 @@
         <v>175</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="E117">
         <v>1</v>
@@ -4146,7 +4166,7 @@
         <v>161</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
       <c r="E118">
         <v>1</v>
@@ -4169,7 +4189,7 @@
         <v>162</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="E119">
         <v>1</v>
@@ -4192,7 +4212,7 @@
         <v>163</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>378</v>
+        <v>421</v>
       </c>
       <c r="E120">
         <v>1</v>
@@ -4215,7 +4235,7 @@
         <v>164</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="E121">
         <v>1</v>
@@ -4238,7 +4258,7 @@
         <v>165</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="E122">
         <v>1</v>
@@ -4261,7 +4281,7 @@
         <v>17</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="E123">
         <v>1</v>
@@ -4284,7 +4304,7 @@
         <v>171</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>396</v>
+        <v>420</v>
       </c>
       <c r="E124">
         <v>1</v>
@@ -4399,7 +4419,7 @@
         <v>218</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>411</v>
+        <v>417</v>
       </c>
       <c r="E129">
         <v>1</v>
@@ -4422,7 +4442,7 @@
         <v>215</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="E130">
         <v>1</v>
@@ -4445,7 +4465,7 @@
         <v>205</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="E131">
         <v>1</v>
@@ -4468,7 +4488,7 @@
         <v>206</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>391</v>
+        <v>385</v>
       </c>
       <c r="E132">
         <v>1</v>
@@ -4491,7 +4511,7 @@
         <v>207</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>393</v>
+        <v>387</v>
       </c>
       <c r="E133">
         <v>1</v>
@@ -4514,7 +4534,7 @@
         <v>18</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="E134">
         <v>1</v>
@@ -4534,10 +4554,10 @@
         <v>208</v>
       </c>
       <c r="C135" t="s">
-        <v>201</v>
+        <v>425</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>394</v>
+        <v>355</v>
       </c>
       <c r="E135">
         <v>1</v>
@@ -4557,10 +4577,10 @@
         <v>201</v>
       </c>
       <c r="C136" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>356</v>
+        <v>388</v>
       </c>
       <c r="E136">
         <v>1</v>
@@ -4580,10 +4600,10 @@
         <v>199</v>
       </c>
       <c r="C137" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>366</v>
+        <v>355</v>
       </c>
       <c r="E137">
         <v>1</v>
@@ -4606,7 +4626,7 @@
         <v>193</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>361</v>
+        <v>422</v>
       </c>
       <c r="E138">
         <v>1</v>
@@ -4629,7 +4649,7 @@
         <v>203</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="E139">
         <v>1</v>
@@ -4744,7 +4764,7 @@
         <v>219</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>373</v>
+        <v>419</v>
       </c>
       <c r="E144">
         <v>1</v>
@@ -4767,7 +4787,7 @@
         <v>19</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>382</v>
+        <v>376</v>
       </c>
       <c r="E145">
         <v>1</v>
@@ -4790,7 +4810,7 @@
         <v>216</v>
       </c>
       <c r="D146" s="2" t="s">
-        <v>374</v>
+        <v>418</v>
       </c>
       <c r="E146">
         <v>1</v>
@@ -4813,7 +4833,7 @@
         <v>209</v>
       </c>
       <c r="D147" s="2" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="E147">
         <v>1</v>
@@ -4836,7 +4856,7 @@
         <v>210</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>393</v>
+        <v>387</v>
       </c>
       <c r="E148">
         <v>1</v>
@@ -4859,7 +4879,7 @@
         <v>211</v>
       </c>
       <c r="D149" s="2" t="s">
-        <v>393</v>
+        <v>387</v>
       </c>
       <c r="E149">
         <v>1</v>
@@ -4882,7 +4902,7 @@
         <v>202</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E150">
         <v>1</v>
@@ -4928,7 +4948,7 @@
         <v>197</v>
       </c>
       <c r="D152" s="2" t="s">
-        <v>397</v>
+        <v>390</v>
       </c>
       <c r="E152">
         <v>1</v>
@@ -4951,7 +4971,7 @@
         <v>194</v>
       </c>
       <c r="D153" s="2" t="s">
-        <v>398</v>
+        <v>391</v>
       </c>
       <c r="E153">
         <v>1</v>
@@ -5445,7 +5465,7 @@
         <v>62</v>
       </c>
       <c r="D181" s="2" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="E181">
         <v>1</v>
@@ -5468,7 +5488,7 @@
         <v>50</v>
       </c>
       <c r="D182" s="2" t="s">
-        <v>403</v>
+        <v>396</v>
       </c>
       <c r="E182">
         <v>1</v>
@@ -5508,7 +5528,7 @@
         <v>47</v>
       </c>
       <c r="D184" s="2" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="E184">
         <v>1</v>
@@ -5528,7 +5548,7 @@
         <v>46</v>
       </c>
       <c r="D185" s="2" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="E185">
         <v>1</v>
@@ -5568,7 +5588,7 @@
         <v>44</v>
       </c>
       <c r="D187" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E187">
         <v>1</v>
@@ -5588,7 +5608,7 @@
         <v>43</v>
       </c>
       <c r="D188" s="2" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="E188">
         <v>1</v>
@@ -5631,7 +5651,7 @@
         <v>33</v>
       </c>
       <c r="D190" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E190">
         <v>1</v>
@@ -5677,7 +5697,7 @@
         <v>63</v>
       </c>
       <c r="D192" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E192">
         <v>1</v>
@@ -5723,7 +5743,7 @@
         <v>104</v>
       </c>
       <c r="D194" s="2" t="s">
-        <v>384</v>
+        <v>378</v>
       </c>
       <c r="E194">
         <v>1</v>
@@ -5743,7 +5763,7 @@
         <v>105</v>
       </c>
       <c r="D195" s="2" t="s">
-        <v>383</v>
+        <v>377</v>
       </c>
       <c r="E195">
         <v>1</v>
@@ -5763,7 +5783,7 @@
         <v>159</v>
       </c>
       <c r="D196" s="2" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="E196">
         <v>1</v>
@@ -5829,7 +5849,7 @@
         <v>21</v>
       </c>
       <c r="D199" s="2" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="E199">
         <v>1</v>
@@ -5852,7 +5872,7 @@
         <v>4</v>
       </c>
       <c r="D200" s="2" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="E200">
         <v>1</v>
@@ -5872,10 +5892,10 @@
         <v>5</v>
       </c>
       <c r="C201" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="D201" s="2" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="E201">
         <v>1</v>
@@ -5898,7 +5918,7 @@
         <v>14</v>
       </c>
       <c r="D202" s="2" t="s">
-        <v>386</v>
+        <v>380</v>
       </c>
       <c r="E202">
         <v>1</v>
@@ -5955,7 +5975,7 @@
         <v>64</v>
       </c>
       <c r="D205" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E205">
         <v>1</v>
@@ -6080,7 +6100,7 @@
         <v>103</v>
       </c>
       <c r="D212" s="2" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="E212">
         <v>1</v>
@@ -6160,7 +6180,7 @@
         <v>65</v>
       </c>
       <c r="D216" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E216">
         <v>1</v>
@@ -6243,7 +6263,7 @@
         <v>148</v>
       </c>
       <c r="D220" s="2" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="E220">
         <v>1</v>
@@ -6266,7 +6286,7 @@
         <v>149</v>
       </c>
       <c r="D221" s="2" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="E221">
         <v>1</v>
@@ -6289,7 +6309,7 @@
         <v>150</v>
       </c>
       <c r="D222" s="2" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="E222">
         <v>1</v>
@@ -6312,7 +6332,7 @@
         <v>151</v>
       </c>
       <c r="D223" s="2" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="E223">
         <v>1</v>
@@ -6335,7 +6355,7 @@
         <v>152</v>
       </c>
       <c r="D224" s="2" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="E224">
         <v>1</v>
@@ -6347,7 +6367,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="225" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="225" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A225">
         <v>158</v>
       </c>
@@ -6358,7 +6378,7 @@
         <v>153</v>
       </c>
       <c r="D225" s="2" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="E225">
         <v>1</v>
@@ -6370,7 +6390,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="226" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="226" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A226">
         <v>159</v>
       </c>
@@ -6381,7 +6401,7 @@
         <v>154</v>
       </c>
       <c r="D226" s="2" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="E226">
         <v>1</v>
@@ -6393,7 +6413,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="227" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="227" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A227">
         <v>67</v>
       </c>
@@ -6404,7 +6424,7 @@
         <v>66</v>
       </c>
       <c r="D227" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E227">
         <v>1</v>
@@ -6416,7 +6436,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="228" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="228" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A228">
         <v>160</v>
       </c>
@@ -6427,7 +6447,7 @@
         <v>155</v>
       </c>
       <c r="D228" s="2" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="E228">
         <v>1</v>
@@ -6439,7 +6459,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="229" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="229" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A229">
         <v>161</v>
       </c>
@@ -6450,7 +6470,7 @@
         <v>156</v>
       </c>
       <c r="D229" s="2" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="E229">
         <v>1</v>
@@ -6462,7 +6482,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="230" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="230" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A230">
         <v>162</v>
       </c>
@@ -6473,7 +6493,7 @@
         <v>157</v>
       </c>
       <c r="D230" s="2" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="E230">
         <v>1</v>
@@ -6485,7 +6505,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="231" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="231" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A231">
         <v>176</v>
       </c>
@@ -6496,7 +6516,7 @@
         <v>170</v>
       </c>
       <c r="D231" s="2" t="s">
-        <v>402</v>
+        <v>395</v>
       </c>
       <c r="E231">
         <v>1</v>
@@ -6507,8 +6527,11 @@
       <c r="G231" t="s">
         <v>328</v>
       </c>
-    </row>
-    <row r="232" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="I231" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="232" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A232">
         <v>196</v>
       </c>
@@ -6519,7 +6542,7 @@
         <v>188</v>
       </c>
       <c r="D232" s="2" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="E232">
         <v>1</v>
@@ -6531,7 +6554,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="233" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="233" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A233">
         <v>200</v>
       </c>
@@ -6542,7 +6565,7 @@
         <v>192</v>
       </c>
       <c r="D233" s="2" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="E233">
         <v>1</v>
@@ -6554,7 +6577,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="234" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="234" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A234">
         <v>204</v>
       </c>
@@ -6571,7 +6594,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="235" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="235" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A235">
         <v>207</v>
       </c>
@@ -6588,7 +6611,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="236" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="236" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A236">
         <v>178</v>
       </c>
@@ -6599,7 +6622,7 @@
         <v>172</v>
       </c>
       <c r="D236" s="2" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="E236">
         <v>1</v>
@@ -6611,7 +6634,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="237" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="237" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A237">
         <v>179</v>
       </c>
@@ -6622,7 +6645,7 @@
         <v>173</v>
       </c>
       <c r="D237" s="2" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="E237">
         <v>1</v>
@@ -6634,7 +6657,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="238" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="238" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A238">
         <v>230</v>
       </c>
@@ -6645,7 +6668,7 @@
         <v>220</v>
       </c>
       <c r="D238" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E238">
         <v>1</v>
@@ -6657,7 +6680,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="239" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="239" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A239">
         <v>231</v>
       </c>
@@ -6668,7 +6691,7 @@
         <v>221</v>
       </c>
       <c r="D239" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E239">
         <v>1</v>
@@ -6680,7 +6703,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="240" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="240" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A240">
         <v>232</v>
       </c>
@@ -6691,7 +6714,7 @@
         <v>222</v>
       </c>
       <c r="D240" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E240">
         <v>1</v>
@@ -6714,7 +6737,7 @@
         <v>223</v>
       </c>
       <c r="D241" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E241">
         <v>1</v>
@@ -6737,7 +6760,7 @@
         <v>224</v>
       </c>
       <c r="D242" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E242">
         <v>1</v>
@@ -6753,14 +6776,14 @@
       <c r="A243">
         <v>235</v>
       </c>
-      <c r="B243" s="5" t="s">
+      <c r="B243" s="4" t="s">
         <v>225</v>
       </c>
       <c r="C243" t="s">
         <v>225</v>
       </c>
       <c r="D243" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E243">
         <v>1</v>
@@ -6783,7 +6806,7 @@
         <v>226</v>
       </c>
       <c r="D244" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E244">
         <v>1</v>
@@ -6806,7 +6829,7 @@
         <v>227</v>
       </c>
       <c r="D245" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E245">
         <v>1</v>
@@ -6829,7 +6852,7 @@
         <v>228</v>
       </c>
       <c r="D246" s="2" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="E246">
         <v>1</v>
@@ -6852,7 +6875,7 @@
         <v>229</v>
       </c>
       <c r="D247" s="2" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="E247">
         <v>1</v>
@@ -6875,7 +6898,7 @@
         <v>67</v>
       </c>
       <c r="D248" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E248">
         <v>1</v>
@@ -6898,7 +6921,7 @@
         <v>230</v>
       </c>
       <c r="D249" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E249">
         <v>1</v>
@@ -6921,7 +6944,7 @@
         <v>231</v>
       </c>
       <c r="D250" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E250">
         <v>1</v>
@@ -6944,7 +6967,7 @@
         <v>232</v>
       </c>
       <c r="D251" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E251">
         <v>1</v>
@@ -6967,7 +6990,7 @@
         <v>233</v>
       </c>
       <c r="D252" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E252">
         <v>1</v>
@@ -6990,7 +7013,7 @@
         <v>234</v>
       </c>
       <c r="D253" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E253">
         <v>1</v>
@@ -7013,7 +7036,7 @@
         <v>235</v>
       </c>
       <c r="D254" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E254">
         <v>1</v>
@@ -7036,7 +7059,7 @@
         <v>236</v>
       </c>
       <c r="D255" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E255">
         <v>1</v>
@@ -7059,7 +7082,7 @@
         <v>237</v>
       </c>
       <c r="D256" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E256">
         <v>1</v>
@@ -7082,7 +7105,7 @@
         <v>256</v>
       </c>
       <c r="D257" s="2" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="E257">
         <v>1</v>
@@ -7105,7 +7128,7 @@
         <v>257</v>
       </c>
       <c r="D258" s="2" t="s">
-        <v>377</v>
+        <v>370</v>
       </c>
       <c r="E258">
         <v>1</v>
@@ -7128,7 +7151,7 @@
         <v>258</v>
       </c>
       <c r="D259" s="2" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="E259">
         <v>1</v>
@@ -7151,7 +7174,7 @@
         <v>259</v>
       </c>
       <c r="D260" s="2" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="E260">
         <v>1</v>
@@ -7174,7 +7197,7 @@
         <v>260</v>
       </c>
       <c r="D261" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E261">
         <v>1</v>
@@ -7197,7 +7220,7 @@
         <v>261</v>
       </c>
       <c r="D262" s="2" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="E262">
         <v>1</v>
@@ -7220,7 +7243,7 @@
         <v>262</v>
       </c>
       <c r="D263" s="2" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="E263">
         <v>1</v>
@@ -7243,7 +7266,7 @@
         <v>263</v>
       </c>
       <c r="D264" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E264">
         <v>1</v>
@@ -7266,7 +7289,7 @@
         <v>213</v>
       </c>
       <c r="D265" s="2" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="E265">
         <v>1</v>
@@ -7286,7 +7309,7 @@
         <v>240</v>
       </c>
       <c r="D266" s="2" t="s">
-        <v>399</v>
+        <v>392</v>
       </c>
       <c r="E266">
         <v>1</v>
@@ -7309,7 +7332,7 @@
         <v>241</v>
       </c>
       <c r="D267" s="2" t="s">
-        <v>399</v>
+        <v>392</v>
       </c>
       <c r="E267">
         <v>1</v>
@@ -7332,7 +7355,7 @@
         <v>243</v>
       </c>
       <c r="D268" s="2" t="s">
-        <v>401</v>
+        <v>394</v>
       </c>
       <c r="E268">
         <v>1</v>
@@ -7352,7 +7375,7 @@
         <v>68</v>
       </c>
       <c r="D269" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E269">
         <v>1</v>
@@ -7398,7 +7421,7 @@
         <v>217</v>
       </c>
       <c r="D271" s="2" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="E271">
         <v>1</v>
@@ -7421,7 +7444,7 @@
         <v>189</v>
       </c>
       <c r="D272" s="2" t="s">
-        <v>400</v>
+        <v>393</v>
       </c>
       <c r="E272">
         <v>1</v>
@@ -7444,7 +7467,7 @@
         <v>190</v>
       </c>
       <c r="D273" s="2" t="s">
-        <v>400</v>
+        <v>393</v>
       </c>
       <c r="E273">
         <v>1</v>
@@ -7550,7 +7573,7 @@
         <v>78</v>
       </c>
       <c r="D278" s="2" t="s">
-        <v>388</v>
+        <v>382</v>
       </c>
       <c r="E278">
         <v>1</v>
@@ -7570,7 +7593,7 @@
         <v>79</v>
       </c>
       <c r="D279" s="2" t="s">
-        <v>387</v>
+        <v>381</v>
       </c>
       <c r="E279">
         <v>1</v>
@@ -7631,7 +7654,7 @@
         <v>11</v>
       </c>
       <c r="D282" s="2" t="s">
-        <v>381</v>
+        <v>375</v>
       </c>
       <c r="E282">
         <v>1</v>
@@ -7654,7 +7677,7 @@
         <v>158</v>
       </c>
       <c r="D283" s="2" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="E283">
         <v>1</v>

--- a/sch/components.xlsx
+++ b/sch/components.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\miha\Desktop\vezje-idp\kicad\sch\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F7835F9-2275-499B-89E0-5C8DAB8BD279}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14C65A4B-2133-462B-A69A-AB3DCDD4AC7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12552" xr2:uid="{6172FD7F-16CD-47D1-A3E4-D63AC8EC044E}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="929" uniqueCount="428">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="932" uniqueCount="431">
   <si>
     <t>ID</t>
   </si>
@@ -1309,6 +1309,15 @@
   </si>
   <si>
     <t>MM2716Q (EPROM)</t>
+  </si>
+  <si>
+    <t># Pads</t>
+  </si>
+  <si>
+    <t>Circular</t>
+  </si>
+  <si>
+    <t>Square</t>
   </si>
 </sst>
 </file>
@@ -1357,7 +1366,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1365,9 +1374,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1682,17 +1688,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A507EC0B-FECA-46C5-861D-53A4B99CDA9D}">
-  <dimension ref="A1:I283"/>
+  <dimension ref="A1:L284"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="3" max="3" width="15.83984375" customWidth="1"/>
     <col min="4" max="4" width="15.5234375" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="31.3125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.15625" customWidth="1"/>
-    <col min="9" max="9" width="53.9453125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="31.3125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16.15625" customWidth="1"/>
+    <col min="12" max="12" width="53.9453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
         <v>343</v>
       </c>
@@ -1709,19 +1715,28 @@
         <v>2</v>
       </c>
       <c r="F1" t="s">
-        <v>1</v>
+        <v>428</v>
       </c>
       <c r="G1" t="s">
+        <v>429</v>
+      </c>
+      <c r="H1" t="s">
+        <v>430</v>
+      </c>
+      <c r="I1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J1" t="s">
         <v>125</v>
       </c>
-      <c r="H1" t="s">
+      <c r="K1" t="s">
         <v>426</v>
       </c>
-      <c r="I1" t="s">
+      <c r="L1" t="s">
         <v>423</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A2">
         <v>79</v>
       </c>
@@ -1738,10 +1753,20 @@
         <v>1</v>
       </c>
       <c r="F2">
+        <v>3</v>
+      </c>
+      <c r="G2">
+        <f>F2-H2</f>
+        <v>3</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
         <v>2.1</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A3">
         <v>71</v>
       </c>
@@ -1752,10 +1777,20 @@
         <v>1</v>
       </c>
       <c r="F3">
+        <v>2</v>
+      </c>
+      <c r="G3">
+        <f t="shared" ref="G3:G66" si="0">F3-H3</f>
+        <v>2</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
         <v>1.6</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A4">
         <v>96</v>
       </c>
@@ -1766,13 +1801,23 @@
         <v>1</v>
       </c>
       <c r="F4">
+        <v>2</v>
+      </c>
+      <c r="G4">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
         <v>2.2000000000000002</v>
       </c>
-      <c r="G4" t="s">
+      <c r="J4" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A5">
         <v>104</v>
       </c>
@@ -1783,13 +1828,23 @@
         <v>1</v>
       </c>
       <c r="F5">
+        <v>2</v>
+      </c>
+      <c r="G5">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
         <v>2.2000000000000002</v>
       </c>
-      <c r="G5" t="s">
+      <c r="J5" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A6">
         <v>199</v>
       </c>
@@ -1800,13 +1855,23 @@
         <v>1</v>
       </c>
       <c r="F6">
+        <v>2</v>
+      </c>
+      <c r="G6">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
         <v>5.2</v>
       </c>
-      <c r="G6" t="s">
+      <c r="J6" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A7">
         <v>121</v>
       </c>
@@ -1823,10 +1888,20 @@
         <v>1</v>
       </c>
       <c r="F7">
+        <v>2</v>
+      </c>
+      <c r="G7">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
         <v>2.4</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A8">
         <v>75</v>
       </c>
@@ -1843,10 +1918,20 @@
         <v>1</v>
       </c>
       <c r="F8">
+        <v>2</v>
+      </c>
+      <c r="G8">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
         <v>2.1</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A9">
         <v>97</v>
       </c>
@@ -1857,13 +1942,23 @@
         <v>1</v>
       </c>
       <c r="F9">
+        <v>2</v>
+      </c>
+      <c r="G9">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
         <v>2.2000000000000002</v>
       </c>
-      <c r="G9" t="s">
+      <c r="J9" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A10">
         <v>83</v>
       </c>
@@ -1880,10 +1975,20 @@
         <v>1</v>
       </c>
       <c r="F10">
+        <v>2</v>
+      </c>
+      <c r="G10">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
         <v>2.1</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A11">
         <v>98</v>
       </c>
@@ -1894,13 +1999,23 @@
         <v>1</v>
       </c>
       <c r="F11">
+        <v>2</v>
+      </c>
+      <c r="G11">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
         <v>2.2000000000000002</v>
       </c>
-      <c r="G11" t="s">
+      <c r="J11" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A12">
         <v>99</v>
       </c>
@@ -1911,13 +2026,23 @@
         <v>1</v>
       </c>
       <c r="F12">
+        <v>2</v>
+      </c>
+      <c r="G12">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
         <v>2.2000000000000002</v>
       </c>
-      <c r="G12" t="s">
+      <c r="J12" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A13">
         <v>100</v>
       </c>
@@ -1928,13 +2053,23 @@
         <v>1</v>
       </c>
       <c r="F13">
+        <v>2</v>
+      </c>
+      <c r="G13">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
         <v>2.2000000000000002</v>
       </c>
-      <c r="G13" t="s">
+      <c r="J13" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A14">
         <v>101</v>
       </c>
@@ -1945,13 +2080,23 @@
         <v>1</v>
       </c>
       <c r="F14">
+        <v>2</v>
+      </c>
+      <c r="G14">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
         <v>2.2000000000000002</v>
       </c>
-      <c r="G14" t="s">
+      <c r="J14" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A15">
         <v>102</v>
       </c>
@@ -1962,13 +2107,23 @@
         <v>1</v>
       </c>
       <c r="F15">
+        <v>2</v>
+      </c>
+      <c r="G15">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
         <v>2.2000000000000002</v>
       </c>
-      <c r="G15" t="s">
+      <c r="J15" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A16">
         <v>174</v>
       </c>
@@ -1985,10 +2140,20 @@
         <v>1</v>
       </c>
       <c r="F16">
+        <v>2</v>
+      </c>
+      <c r="G16">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+      <c r="I16">
         <v>4.2</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A17">
         <v>175</v>
       </c>
@@ -2005,10 +2170,20 @@
         <v>1</v>
       </c>
       <c r="F17">
+        <v>2</v>
+      </c>
+      <c r="G17">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17">
         <v>4.2</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A18">
         <v>203</v>
       </c>
@@ -2019,13 +2194,23 @@
         <v>1</v>
       </c>
       <c r="F18">
+        <v>2</v>
+      </c>
+      <c r="G18">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="H18">
+        <v>0</v>
+      </c>
+      <c r="I18">
         <v>5.2</v>
       </c>
-      <c r="G18" t="s">
+      <c r="J18" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A19">
         <v>72</v>
       </c>
@@ -2036,10 +2221,20 @@
         <v>1</v>
       </c>
       <c r="F19">
+        <v>2</v>
+      </c>
+      <c r="G19">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="H19">
+        <v>0</v>
+      </c>
+      <c r="I19">
         <v>1.6</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A20">
         <v>250</v>
       </c>
@@ -2056,10 +2251,20 @@
         <v>1</v>
       </c>
       <c r="F20">
+        <v>2</v>
+      </c>
+      <c r="G20">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="H20">
+        <v>0</v>
+      </c>
+      <c r="I20">
         <v>6.1</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A21">
         <v>10</v>
       </c>
@@ -2076,13 +2281,23 @@
         <v>1</v>
       </c>
       <c r="F21">
+        <v>2</v>
+      </c>
+      <c r="G21">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="H21">
+        <v>0</v>
+      </c>
+      <c r="I21">
         <v>1.1000000000000001</v>
       </c>
-      <c r="G21" t="s">
+      <c r="J21" t="s">
         <v>281</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A22">
         <v>11</v>
       </c>
@@ -2099,13 +2314,23 @@
         <v>1</v>
       </c>
       <c r="F22">
+        <v>2</v>
+      </c>
+      <c r="G22">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="H22">
+        <v>0</v>
+      </c>
+      <c r="I22">
         <v>1.1000000000000001</v>
       </c>
-      <c r="G22" t="s">
+      <c r="J22" t="s">
         <v>281</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A23">
         <v>61</v>
       </c>
@@ -2116,10 +2341,20 @@
         <v>1</v>
       </c>
       <c r="F23">
+        <v>2</v>
+      </c>
+      <c r="G23">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="H23">
+        <v>0</v>
+      </c>
+      <c r="I23">
         <v>1.6</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A24">
         <v>8</v>
       </c>
@@ -2136,13 +2371,23 @@
         <v>1</v>
       </c>
       <c r="F24">
+        <v>2</v>
+      </c>
+      <c r="G24">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="H24">
+        <v>0</v>
+      </c>
+      <c r="I24">
         <v>1.1000000000000001</v>
       </c>
-      <c r="G24" s="1" t="s">
+      <c r="J24" s="1" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A25">
         <v>253</v>
       </c>
@@ -2159,10 +2404,20 @@
         <v>1</v>
       </c>
       <c r="F25">
+        <v>2</v>
+      </c>
+      <c r="G25">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="H25">
+        <v>0</v>
+      </c>
+      <c r="I25">
         <v>6.1</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A26">
         <v>62</v>
       </c>
@@ -2173,10 +2428,20 @@
         <v>1</v>
       </c>
       <c r="F26">
+        <v>2</v>
+      </c>
+      <c r="G26">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="H26">
+        <v>0</v>
+      </c>
+      <c r="I26">
         <v>1.6</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A27">
         <v>52</v>
       </c>
@@ -2193,10 +2458,20 @@
         <v>1</v>
       </c>
       <c r="F27">
+        <v>2</v>
+      </c>
+      <c r="G27">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="H27">
+        <v>0</v>
+      </c>
+      <c r="I27">
         <v>1.5</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A28">
         <v>37</v>
       </c>
@@ -2213,10 +2488,20 @@
         <v>1</v>
       </c>
       <c r="F28">
+        <v>2</v>
+      </c>
+      <c r="G28">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="H28">
+        <v>0</v>
+      </c>
+      <c r="I28">
         <v>1.4</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A29">
         <v>34</v>
       </c>
@@ -2233,10 +2518,20 @@
         <v>1</v>
       </c>
       <c r="F29">
+        <v>2</v>
+      </c>
+      <c r="G29">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="H29">
+        <v>0</v>
+      </c>
+      <c r="I29">
         <v>1.4</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A30">
         <v>35</v>
       </c>
@@ -2253,10 +2548,20 @@
         <v>1</v>
       </c>
       <c r="F30">
+        <v>2</v>
+      </c>
+      <c r="G30">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="H30">
+        <v>0</v>
+      </c>
+      <c r="I30">
         <v>1.4</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A31">
         <v>95</v>
       </c>
@@ -2267,13 +2572,23 @@
         <v>1</v>
       </c>
       <c r="F31">
+        <v>2</v>
+      </c>
+      <c r="G31">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="H31">
+        <v>0</v>
+      </c>
+      <c r="I31">
         <v>2.2000000000000002</v>
       </c>
-      <c r="G31" t="s">
+      <c r="J31" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A32">
         <v>1</v>
       </c>
@@ -2284,13 +2599,24 @@
         <v>4</v>
       </c>
       <c r="F32">
+        <f>E32*2</f>
+        <v>8</v>
+      </c>
+      <c r="G32">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="H32">
+        <v>0</v>
+      </c>
+      <c r="I32">
         <v>1.1000000000000001</v>
       </c>
-      <c r="G32" t="s">
+      <c r="J32" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A33">
         <v>15</v>
       </c>
@@ -2301,13 +2627,24 @@
         <v>2</v>
       </c>
       <c r="F33">
+        <f t="shared" ref="F33:F47" si="1">E33*2</f>
+        <v>4</v>
+      </c>
+      <c r="G33">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="H33">
+        <v>0</v>
+      </c>
+      <c r="I33">
         <v>1.2</v>
       </c>
-      <c r="G33" t="s">
+      <c r="J33" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A34">
         <v>24</v>
       </c>
@@ -2318,13 +2655,24 @@
         <v>1</v>
       </c>
       <c r="F34">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="G34">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="H34">
+        <v>0</v>
+      </c>
+      <c r="I34">
         <v>1.3</v>
       </c>
-      <c r="G34" t="s">
+      <c r="J34" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A35">
         <v>48</v>
       </c>
@@ -2335,13 +2683,24 @@
         <v>1</v>
       </c>
       <c r="F35">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="G35">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="H35">
+        <v>0</v>
+      </c>
+      <c r="I35">
         <v>1.4</v>
       </c>
-      <c r="G35" t="s">
+      <c r="J35" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A36">
         <v>74</v>
       </c>
@@ -2352,13 +2711,24 @@
         <v>2</v>
       </c>
       <c r="F36">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="G36">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="H36">
+        <v>0</v>
+      </c>
+      <c r="I36">
         <v>2.1</v>
       </c>
-      <c r="G36" t="s">
+      <c r="J36" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A37">
         <v>108</v>
       </c>
@@ -2369,13 +2739,24 @@
         <v>1</v>
       </c>
       <c r="F37">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="G37">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="H37">
+        <v>0</v>
+      </c>
+      <c r="I37">
         <v>2.2999999999999998</v>
       </c>
-      <c r="G37" t="s">
+      <c r="J37" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A38">
         <v>125</v>
       </c>
@@ -2386,13 +2767,24 @@
         <v>4</v>
       </c>
       <c r="F38">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="G38">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="H38">
+        <v>0</v>
+      </c>
+      <c r="I38">
         <v>3.1</v>
       </c>
-      <c r="G38" t="s">
+      <c r="J38" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A39">
         <v>130</v>
       </c>
@@ -2403,13 +2795,24 @@
         <v>2</v>
       </c>
       <c r="F39">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="G39">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="H39">
+        <v>0</v>
+      </c>
+      <c r="I39">
         <v>3.2</v>
       </c>
-      <c r="G39" t="s">
+      <c r="J39" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A40">
         <v>144</v>
       </c>
@@ -2420,13 +2823,24 @@
         <v>8</v>
       </c>
       <c r="F40">
+        <f t="shared" si="1"/>
+        <v>16</v>
+      </c>
+      <c r="G40">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="H40">
+        <v>0</v>
+      </c>
+      <c r="I40">
         <v>4.0999999999999996</v>
       </c>
-      <c r="G40" t="s">
+      <c r="J40" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A41">
         <v>163</v>
       </c>
@@ -2437,13 +2851,24 @@
         <v>2</v>
       </c>
       <c r="F41">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="G41">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="H41">
+        <v>0</v>
+      </c>
+      <c r="I41">
         <v>4.2</v>
       </c>
-      <c r="G41" t="s">
+      <c r="J41" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A42">
         <v>186</v>
       </c>
@@ -2454,13 +2879,24 @@
         <v>4</v>
       </c>
       <c r="F42">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="G42">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="H42">
+        <v>0</v>
+      </c>
+      <c r="I42">
         <v>5.0999999999999996</v>
       </c>
-      <c r="G42" t="s">
+      <c r="J42" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A43">
         <v>195</v>
       </c>
@@ -2471,13 +2907,24 @@
         <v>5</v>
       </c>
       <c r="F43">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="G43">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="H43">
+        <v>0</v>
+      </c>
+      <c r="I43">
         <v>5.2</v>
       </c>
-      <c r="G43" t="s">
+      <c r="J43" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A44">
         <v>213</v>
       </c>
@@ -2488,13 +2935,24 @@
         <v>1</v>
       </c>
       <c r="F44">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="G44">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="H44">
+        <v>0</v>
+      </c>
+      <c r="I44">
         <v>5.3</v>
       </c>
-      <c r="G44" t="s">
+      <c r="J44" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A45">
         <v>221</v>
       </c>
@@ -2505,13 +2963,24 @@
         <v>1</v>
       </c>
       <c r="F45">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="G45">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="H45">
+        <v>0</v>
+      </c>
+      <c r="I45">
         <v>5.4</v>
       </c>
-      <c r="G45" t="s">
+      <c r="J45" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A46">
         <v>248</v>
       </c>
@@ -2522,13 +2991,24 @@
         <v>2</v>
       </c>
       <c r="F46">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="G46">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="H46">
+        <v>0</v>
+      </c>
+      <c r="I46">
         <v>6.1</v>
       </c>
-      <c r="G46" t="s">
+      <c r="J46" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A47">
         <v>264</v>
       </c>
@@ -2539,13 +3019,24 @@
         <v>1</v>
       </c>
       <c r="F47">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="G47">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="H47">
+        <v>0</v>
+      </c>
+      <c r="I47">
         <v>6.2</v>
       </c>
-      <c r="G47" t="s">
+      <c r="J47" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A48">
         <v>55</v>
       </c>
@@ -2562,13 +3053,23 @@
         <v>1</v>
       </c>
       <c r="F48">
+        <v>16</v>
+      </c>
+      <c r="G48">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="H48">
+        <v>1</v>
+      </c>
+      <c r="I48">
         <v>1.5</v>
       </c>
-      <c r="G48" t="s">
+      <c r="J48" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A49">
         <v>4</v>
       </c>
@@ -2585,13 +3086,23 @@
         <v>1</v>
       </c>
       <c r="F49">
+        <v>14</v>
+      </c>
+      <c r="G49">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="H49">
+        <v>1</v>
+      </c>
+      <c r="I49">
         <v>1.1000000000000001</v>
       </c>
-      <c r="G49" t="s">
+      <c r="J49" t="s">
         <v>273</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A50">
         <v>193</v>
       </c>
@@ -2608,13 +3119,23 @@
         <v>1</v>
       </c>
       <c r="F50">
+        <v>16</v>
+      </c>
+      <c r="G50">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="H50">
+        <v>1</v>
+      </c>
+      <c r="I50">
         <v>5.0999999999999996</v>
       </c>
-      <c r="G50" t="s">
+      <c r="J50" t="s">
         <v>319</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A51">
         <v>194</v>
       </c>
@@ -2631,13 +3152,23 @@
         <v>1</v>
       </c>
       <c r="F51">
+        <v>16</v>
+      </c>
+      <c r="G51">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="H51">
+        <v>1</v>
+      </c>
+      <c r="I51">
         <v>5.0999999999999996</v>
       </c>
-      <c r="G51" t="s">
+      <c r="J51" t="s">
         <v>319</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A52">
         <v>266</v>
       </c>
@@ -2654,13 +3185,23 @@
         <v>1</v>
       </c>
       <c r="F52">
+        <v>14</v>
+      </c>
+      <c r="G52">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="H52">
+        <v>1</v>
+      </c>
+      <c r="I52">
         <v>6.2</v>
       </c>
-      <c r="G52" t="s">
+      <c r="J52" t="s">
         <v>342</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A53">
         <v>258</v>
       </c>
@@ -2677,13 +3218,23 @@
         <v>1</v>
       </c>
       <c r="F53">
+        <v>14</v>
+      </c>
+      <c r="G53">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="H53">
+        <v>1</v>
+      </c>
+      <c r="I53">
         <v>6.1</v>
       </c>
-      <c r="G53" t="s">
+      <c r="J53" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A54">
         <v>259</v>
       </c>
@@ -2700,13 +3251,23 @@
         <v>1</v>
       </c>
       <c r="F54">
+        <v>14</v>
+      </c>
+      <c r="G54">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="H54">
+        <v>1</v>
+      </c>
+      <c r="I54">
         <v>6.1</v>
       </c>
-      <c r="G54" t="s">
+      <c r="J54" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A55">
         <v>260</v>
       </c>
@@ -2723,13 +3284,23 @@
         <v>1</v>
       </c>
       <c r="F55">
+        <v>14</v>
+      </c>
+      <c r="G55">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="H55">
+        <v>1</v>
+      </c>
+      <c r="I55">
         <v>6.1</v>
       </c>
-      <c r="G55" t="s">
+      <c r="J55" t="s">
         <v>339</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A56">
         <v>261</v>
       </c>
@@ -2746,13 +3317,23 @@
         <v>1</v>
       </c>
       <c r="F56">
+        <v>14</v>
+      </c>
+      <c r="G56">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="H56">
+        <v>1</v>
+      </c>
+      <c r="I56">
         <v>6.1</v>
       </c>
-      <c r="G56" t="s">
+      <c r="J56" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A57">
         <v>262</v>
       </c>
@@ -2769,13 +3350,23 @@
         <v>1</v>
       </c>
       <c r="F57">
+        <v>14</v>
+      </c>
+      <c r="G57">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="H57">
+        <v>1</v>
+      </c>
+      <c r="I57">
         <v>6.1</v>
       </c>
-      <c r="G57" t="s">
+      <c r="J57" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A58">
         <v>263</v>
       </c>
@@ -2792,13 +3383,23 @@
         <v>1</v>
       </c>
       <c r="F58">
+        <v>14</v>
+      </c>
+      <c r="G58">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="H58">
+        <v>1</v>
+      </c>
+      <c r="I58">
         <v>6.1</v>
       </c>
-      <c r="G58" t="s">
+      <c r="J58" t="s">
         <v>334</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A59">
         <v>5</v>
       </c>
@@ -2815,13 +3416,23 @@
         <v>1</v>
       </c>
       <c r="F59">
+        <v>14</v>
+      </c>
+      <c r="G59">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="H59">
+        <v>1</v>
+      </c>
+      <c r="I59">
         <v>1.1000000000000001</v>
       </c>
-      <c r="G59" t="s">
+      <c r="J59" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A60">
         <v>58</v>
       </c>
@@ -2838,13 +3449,23 @@
         <v>1</v>
       </c>
       <c r="F60">
+        <v>20</v>
+      </c>
+      <c r="G60">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="H60">
+        <v>1</v>
+      </c>
+      <c r="I60">
         <v>1.5</v>
       </c>
-      <c r="G60" t="s">
+      <c r="J60" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A61">
         <v>59</v>
       </c>
@@ -2861,13 +3482,23 @@
         <v>1</v>
       </c>
       <c r="F61">
+        <v>20</v>
+      </c>
+      <c r="G61">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="H61">
+        <v>1</v>
+      </c>
+      <c r="I61">
         <v>1.5</v>
       </c>
-      <c r="G61" t="s">
+      <c r="J61" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A62">
         <v>50</v>
       </c>
@@ -2884,13 +3515,23 @@
         <v>1</v>
       </c>
       <c r="F62">
+        <v>16</v>
+      </c>
+      <c r="G62">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="H62">
+        <v>1</v>
+      </c>
+      <c r="I62">
         <v>1.4</v>
       </c>
-      <c r="G62" t="s">
+      <c r="J62" t="s">
         <v>297</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A63">
         <v>49</v>
       </c>
@@ -2907,13 +3548,23 @@
         <v>1</v>
       </c>
       <c r="F63">
+        <v>20</v>
+      </c>
+      <c r="G63">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="H63">
+        <v>1</v>
+      </c>
+      <c r="I63">
         <v>1.4</v>
       </c>
-      <c r="G63" t="s">
+      <c r="J63" t="s">
         <v>289</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A64">
         <v>29</v>
       </c>
@@ -2930,13 +3581,23 @@
         <v>1</v>
       </c>
       <c r="F64">
+        <v>16</v>
+      </c>
+      <c r="G64">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="H64">
+        <v>1</v>
+      </c>
+      <c r="I64">
         <v>1.3</v>
       </c>
-      <c r="G64" t="s">
+      <c r="J64" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A65">
         <v>30</v>
       </c>
@@ -2953,13 +3614,23 @@
         <v>1</v>
       </c>
       <c r="F65">
+        <v>20</v>
+      </c>
+      <c r="G65">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="H65">
+        <v>1</v>
+      </c>
+      <c r="I65">
         <v>1.3</v>
       </c>
-      <c r="G65" t="s">
+      <c r="J65" t="s">
         <v>284</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="66" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A66">
         <v>31</v>
       </c>
@@ -2976,13 +3647,23 @@
         <v>1</v>
       </c>
       <c r="F66">
+        <v>20</v>
+      </c>
+      <c r="G66">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="H66">
+        <v>1</v>
+      </c>
+      <c r="I66">
         <v>1.3</v>
       </c>
-      <c r="G66" t="s">
+      <c r="J66" t="s">
         <v>284</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="67" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A67">
         <v>21</v>
       </c>
@@ -2999,13 +3680,23 @@
         <v>1</v>
       </c>
       <c r="F67">
+        <v>20</v>
+      </c>
+      <c r="G67">
+        <f t="shared" ref="G67:G130" si="2">F67-H67</f>
+        <v>19</v>
+      </c>
+      <c r="H67">
+        <v>1</v>
+      </c>
+      <c r="I67">
         <v>1.2</v>
       </c>
-      <c r="G67" t="s">
+      <c r="J67" t="s">
         <v>289</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="68" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A68">
         <v>56</v>
       </c>
@@ -3022,13 +3713,23 @@
         <v>1</v>
       </c>
       <c r="F68">
+        <v>14</v>
+      </c>
+      <c r="G68">
+        <f t="shared" si="2"/>
+        <v>13</v>
+      </c>
+      <c r="H68">
+        <v>1</v>
+      </c>
+      <c r="I68">
         <v>1.5</v>
       </c>
-      <c r="G68" t="s">
+      <c r="J68" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="69" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A69">
         <v>22</v>
       </c>
@@ -3045,13 +3746,23 @@
         <v>1</v>
       </c>
       <c r="F69">
+        <v>20</v>
+      </c>
+      <c r="G69">
+        <f t="shared" si="2"/>
+        <v>19</v>
+      </c>
+      <c r="H69">
+        <v>1</v>
+      </c>
+      <c r="I69">
         <v>1.2</v>
       </c>
-      <c r="G69" t="s">
+      <c r="J69" t="s">
         <v>289</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="70" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A70">
         <v>23</v>
       </c>
@@ -3068,13 +3779,23 @@
         <v>1</v>
       </c>
       <c r="F70">
+        <v>14</v>
+      </c>
+      <c r="G70">
+        <f t="shared" si="2"/>
+        <v>13</v>
+      </c>
+      <c r="H70">
+        <v>1</v>
+      </c>
+      <c r="I70">
         <v>1.2</v>
       </c>
-      <c r="G70" t="s">
+      <c r="J70" t="s">
         <v>287</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="71" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A71">
         <v>6</v>
       </c>
@@ -3091,13 +3812,23 @@
         <v>1</v>
       </c>
       <c r="F71">
+        <v>14</v>
+      </c>
+      <c r="G71">
+        <f t="shared" si="2"/>
+        <v>13</v>
+      </c>
+      <c r="H71">
+        <v>1</v>
+      </c>
+      <c r="I71">
         <v>1.1000000000000001</v>
       </c>
-      <c r="G71" t="s">
+      <c r="J71" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="72" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A72">
         <v>7</v>
       </c>
@@ -3114,13 +3845,23 @@
         <v>1</v>
       </c>
       <c r="F72">
+        <v>14</v>
+      </c>
+      <c r="G72">
+        <f t="shared" si="2"/>
+        <v>13</v>
+      </c>
+      <c r="H72">
+        <v>1</v>
+      </c>
+      <c r="I72">
         <v>1.1000000000000001</v>
       </c>
-      <c r="G72" t="s">
+      <c r="J72" t="s">
         <v>275</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="73" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A73">
         <v>13</v>
       </c>
@@ -3137,13 +3878,23 @@
         <v>1</v>
       </c>
       <c r="F73">
+        <v>14</v>
+      </c>
+      <c r="G73">
+        <f t="shared" si="2"/>
+        <v>13</v>
+      </c>
+      <c r="H73">
+        <v>1</v>
+      </c>
+      <c r="I73">
         <v>1.1000000000000001</v>
       </c>
-      <c r="G73" t="s">
+      <c r="J73" t="s">
         <v>275</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="74" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A74">
         <v>14</v>
       </c>
@@ -3160,13 +3911,23 @@
         <v>1</v>
       </c>
       <c r="F74">
+        <v>14</v>
+      </c>
+      <c r="G74">
+        <f t="shared" si="2"/>
+        <v>13</v>
+      </c>
+      <c r="H74">
+        <v>1</v>
+      </c>
+      <c r="I74">
         <v>1.1000000000000001</v>
       </c>
-      <c r="G74" t="s">
+      <c r="J74" t="s">
         <v>280</v>
       </c>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="75" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A75">
         <v>123</v>
       </c>
@@ -3183,13 +3944,23 @@
         <v>1</v>
       </c>
       <c r="F75">
+        <v>14</v>
+      </c>
+      <c r="G75">
+        <f t="shared" si="2"/>
+        <v>13</v>
+      </c>
+      <c r="H75">
+        <v>1</v>
+      </c>
+      <c r="I75">
         <v>2.4</v>
       </c>
-      <c r="G75" t="s">
+      <c r="J75" t="s">
         <v>310</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="76" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A76">
         <v>124</v>
       </c>
@@ -3206,13 +3977,23 @@
         <v>1</v>
       </c>
       <c r="F76">
+        <v>14</v>
+      </c>
+      <c r="G76">
+        <f t="shared" si="2"/>
+        <v>13</v>
+      </c>
+      <c r="H76">
+        <v>1</v>
+      </c>
+      <c r="I76">
         <v>2.4</v>
       </c>
-      <c r="G76" t="s">
+      <c r="J76" t="s">
         <v>310</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="77" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A77">
         <v>122</v>
       </c>
@@ -3229,13 +4010,23 @@
         <v>1</v>
       </c>
       <c r="F77">
+        <v>14</v>
+      </c>
+      <c r="G77">
+        <f t="shared" si="2"/>
+        <v>13</v>
+      </c>
+      <c r="H77">
+        <v>1</v>
+      </c>
+      <c r="I77">
         <v>2.4</v>
       </c>
-      <c r="G77" t="s">
+      <c r="J77" t="s">
         <v>310</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="78" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A78">
         <v>113</v>
       </c>
@@ -3252,13 +4043,23 @@
         <v>1</v>
       </c>
       <c r="F78">
+        <v>20</v>
+      </c>
+      <c r="G78">
+        <f t="shared" si="2"/>
+        <v>19</v>
+      </c>
+      <c r="H78">
+        <v>1</v>
+      </c>
+      <c r="I78">
         <v>2.4</v>
       </c>
-      <c r="G78" t="s">
+      <c r="J78" t="s">
         <v>289</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="79" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A79">
         <v>40</v>
       </c>
@@ -3275,13 +4076,23 @@
         <v>1</v>
       </c>
       <c r="F79">
+        <v>14</v>
+      </c>
+      <c r="G79">
+        <f t="shared" si="2"/>
+        <v>13</v>
+      </c>
+      <c r="H79">
+        <v>1</v>
+      </c>
+      <c r="I79">
         <v>1.4</v>
       </c>
-      <c r="G79" t="s">
+      <c r="J79" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="80" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A80">
         <v>109</v>
       </c>
@@ -3298,13 +4109,23 @@
         <v>1</v>
       </c>
       <c r="F80">
+        <v>40</v>
+      </c>
+      <c r="G80">
+        <f t="shared" si="2"/>
+        <v>39</v>
+      </c>
+      <c r="H80">
+        <v>1</v>
+      </c>
+      <c r="I80">
         <v>2.2999999999999998</v>
       </c>
-      <c r="G80" t="s">
+      <c r="J80" t="s">
         <v>307</v>
       </c>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="81" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A81">
         <v>110</v>
       </c>
@@ -3321,13 +4142,23 @@
         <v>1</v>
       </c>
       <c r="F81">
+        <v>40</v>
+      </c>
+      <c r="G81">
+        <f t="shared" si="2"/>
+        <v>39</v>
+      </c>
+      <c r="H81">
+        <v>1</v>
+      </c>
+      <c r="I81">
         <v>2.2999999999999998</v>
       </c>
-      <c r="G81" t="s">
+      <c r="J81" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="82" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A82">
         <v>111</v>
       </c>
@@ -3344,13 +4175,23 @@
         <v>1</v>
       </c>
       <c r="F82">
+        <v>40</v>
+      </c>
+      <c r="G82">
+        <f t="shared" si="2"/>
+        <v>39</v>
+      </c>
+      <c r="H82">
+        <v>1</v>
+      </c>
+      <c r="I82">
         <v>2.2999999999999998</v>
       </c>
-      <c r="G82" t="s">
+      <c r="J82" t="s">
         <v>308</v>
       </c>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="83" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A83">
         <v>112</v>
       </c>
@@ -3367,13 +4208,23 @@
         <v>1</v>
       </c>
       <c r="F83">
+        <v>40</v>
+      </c>
+      <c r="G83">
+        <f t="shared" si="2"/>
+        <v>39</v>
+      </c>
+      <c r="H83">
+        <v>1</v>
+      </c>
+      <c r="I83">
         <v>2.2999999999999998</v>
       </c>
-      <c r="G83" t="s">
+      <c r="J83" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="84" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A84">
         <v>94</v>
       </c>
@@ -3390,13 +4241,23 @@
         <v>1</v>
       </c>
       <c r="F84">
+        <v>14</v>
+      </c>
+      <c r="G84">
+        <f t="shared" si="2"/>
+        <v>13</v>
+      </c>
+      <c r="H84">
+        <v>1</v>
+      </c>
+      <c r="I84">
         <v>2.2000000000000002</v>
       </c>
-      <c r="G84" t="s">
+      <c r="J84" t="s">
         <v>303</v>
       </c>
     </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="85" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A85">
         <v>93</v>
       </c>
@@ -3413,13 +4274,23 @@
         <v>1</v>
       </c>
       <c r="F85">
+        <v>24</v>
+      </c>
+      <c r="G85">
+        <f t="shared" si="2"/>
+        <v>23</v>
+      </c>
+      <c r="H85">
+        <v>1</v>
+      </c>
+      <c r="I85">
         <v>2.2000000000000002</v>
       </c>
-      <c r="G85" t="s">
+      <c r="J85" t="s">
         <v>305</v>
       </c>
     </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="86" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A86">
         <v>76</v>
       </c>
@@ -3436,13 +4307,23 @@
         <v>1</v>
       </c>
       <c r="F86">
+        <v>14</v>
+      </c>
+      <c r="G86">
+        <f t="shared" si="2"/>
+        <v>13</v>
+      </c>
+      <c r="H86">
+        <v>1</v>
+      </c>
+      <c r="I86">
         <v>2.1</v>
       </c>
-      <c r="G86" t="s">
+      <c r="J86" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="87" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A87">
         <v>103</v>
       </c>
@@ -3459,13 +4340,23 @@
         <v>1</v>
       </c>
       <c r="F87">
+        <v>14</v>
+      </c>
+      <c r="G87">
+        <f t="shared" si="2"/>
+        <v>13</v>
+      </c>
+      <c r="H87">
+        <v>1</v>
+      </c>
+      <c r="I87">
         <v>2.2000000000000002</v>
       </c>
-      <c r="G87" t="s">
+      <c r="J87" t="s">
         <v>306</v>
       </c>
     </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="88" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A88">
         <v>77</v>
       </c>
@@ -3482,13 +4373,23 @@
         <v>1</v>
       </c>
       <c r="F88">
+        <v>14</v>
+      </c>
+      <c r="G88">
+        <f t="shared" si="2"/>
+        <v>13</v>
+      </c>
+      <c r="H88">
+        <v>1</v>
+      </c>
+      <c r="I88">
         <v>2.1</v>
       </c>
-      <c r="G88" t="s">
+      <c r="J88" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="89" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A89">
         <v>84</v>
       </c>
@@ -3505,13 +4406,23 @@
         <v>1</v>
       </c>
       <c r="F89">
+        <v>20</v>
+      </c>
+      <c r="G89">
+        <f t="shared" si="2"/>
+        <v>19</v>
+      </c>
+      <c r="H89">
+        <v>1</v>
+      </c>
+      <c r="I89">
         <v>2.1</v>
       </c>
-      <c r="G89" t="s">
+      <c r="J89" t="s">
         <v>289</v>
       </c>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="90" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A90">
         <v>25</v>
       </c>
@@ -3528,13 +4439,23 @@
         <v>1</v>
       </c>
       <c r="F90">
+        <v>14</v>
+      </c>
+      <c r="G90">
+        <f t="shared" si="2"/>
+        <v>13</v>
+      </c>
+      <c r="H90">
+        <v>1</v>
+      </c>
+      <c r="I90">
         <v>1.3</v>
       </c>
-      <c r="G90" t="s">
+      <c r="J90" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="91" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A91">
         <v>82</v>
       </c>
@@ -3551,13 +4472,23 @@
         <v>1</v>
       </c>
       <c r="F91">
+        <v>16</v>
+      </c>
+      <c r="G91">
+        <f t="shared" si="2"/>
+        <v>15</v>
+      </c>
+      <c r="H91">
+        <v>1</v>
+      </c>
+      <c r="I91">
         <v>2.1</v>
       </c>
-      <c r="G91" t="s">
+      <c r="J91" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="92" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A92">
         <v>78</v>
       </c>
@@ -3574,13 +4505,23 @@
         <v>1</v>
       </c>
       <c r="F92">
+        <v>14</v>
+      </c>
+      <c r="G92">
+        <f t="shared" si="2"/>
+        <v>13</v>
+      </c>
+      <c r="H92">
+        <v>1</v>
+      </c>
+      <c r="I92">
         <v>2.1</v>
       </c>
-      <c r="G92" t="s">
+      <c r="J92" t="s">
         <v>303</v>
       </c>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="93" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A93">
         <v>120</v>
       </c>
@@ -3597,10 +4538,20 @@
         <v>1</v>
       </c>
       <c r="F93">
+        <v>14</v>
+      </c>
+      <c r="G93">
+        <f t="shared" si="2"/>
+        <v>13</v>
+      </c>
+      <c r="H93">
+        <v>1</v>
+      </c>
+      <c r="I93">
         <v>2.4</v>
       </c>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="94" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A94">
         <v>138</v>
       </c>
@@ -3617,13 +4568,23 @@
         <v>1</v>
       </c>
       <c r="F94">
+        <v>14</v>
+      </c>
+      <c r="G94">
+        <f t="shared" si="2"/>
+        <v>13</v>
+      </c>
+      <c r="H94">
+        <v>1</v>
+      </c>
+      <c r="I94">
         <v>3.3</v>
       </c>
-      <c r="G94" t="s">
+      <c r="J94" t="s">
         <v>317</v>
       </c>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="95" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A95">
         <v>139</v>
       </c>
@@ -3640,13 +4601,23 @@
         <v>1</v>
       </c>
       <c r="F95">
+        <v>14</v>
+      </c>
+      <c r="G95">
+        <f t="shared" si="2"/>
+        <v>13</v>
+      </c>
+      <c r="H95">
+        <v>1</v>
+      </c>
+      <c r="I95">
         <v>3.3</v>
       </c>
-      <c r="G95" t="s">
+      <c r="J95" t="s">
         <v>318</v>
       </c>
     </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="96" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A96">
         <v>135</v>
       </c>
@@ -3663,13 +4634,23 @@
         <v>1</v>
       </c>
       <c r="F96">
+        <v>14</v>
+      </c>
+      <c r="G96">
+        <f t="shared" si="2"/>
+        <v>13</v>
+      </c>
+      <c r="H96">
+        <v>1</v>
+      </c>
+      <c r="I96">
         <v>3.2</v>
       </c>
-      <c r="G96" t="s">
+      <c r="J96" t="s">
         <v>316</v>
       </c>
     </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="97" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A97">
         <v>136</v>
       </c>
@@ -3686,13 +4667,23 @@
         <v>1</v>
       </c>
       <c r="F97">
+        <v>14</v>
+      </c>
+      <c r="G97">
+        <f t="shared" si="2"/>
+        <v>13</v>
+      </c>
+      <c r="H97">
+        <v>1</v>
+      </c>
+      <c r="I97">
         <v>3.2</v>
       </c>
-      <c r="G97" t="s">
+      <c r="J97" t="s">
         <v>303</v>
       </c>
     </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="98" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A98">
         <v>137</v>
       </c>
@@ -3709,13 +4700,23 @@
         <v>1</v>
       </c>
       <c r="F98">
+        <v>14</v>
+      </c>
+      <c r="G98">
+        <f t="shared" si="2"/>
+        <v>13</v>
+      </c>
+      <c r="H98">
+        <v>1</v>
+      </c>
+      <c r="I98">
         <v>3.2</v>
       </c>
-      <c r="G98" t="s">
+      <c r="J98" t="s">
         <v>275</v>
       </c>
     </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="99" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A99">
         <v>129</v>
       </c>
@@ -3732,13 +4733,23 @@
         <v>1</v>
       </c>
       <c r="F99">
+        <v>20</v>
+      </c>
+      <c r="G99">
+        <f t="shared" si="2"/>
+        <v>19</v>
+      </c>
+      <c r="H99">
+        <v>1</v>
+      </c>
+      <c r="I99">
         <v>3.2</v>
       </c>
-      <c r="G99" t="s">
+      <c r="J99" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="100" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A100">
         <v>126</v>
       </c>
@@ -3755,13 +4766,23 @@
         <v>1</v>
       </c>
       <c r="F100">
+        <v>16</v>
+      </c>
+      <c r="G100">
+        <f t="shared" si="2"/>
+        <v>15</v>
+      </c>
+      <c r="H100">
+        <v>1</v>
+      </c>
+      <c r="I100">
         <v>3.1</v>
       </c>
-      <c r="G100" t="s">
+      <c r="J100" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="101" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A101">
         <v>26</v>
       </c>
@@ -3778,13 +4799,23 @@
         <v>1</v>
       </c>
       <c r="F101">
+        <v>20</v>
+      </c>
+      <c r="G101">
+        <f t="shared" si="2"/>
+        <v>19</v>
+      </c>
+      <c r="H101">
+        <v>1</v>
+      </c>
+      <c r="I101">
         <v>1.3</v>
       </c>
-      <c r="G101" t="s">
+      <c r="J101" t="s">
         <v>284</v>
       </c>
     </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="102" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A102">
         <v>127</v>
       </c>
@@ -3794,20 +4825,30 @@
       <c r="C102" t="s">
         <v>123</v>
       </c>
-      <c r="D102" s="5">
+      <c r="D102" s="2">
         <v>2716</v>
       </c>
       <c r="E102">
         <v>1</v>
       </c>
       <c r="F102">
+        <v>24</v>
+      </c>
+      <c r="G102">
+        <f t="shared" si="2"/>
+        <v>23</v>
+      </c>
+      <c r="H102">
+        <v>1</v>
+      </c>
+      <c r="I102">
         <v>3.1</v>
       </c>
-      <c r="G102" t="s">
+      <c r="J102" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="103" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A103">
         <v>128</v>
       </c>
@@ -3817,23 +4858,33 @@
       <c r="C103" t="s">
         <v>124</v>
       </c>
-      <c r="D103" s="5">
+      <c r="D103" s="2">
         <v>2716</v>
       </c>
       <c r="E103">
         <v>1</v>
       </c>
       <c r="F103">
+        <v>24</v>
+      </c>
+      <c r="G103">
+        <f t="shared" si="2"/>
+        <v>23</v>
+      </c>
+      <c r="H103">
+        <v>1</v>
+      </c>
+      <c r="I103">
         <v>3.1</v>
       </c>
-      <c r="G103" t="s">
+      <c r="J103" t="s">
         <v>279</v>
       </c>
-      <c r="H103" t="s">
+      <c r="K103" t="s">
         <v>427</v>
       </c>
     </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="104" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A104">
         <v>141</v>
       </c>
@@ -3850,13 +4901,23 @@
         <v>1</v>
       </c>
       <c r="F104">
+        <v>14</v>
+      </c>
+      <c r="G104">
+        <f t="shared" si="2"/>
+        <v>13</v>
+      </c>
+      <c r="H104">
+        <v>1</v>
+      </c>
+      <c r="I104">
         <v>3.3</v>
       </c>
-      <c r="G104" t="s">
+      <c r="J104" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="105" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A105">
         <v>134</v>
       </c>
@@ -3873,13 +4934,23 @@
         <v>1</v>
       </c>
       <c r="F105">
+        <v>14</v>
+      </c>
+      <c r="G105">
+        <f t="shared" si="2"/>
+        <v>13</v>
+      </c>
+      <c r="H105">
+        <v>1</v>
+      </c>
+      <c r="I105">
         <v>3.2</v>
       </c>
-      <c r="G105" t="s">
+      <c r="J105" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="106" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A106">
         <v>133</v>
       </c>
@@ -3896,13 +4967,23 @@
         <v>1</v>
       </c>
       <c r="F106">
+        <v>14</v>
+      </c>
+      <c r="G106">
+        <f t="shared" si="2"/>
+        <v>13</v>
+      </c>
+      <c r="H106">
+        <v>1</v>
+      </c>
+      <c r="I106">
         <v>3.2</v>
       </c>
-      <c r="G106" t="s">
+      <c r="J106" t="s">
         <v>303</v>
       </c>
     </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="107" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A107">
         <v>132</v>
       </c>
@@ -3919,13 +5000,23 @@
         <v>1</v>
       </c>
       <c r="F107">
+        <v>14</v>
+      </c>
+      <c r="G107">
+        <f t="shared" si="2"/>
+        <v>13</v>
+      </c>
+      <c r="H107">
+        <v>1</v>
+      </c>
+      <c r="I107">
         <v>3.2</v>
       </c>
-      <c r="G107" t="s">
+      <c r="J107" t="s">
         <v>314</v>
       </c>
     </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="108" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A108">
         <v>131</v>
       </c>
@@ -3942,13 +5033,23 @@
         <v>1</v>
       </c>
       <c r="F108">
+        <v>40</v>
+      </c>
+      <c r="G108">
+        <f t="shared" si="2"/>
+        <v>39</v>
+      </c>
+      <c r="H108">
+        <v>1</v>
+      </c>
+      <c r="I108">
         <v>3.2</v>
       </c>
-      <c r="G108" t="s">
+      <c r="J108" t="s">
         <v>313</v>
       </c>
     </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="109" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A109">
         <v>172</v>
       </c>
@@ -3965,13 +5066,23 @@
         <v>1</v>
       </c>
       <c r="F109">
+        <v>18</v>
+      </c>
+      <c r="G109">
+        <f t="shared" si="2"/>
+        <v>17</v>
+      </c>
+      <c r="H109">
+        <v>1</v>
+      </c>
+      <c r="I109">
         <v>4.2</v>
       </c>
-      <c r="G109" t="s">
+      <c r="J109" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="110" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A110">
         <v>173</v>
       </c>
@@ -3988,13 +5099,23 @@
         <v>1</v>
       </c>
       <c r="F110">
+        <v>16</v>
+      </c>
+      <c r="G110">
+        <f t="shared" si="2"/>
+        <v>15</v>
+      </c>
+      <c r="H110">
+        <v>1</v>
+      </c>
+      <c r="I110">
         <v>4.2</v>
       </c>
-      <c r="G110" t="s">
+      <c r="J110" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="111" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A111">
         <v>145</v>
       </c>
@@ -4011,13 +5132,23 @@
         <v>1</v>
       </c>
       <c r="F111">
+        <v>16</v>
+      </c>
+      <c r="G111">
+        <f t="shared" si="2"/>
+        <v>15</v>
+      </c>
+      <c r="H111">
+        <v>1</v>
+      </c>
+      <c r="I111">
         <v>4.0999999999999996</v>
       </c>
-      <c r="G111" t="s">
+      <c r="J111" t="s">
         <v>319</v>
       </c>
     </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="112" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A112">
         <v>27</v>
       </c>
@@ -4034,13 +5165,23 @@
         <v>1</v>
       </c>
       <c r="F112">
+        <v>20</v>
+      </c>
+      <c r="G112">
+        <f t="shared" si="2"/>
+        <v>19</v>
+      </c>
+      <c r="H112">
+        <v>1</v>
+      </c>
+      <c r="I112">
         <v>1.3</v>
       </c>
-      <c r="G112" t="s">
+      <c r="J112" t="s">
         <v>289</v>
       </c>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="113" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A113">
         <v>146</v>
       </c>
@@ -4057,13 +5198,23 @@
         <v>1</v>
       </c>
       <c r="F113">
+        <v>16</v>
+      </c>
+      <c r="G113">
+        <f t="shared" si="2"/>
+        <v>15</v>
+      </c>
+      <c r="H113">
+        <v>1</v>
+      </c>
+      <c r="I113">
         <v>4.0999999999999996</v>
       </c>
-      <c r="G113" t="s">
+      <c r="J113" t="s">
         <v>319</v>
       </c>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="114" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A114">
         <v>147</v>
       </c>
@@ -4080,13 +5231,23 @@
         <v>1</v>
       </c>
       <c r="F114">
+        <v>16</v>
+      </c>
+      <c r="G114">
+        <f t="shared" si="2"/>
+        <v>15</v>
+      </c>
+      <c r="H114">
+        <v>1</v>
+      </c>
+      <c r="I114">
         <v>4.0999999999999996</v>
       </c>
-      <c r="G114" t="s">
+      <c r="J114" t="s">
         <v>319</v>
       </c>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="115" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A115">
         <v>148</v>
       </c>
@@ -4103,13 +5264,23 @@
         <v>1</v>
       </c>
       <c r="F115">
+        <v>16</v>
+      </c>
+      <c r="G115">
+        <f t="shared" si="2"/>
+        <v>15</v>
+      </c>
+      <c r="H115">
+        <v>1</v>
+      </c>
+      <c r="I115">
         <v>4.0999999999999996</v>
       </c>
-      <c r="G115" t="s">
+      <c r="J115" t="s">
         <v>319</v>
       </c>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="116" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A116">
         <v>183</v>
       </c>
@@ -4126,13 +5297,23 @@
         <v>1</v>
       </c>
       <c r="F116">
+        <v>40</v>
+      </c>
+      <c r="G116">
+        <f t="shared" si="2"/>
+        <v>39</v>
+      </c>
+      <c r="H116">
+        <v>1</v>
+      </c>
+      <c r="I116">
         <v>4.3</v>
       </c>
-      <c r="G116" t="s">
+      <c r="J116" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="117" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A117">
         <v>181</v>
       </c>
@@ -4149,13 +5330,23 @@
         <v>1</v>
       </c>
       <c r="F117">
+        <v>24</v>
+      </c>
+      <c r="G117">
+        <f t="shared" si="2"/>
+        <v>23</v>
+      </c>
+      <c r="H117">
+        <v>1</v>
+      </c>
+      <c r="I117">
         <v>4.3</v>
       </c>
-      <c r="G117" t="s">
+      <c r="J117" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="118" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A118">
         <v>167</v>
       </c>
@@ -4172,13 +5363,23 @@
         <v>1</v>
       </c>
       <c r="F118">
+        <v>20</v>
+      </c>
+      <c r="G118">
+        <f t="shared" si="2"/>
+        <v>19</v>
+      </c>
+      <c r="H118">
+        <v>1</v>
+      </c>
+      <c r="I118">
         <v>4.2</v>
       </c>
-      <c r="G118" t="s">
+      <c r="J118" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="119" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A119">
         <v>168</v>
       </c>
@@ -4195,13 +5396,23 @@
         <v>1</v>
       </c>
       <c r="F119">
+        <v>20</v>
+      </c>
+      <c r="G119">
+        <f t="shared" si="2"/>
+        <v>19</v>
+      </c>
+      <c r="H119">
+        <v>1</v>
+      </c>
+      <c r="I119">
         <v>4.2</v>
       </c>
-      <c r="G119" t="s">
+      <c r="J119" t="s">
         <v>289</v>
       </c>
     </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="120" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A120">
         <v>169</v>
       </c>
@@ -4218,13 +5429,23 @@
         <v>1</v>
       </c>
       <c r="F120">
+        <v>28</v>
+      </c>
+      <c r="G120">
+        <f t="shared" si="2"/>
+        <v>27</v>
+      </c>
+      <c r="H120">
+        <v>1</v>
+      </c>
+      <c r="I120">
         <v>4.2</v>
       </c>
-      <c r="G120" t="s">
+      <c r="J120" t="s">
         <v>323</v>
       </c>
     </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="121" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A121">
         <v>170</v>
       </c>
@@ -4241,13 +5462,23 @@
         <v>1</v>
       </c>
       <c r="F121">
+        <v>16</v>
+      </c>
+      <c r="G121">
+        <f t="shared" si="2"/>
+        <v>15</v>
+      </c>
+      <c r="H121">
+        <v>1</v>
+      </c>
+      <c r="I121">
         <v>4.2</v>
       </c>
-      <c r="G121" t="s">
+      <c r="J121" t="s">
         <v>325</v>
       </c>
     </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="122" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A122">
         <v>171</v>
       </c>
@@ -4264,13 +5495,23 @@
         <v>1</v>
       </c>
       <c r="F122">
+        <v>16</v>
+      </c>
+      <c r="G122">
+        <f t="shared" si="2"/>
+        <v>15</v>
+      </c>
+      <c r="H122">
+        <v>1</v>
+      </c>
+      <c r="I122">
         <v>4.2</v>
       </c>
-      <c r="G122" t="s">
+      <c r="J122" t="s">
         <v>326</v>
       </c>
     </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="123" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A123">
         <v>16</v>
       </c>
@@ -4287,13 +5528,23 @@
         <v>1</v>
       </c>
       <c r="F123">
+        <v>20</v>
+      </c>
+      <c r="G123">
+        <f t="shared" si="2"/>
+        <v>19</v>
+      </c>
+      <c r="H123">
+        <v>1</v>
+      </c>
+      <c r="I123">
         <v>1.2</v>
       </c>
-      <c r="G123" t="s">
+      <c r="J123" t="s">
         <v>284</v>
       </c>
     </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="124" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A124">
         <v>177</v>
       </c>
@@ -4310,13 +5561,23 @@
         <v>1</v>
       </c>
       <c r="F124">
+        <v>16</v>
+      </c>
+      <c r="G124">
+        <f t="shared" si="2"/>
+        <v>15</v>
+      </c>
+      <c r="H124">
+        <v>1</v>
+      </c>
+      <c r="I124">
         <v>4.2</v>
       </c>
-      <c r="G124" t="s">
+      <c r="J124" t="s">
         <v>329</v>
       </c>
     </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="125" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A125">
         <v>149</v>
       </c>
@@ -4333,13 +5594,23 @@
         <v>1</v>
       </c>
       <c r="F125">
+        <v>16</v>
+      </c>
+      <c r="G125">
+        <f t="shared" si="2"/>
+        <v>15</v>
+      </c>
+      <c r="H125">
+        <v>1</v>
+      </c>
+      <c r="I125">
         <v>4.0999999999999996</v>
       </c>
-      <c r="G125" t="s">
+      <c r="J125" t="s">
         <v>319</v>
       </c>
     </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="126" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A126">
         <v>150</v>
       </c>
@@ -4356,13 +5627,23 @@
         <v>1</v>
       </c>
       <c r="F126">
+        <v>16</v>
+      </c>
+      <c r="G126">
+        <f t="shared" si="2"/>
+        <v>15</v>
+      </c>
+      <c r="H126">
+        <v>1</v>
+      </c>
+      <c r="I126">
         <v>4.0999999999999996</v>
       </c>
-      <c r="G126" t="s">
+      <c r="J126" t="s">
         <v>319</v>
       </c>
     </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="127" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A127">
         <v>151</v>
       </c>
@@ -4379,13 +5660,23 @@
         <v>1</v>
       </c>
       <c r="F127">
+        <v>16</v>
+      </c>
+      <c r="G127">
+        <f t="shared" si="2"/>
+        <v>15</v>
+      </c>
+      <c r="H127">
+        <v>1</v>
+      </c>
+      <c r="I127">
         <v>4.0999999999999996</v>
       </c>
-      <c r="G127" t="s">
+      <c r="J127" t="s">
         <v>319</v>
       </c>
     </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="128" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A128">
         <v>152</v>
       </c>
@@ -4402,13 +5693,23 @@
         <v>1</v>
       </c>
       <c r="F128">
+        <v>16</v>
+      </c>
+      <c r="G128">
+        <f t="shared" si="2"/>
+        <v>15</v>
+      </c>
+      <c r="H128">
+        <v>1</v>
+      </c>
+      <c r="I128">
         <v>4.0999999999999996</v>
       </c>
-      <c r="G128" t="s">
+      <c r="J128" t="s">
         <v>319</v>
       </c>
     </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="129" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A129">
         <v>228</v>
       </c>
@@ -4425,13 +5726,23 @@
         <v>1</v>
       </c>
       <c r="F129">
+        <v>14</v>
+      </c>
+      <c r="G129">
+        <f t="shared" si="2"/>
+        <v>13</v>
+      </c>
+      <c r="H129">
+        <v>1</v>
+      </c>
+      <c r="I129">
         <v>5.4</v>
       </c>
-      <c r="G129" t="s">
+      <c r="J129" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="130" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A130">
         <v>225</v>
       </c>
@@ -4448,13 +5759,23 @@
         <v>1</v>
       </c>
       <c r="F130">
+        <v>16</v>
+      </c>
+      <c r="G130">
+        <f t="shared" si="2"/>
+        <v>15</v>
+      </c>
+      <c r="H130">
+        <v>1</v>
+      </c>
+      <c r="I130">
         <v>5.4</v>
       </c>
-      <c r="G130" t="s">
+      <c r="J130" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="131" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A131">
         <v>214</v>
       </c>
@@ -4471,13 +5792,23 @@
         <v>1</v>
       </c>
       <c r="F131">
+        <v>14</v>
+      </c>
+      <c r="G131">
+        <f t="shared" ref="G131:G194" si="3">F131-H131</f>
+        <v>13</v>
+      </c>
+      <c r="H131">
+        <v>1</v>
+      </c>
+      <c r="I131">
         <v>5.3</v>
       </c>
-      <c r="G131" t="s">
+      <c r="J131" t="s">
         <v>334</v>
       </c>
     </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="132" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A132">
         <v>215</v>
       </c>
@@ -4494,13 +5825,23 @@
         <v>1</v>
       </c>
       <c r="F132">
+        <v>14</v>
+      </c>
+      <c r="G132">
+        <f t="shared" si="3"/>
+        <v>13</v>
+      </c>
+      <c r="H132">
+        <v>1</v>
+      </c>
+      <c r="I132">
         <v>5.3</v>
       </c>
-      <c r="G132" t="s">
+      <c r="J132" t="s">
         <v>335</v>
       </c>
     </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="133" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A133">
         <v>216</v>
       </c>
@@ -4517,13 +5858,23 @@
         <v>1</v>
       </c>
       <c r="F133">
+        <v>14</v>
+      </c>
+      <c r="G133">
+        <f t="shared" si="3"/>
+        <v>13</v>
+      </c>
+      <c r="H133">
+        <v>1</v>
+      </c>
+      <c r="I133">
         <v>5.3</v>
       </c>
-      <c r="G133" t="s">
+      <c r="J133" t="s">
         <v>273</v>
       </c>
     </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="134" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A134">
         <v>17</v>
       </c>
@@ -4540,13 +5891,23 @@
         <v>1</v>
       </c>
       <c r="F134">
+        <v>20</v>
+      </c>
+      <c r="G134">
+        <f t="shared" si="3"/>
+        <v>19</v>
+      </c>
+      <c r="H134">
+        <v>1</v>
+      </c>
+      <c r="I134">
         <v>1.2</v>
       </c>
-      <c r="G134" t="s">
+      <c r="J134" t="s">
         <v>284</v>
       </c>
     </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="135" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A135">
         <v>217</v>
       </c>
@@ -4563,13 +5924,23 @@
         <v>1</v>
       </c>
       <c r="F135">
+        <v>14</v>
+      </c>
+      <c r="G135">
+        <f t="shared" si="3"/>
+        <v>13</v>
+      </c>
+      <c r="H135">
+        <v>1</v>
+      </c>
+      <c r="I135">
         <v>5.3</v>
       </c>
-      <c r="G135" t="s">
+      <c r="J135" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="136" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A136">
         <v>210</v>
       </c>
@@ -4586,13 +5957,23 @@
         <v>1</v>
       </c>
       <c r="F136">
+        <v>14</v>
+      </c>
+      <c r="G136">
+        <f t="shared" si="3"/>
+        <v>13</v>
+      </c>
+      <c r="H136">
+        <v>1</v>
+      </c>
+      <c r="I136">
         <v>5.2</v>
       </c>
-      <c r="G136" t="s">
+      <c r="J136" t="s">
         <v>333</v>
       </c>
     </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="137" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A137">
         <v>208</v>
       </c>
@@ -4609,13 +5990,23 @@
         <v>1</v>
       </c>
       <c r="F137">
+        <v>14</v>
+      </c>
+      <c r="G137">
+        <f t="shared" si="3"/>
+        <v>13</v>
+      </c>
+      <c r="H137">
+        <v>1</v>
+      </c>
+      <c r="I137">
         <v>5.2</v>
       </c>
-      <c r="G137" t="s">
+      <c r="J137" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="138" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A138">
         <v>201</v>
       </c>
@@ -4632,13 +6023,23 @@
         <v>1</v>
       </c>
       <c r="F138">
+        <v>14</v>
+      </c>
+      <c r="G138">
+        <f t="shared" si="3"/>
+        <v>13</v>
+      </c>
+      <c r="H138">
+        <v>1</v>
+      </c>
+      <c r="I138">
         <v>5.2</v>
       </c>
-      <c r="G138" t="s">
+      <c r="J138" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="139" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A139">
         <v>212</v>
       </c>
@@ -4655,13 +6056,23 @@
         <v>1</v>
       </c>
       <c r="F139">
+        <v>14</v>
+      </c>
+      <c r="G139">
+        <f t="shared" si="3"/>
+        <v>13</v>
+      </c>
+      <c r="H139">
+        <v>1</v>
+      </c>
+      <c r="I139">
         <v>5.2</v>
       </c>
-      <c r="G139" t="s">
+      <c r="J139" t="s">
         <v>334</v>
       </c>
     </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="140" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A140">
         <v>187</v>
       </c>
@@ -4678,13 +6089,23 @@
         <v>1</v>
       </c>
       <c r="F140">
+        <v>16</v>
+      </c>
+      <c r="G140">
+        <f t="shared" si="3"/>
+        <v>15</v>
+      </c>
+      <c r="H140">
+        <v>1</v>
+      </c>
+      <c r="I140">
         <v>5.0999999999999996</v>
       </c>
-      <c r="G140" t="s">
+      <c r="J140" t="s">
         <v>319</v>
       </c>
     </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="141" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A141">
         <v>188</v>
       </c>
@@ -4701,13 +6122,23 @@
         <v>1</v>
       </c>
       <c r="F141">
+        <v>16</v>
+      </c>
+      <c r="G141">
+        <f t="shared" si="3"/>
+        <v>15</v>
+      </c>
+      <c r="H141">
+        <v>1</v>
+      </c>
+      <c r="I141">
         <v>5.0999999999999996</v>
       </c>
-      <c r="G141" t="s">
+      <c r="J141" t="s">
         <v>319</v>
       </c>
     </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="142" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A142">
         <v>189</v>
       </c>
@@ -4724,13 +6155,23 @@
         <v>1</v>
       </c>
       <c r="F142">
+        <v>16</v>
+      </c>
+      <c r="G142">
+        <f t="shared" si="3"/>
+        <v>15</v>
+      </c>
+      <c r="H142">
+        <v>1</v>
+      </c>
+      <c r="I142">
         <v>5.0999999999999996</v>
       </c>
-      <c r="G142" t="s">
+      <c r="J142" t="s">
         <v>319</v>
       </c>
     </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="143" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A143">
         <v>190</v>
       </c>
@@ -4747,13 +6188,23 @@
         <v>1</v>
       </c>
       <c r="F143">
+        <v>16</v>
+      </c>
+      <c r="G143">
+        <f t="shared" si="3"/>
+        <v>15</v>
+      </c>
+      <c r="H143">
+        <v>1</v>
+      </c>
+      <c r="I143">
         <v>5.0999999999999996</v>
       </c>
-      <c r="G143" t="s">
+      <c r="J143" t="s">
         <v>319</v>
       </c>
     </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="144" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A144">
         <v>229</v>
       </c>
@@ -4770,13 +6221,23 @@
         <v>1</v>
       </c>
       <c r="F144">
+        <v>14</v>
+      </c>
+      <c r="G144">
+        <f t="shared" si="3"/>
+        <v>13</v>
+      </c>
+      <c r="H144">
+        <v>1</v>
+      </c>
+      <c r="I144">
         <v>5.4</v>
       </c>
-      <c r="G144" t="s">
+      <c r="J144" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="145" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A145">
         <v>18</v>
       </c>
@@ -4793,13 +6254,23 @@
         <v>1</v>
       </c>
       <c r="F145">
+        <v>14</v>
+      </c>
+      <c r="G145">
+        <f t="shared" si="3"/>
+        <v>13</v>
+      </c>
+      <c r="H145">
+        <v>1</v>
+      </c>
+      <c r="I145">
         <v>1.2</v>
       </c>
-      <c r="G145" t="s">
+      <c r="J145" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="146" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A146">
         <v>226</v>
       </c>
@@ -4816,13 +6287,23 @@
         <v>1</v>
       </c>
       <c r="F146">
+        <v>16</v>
+      </c>
+      <c r="G146">
+        <f t="shared" si="3"/>
+        <v>15</v>
+      </c>
+      <c r="H146">
+        <v>1</v>
+      </c>
+      <c r="I146">
         <v>5.4</v>
       </c>
-      <c r="G146" t="s">
+      <c r="J146" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="147" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A147">
         <v>218</v>
       </c>
@@ -4839,13 +6320,23 @@
         <v>1</v>
       </c>
       <c r="F147">
+        <v>14</v>
+      </c>
+      <c r="G147">
+        <f t="shared" si="3"/>
+        <v>13</v>
+      </c>
+      <c r="H147">
+        <v>1</v>
+      </c>
+      <c r="I147">
         <v>5.3</v>
       </c>
-      <c r="G147" t="s">
+      <c r="J147" t="s">
         <v>279</v>
       </c>
     </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="148" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A148">
         <v>219</v>
       </c>
@@ -4862,13 +6353,23 @@
         <v>1</v>
       </c>
       <c r="F148">
+        <v>14</v>
+      </c>
+      <c r="G148">
+        <f t="shared" si="3"/>
+        <v>13</v>
+      </c>
+      <c r="H148">
+        <v>1</v>
+      </c>
+      <c r="I148">
         <v>5.3</v>
       </c>
-      <c r="G148" t="s">
+      <c r="J148" t="s">
         <v>273</v>
       </c>
     </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="149" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A149">
         <v>220</v>
       </c>
@@ -4885,13 +6386,23 @@
         <v>1</v>
       </c>
       <c r="F149">
+        <v>14</v>
+      </c>
+      <c r="G149">
+        <f t="shared" si="3"/>
+        <v>13</v>
+      </c>
+      <c r="H149">
+        <v>1</v>
+      </c>
+      <c r="I149">
         <v>5.3</v>
       </c>
-      <c r="G149" t="s">
+      <c r="J149" t="s">
         <v>273</v>
       </c>
     </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="150" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A150">
         <v>211</v>
       </c>
@@ -4908,13 +6419,23 @@
         <v>1</v>
       </c>
       <c r="F150">
+        <v>14</v>
+      </c>
+      <c r="G150">
+        <f t="shared" si="3"/>
+        <v>13</v>
+      </c>
+      <c r="H150">
+        <v>1</v>
+      </c>
+      <c r="I150">
         <v>5.2</v>
       </c>
-      <c r="G150" t="s">
+      <c r="J150" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="151" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A151">
         <v>209</v>
       </c>
@@ -4931,13 +6452,23 @@
         <v>1</v>
       </c>
       <c r="F151">
+        <v>14</v>
+      </c>
+      <c r="G151">
+        <f t="shared" si="3"/>
+        <v>13</v>
+      </c>
+      <c r="H151">
+        <v>1</v>
+      </c>
+      <c r="I151">
         <v>5.2</v>
       </c>
-      <c r="G151" t="s">
+      <c r="J151" t="s">
         <v>332</v>
       </c>
     </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="152" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A152">
         <v>206</v>
       </c>
@@ -4954,13 +6485,23 @@
         <v>1</v>
       </c>
       <c r="F152">
+        <v>14</v>
+      </c>
+      <c r="G152">
+        <f t="shared" si="3"/>
+        <v>13</v>
+      </c>
+      <c r="H152">
+        <v>1</v>
+      </c>
+      <c r="I152">
         <v>5.2</v>
       </c>
-      <c r="G152" t="s">
+      <c r="J152" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="153" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A153">
         <v>202</v>
       </c>
@@ -4977,13 +6518,23 @@
         <v>1</v>
       </c>
       <c r="F153">
+        <v>16</v>
+      </c>
+      <c r="G153">
+        <f t="shared" si="3"/>
+        <v>15</v>
+      </c>
+      <c r="H153">
+        <v>1</v>
+      </c>
+      <c r="I153">
         <v>5.2</v>
       </c>
-      <c r="G153" t="s">
+      <c r="J153" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="154" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A154">
         <v>191</v>
       </c>
@@ -5000,13 +6551,23 @@
         <v>1</v>
       </c>
       <c r="F154">
+        <v>16</v>
+      </c>
+      <c r="G154">
+        <f t="shared" si="3"/>
+        <v>15</v>
+      </c>
+      <c r="H154">
+        <v>1</v>
+      </c>
+      <c r="I154">
         <v>5.0999999999999996</v>
       </c>
-      <c r="G154" t="s">
+      <c r="J154" t="s">
         <v>319</v>
       </c>
     </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="155" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A155">
         <v>192</v>
       </c>
@@ -5023,13 +6584,23 @@
         <v>1</v>
       </c>
       <c r="F155">
+        <v>16</v>
+      </c>
+      <c r="G155">
+        <f t="shared" si="3"/>
+        <v>15</v>
+      </c>
+      <c r="H155">
+        <v>1</v>
+      </c>
+      <c r="I155">
         <v>5.0999999999999996</v>
       </c>
-      <c r="G155" t="s">
+      <c r="J155" t="s">
         <v>319</v>
       </c>
     </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="156" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A156">
         <v>73</v>
       </c>
@@ -5040,13 +6611,24 @@
         <v>1</v>
       </c>
       <c r="F156">
+        <v>34</v>
+      </c>
+      <c r="G156">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H156">
+        <f>F156</f>
+        <v>34</v>
+      </c>
+      <c r="I156">
         <v>1.6</v>
       </c>
-      <c r="G156" t="s">
+      <c r="J156" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="157" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A157">
         <v>60</v>
       </c>
@@ -5057,13 +6639,24 @@
         <v>1</v>
       </c>
       <c r="F157">
+        <v>64</v>
+      </c>
+      <c r="G157">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H157">
+        <f t="shared" ref="H157:H180" si="4">F157</f>
+        <v>64</v>
+      </c>
+      <c r="I157">
         <v>1.6</v>
       </c>
-      <c r="G157" t="s">
+      <c r="J157" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="158" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A158">
         <v>53</v>
       </c>
@@ -5074,13 +6667,24 @@
         <v>1</v>
       </c>
       <c r="F158">
+        <v>3</v>
+      </c>
+      <c r="G158">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H158">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="I158">
         <v>1.5</v>
       </c>
-      <c r="G158" t="s">
+      <c r="J158" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="159" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A159">
         <v>70</v>
       </c>
@@ -5091,13 +6695,24 @@
         <v>1</v>
       </c>
       <c r="F159">
+        <v>50</v>
+      </c>
+      <c r="G159">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H159">
+        <f t="shared" si="4"/>
+        <v>50</v>
+      </c>
+      <c r="I159">
         <v>1.6</v>
       </c>
-      <c r="G159" t="s">
+      <c r="J159" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="160" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A160">
         <v>54</v>
       </c>
@@ -5108,13 +6723,24 @@
         <v>1</v>
       </c>
       <c r="F160">
+        <v>5</v>
+      </c>
+      <c r="G160">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H160">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="I160">
         <v>1.5</v>
       </c>
-      <c r="G160" t="s">
+      <c r="J160" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="161" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A161">
         <v>185</v>
       </c>
@@ -5125,13 +6751,24 @@
         <v>1</v>
       </c>
       <c r="F161">
+        <v>40</v>
+      </c>
+      <c r="G161">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H161">
+        <f t="shared" si="4"/>
+        <v>40</v>
+      </c>
+      <c r="I161">
         <v>4.3</v>
       </c>
-      <c r="G161" t="s">
+      <c r="J161" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="162" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A162">
         <v>142</v>
       </c>
@@ -5142,13 +6779,24 @@
         <v>1</v>
       </c>
       <c r="F162">
+        <v>26</v>
+      </c>
+      <c r="G162">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H162">
+        <f t="shared" si="4"/>
+        <v>26</v>
+      </c>
+      <c r="I162">
         <v>3.3</v>
       </c>
-      <c r="G162" t="s">
+      <c r="J162" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="163" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A163">
         <v>143</v>
       </c>
@@ -5159,13 +6807,24 @@
         <v>1</v>
       </c>
       <c r="F163">
+        <v>26</v>
+      </c>
+      <c r="G163">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H163">
+        <f t="shared" si="4"/>
+        <v>26</v>
+      </c>
+      <c r="I163">
         <v>3.3</v>
       </c>
-      <c r="G163" t="s">
+      <c r="J163" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="164" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A164">
         <v>184</v>
       </c>
@@ -5176,13 +6835,24 @@
         <v>1</v>
       </c>
       <c r="F164">
+        <v>26</v>
+      </c>
+      <c r="G164">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H164">
+        <f t="shared" si="4"/>
+        <v>26</v>
+      </c>
+      <c r="I164">
         <v>4.3</v>
       </c>
-      <c r="G164" t="s">
+      <c r="J164" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="165" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A165">
         <v>277</v>
       </c>
@@ -5193,13 +6863,24 @@
         <v>1</v>
       </c>
       <c r="F165">
+        <v>2</v>
+      </c>
+      <c r="G165">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H165">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="I165">
         <v>6.2</v>
       </c>
-      <c r="G165" t="s">
+      <c r="J165" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="166" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A166">
         <v>166</v>
       </c>
@@ -5210,13 +6891,24 @@
         <v>1</v>
       </c>
       <c r="F166">
+        <v>2</v>
+      </c>
+      <c r="G166">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H166">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="I166">
         <v>4.2</v>
       </c>
-      <c r="G166" t="s">
+      <c r="J166" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="167" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A167">
         <v>257</v>
       </c>
@@ -5227,13 +6919,24 @@
         <v>1</v>
       </c>
       <c r="F167">
+        <v>12</v>
+      </c>
+      <c r="G167">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H167">
+        <f t="shared" si="4"/>
+        <v>12</v>
+      </c>
+      <c r="I167">
         <v>6.1</v>
       </c>
-      <c r="G167" t="s">
+      <c r="J167" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="168" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A168">
         <v>19</v>
       </c>
@@ -5244,13 +6947,24 @@
         <v>1</v>
       </c>
       <c r="F168">
+        <v>2</v>
+      </c>
+      <c r="G168">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H168">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="I168">
         <v>1.2</v>
       </c>
-      <c r="G168" t="s">
+      <c r="J168" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="169" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A169">
         <v>265</v>
       </c>
@@ -5261,13 +6975,24 @@
         <v>1</v>
       </c>
       <c r="F169">
+        <v>2</v>
+      </c>
+      <c r="G169">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H169">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="I169">
         <v>6.2</v>
       </c>
-      <c r="G169" t="s">
+      <c r="J169" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="170" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A170">
         <v>224</v>
       </c>
@@ -5278,13 +7003,24 @@
         <v>1</v>
       </c>
       <c r="F170">
+        <v>2</v>
+      </c>
+      <c r="G170">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H170">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="I170">
         <v>5.4</v>
       </c>
-      <c r="G170" t="s">
+      <c r="J170" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="171" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A171">
         <v>280</v>
       </c>
@@ -5295,13 +7031,24 @@
         <v>1</v>
       </c>
       <c r="F171">
+        <v>2</v>
+      </c>
+      <c r="G171">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H171">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="I171">
         <v>6.2</v>
       </c>
-      <c r="G171" t="s">
+      <c r="J171" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="172" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A172">
         <v>279</v>
       </c>
@@ -5312,13 +7059,24 @@
         <v>1</v>
       </c>
       <c r="F172">
+        <v>2</v>
+      </c>
+      <c r="G172">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H172">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="I172">
         <v>6.2</v>
       </c>
-      <c r="G172" t="s">
+      <c r="J172" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="173" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A173">
         <v>267</v>
       </c>
@@ -5329,13 +7087,24 @@
         <v>1</v>
       </c>
       <c r="F173">
+        <v>2</v>
+      </c>
+      <c r="G173">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H173">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="I173">
         <v>6.2</v>
       </c>
-      <c r="G173" t="s">
+      <c r="J173" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="174" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A174">
         <v>222</v>
       </c>
@@ -5346,13 +7115,24 @@
         <v>1</v>
       </c>
       <c r="F174">
+        <v>2</v>
+      </c>
+      <c r="G174">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H174">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="I174">
         <v>5.4</v>
       </c>
-      <c r="G174" t="s">
+      <c r="J174" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="175" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="175" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A175">
         <v>281</v>
       </c>
@@ -5363,13 +7143,24 @@
         <v>1</v>
       </c>
       <c r="F175">
+        <v>2</v>
+      </c>
+      <c r="G175">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H175">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="I175">
         <v>6.2</v>
       </c>
-      <c r="G175" t="s">
+      <c r="J175" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="176" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="176" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A176">
         <v>140</v>
       </c>
@@ -5380,13 +7171,24 @@
         <v>1</v>
       </c>
       <c r="F176">
+        <v>4</v>
+      </c>
+      <c r="G176">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H176">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="I176">
         <v>3.3</v>
       </c>
-      <c r="G176" t="s">
+      <c r="J176" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="177" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="177" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A177">
         <v>282</v>
       </c>
@@ -5397,13 +7199,24 @@
         <v>1</v>
       </c>
       <c r="F177">
+        <v>2</v>
+      </c>
+      <c r="G177">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H177">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="I177">
         <v>6.2</v>
       </c>
-      <c r="G177" t="s">
+      <c r="J177" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="178" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="178" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A178">
         <v>278</v>
       </c>
@@ -5414,13 +7227,24 @@
         <v>1</v>
       </c>
       <c r="F178">
+        <v>2</v>
+      </c>
+      <c r="G178">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H178">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="I178">
         <v>6.2</v>
       </c>
-      <c r="G178" t="s">
+      <c r="J178" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="179" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="179" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A179">
         <v>182</v>
       </c>
@@ -5431,13 +7255,24 @@
         <v>1</v>
       </c>
       <c r="F179">
+        <v>18</v>
+      </c>
+      <c r="G179">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H179">
+        <f t="shared" si="4"/>
+        <v>18</v>
+      </c>
+      <c r="I179">
         <v>4.3</v>
       </c>
-      <c r="G179" t="s">
+      <c r="J179" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="180" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="180" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A180">
         <v>180</v>
       </c>
@@ -5448,13 +7283,24 @@
         <v>1</v>
       </c>
       <c r="F180">
+        <v>4</v>
+      </c>
+      <c r="G180">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H180">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="I180">
         <v>4.3</v>
       </c>
-      <c r="G180" t="s">
+      <c r="J180" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="181" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="181" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A181">
         <v>63</v>
       </c>
@@ -5471,13 +7317,23 @@
         <v>1</v>
       </c>
       <c r="F181">
+        <v>2</v>
+      </c>
+      <c r="G181">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+      <c r="H181">
+        <v>0</v>
+      </c>
+      <c r="I181">
         <v>1.6</v>
       </c>
-      <c r="G181" t="s">
+      <c r="J181" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="182" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="182" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A182">
         <v>51</v>
       </c>
@@ -5494,10 +7350,20 @@
         <v>1</v>
       </c>
       <c r="F182">
+        <v>2</v>
+      </c>
+      <c r="G182">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+      <c r="H182">
+        <v>0</v>
+      </c>
+      <c r="I182">
         <v>1.5</v>
       </c>
     </row>
-    <row r="183" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="183" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A183">
         <v>38</v>
       </c>
@@ -5514,10 +7380,20 @@
         <v>1</v>
       </c>
       <c r="F183">
+        <v>2</v>
+      </c>
+      <c r="G183">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+      <c r="H183">
+        <v>0</v>
+      </c>
+      <c r="I183">
         <v>1.4</v>
       </c>
     </row>
-    <row r="184" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="184" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A184">
         <v>46</v>
       </c>
@@ -5534,10 +7410,20 @@
         <v>1</v>
       </c>
       <c r="F184">
+        <v>2</v>
+      </c>
+      <c r="G184">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+      <c r="H184">
+        <v>0</v>
+      </c>
+      <c r="I184">
         <v>1.4</v>
       </c>
     </row>
-    <row r="185" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="185" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A185">
         <v>45</v>
       </c>
@@ -5554,10 +7440,20 @@
         <v>1</v>
       </c>
       <c r="F185">
+        <v>2</v>
+      </c>
+      <c r="G185">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+      <c r="H185">
+        <v>0</v>
+      </c>
+      <c r="I185">
         <v>1.4</v>
       </c>
     </row>
-    <row r="186" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="186" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A186">
         <v>44</v>
       </c>
@@ -5574,10 +7470,20 @@
         <v>1</v>
       </c>
       <c r="F186">
+        <v>2</v>
+      </c>
+      <c r="G186">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+      <c r="H186">
+        <v>0</v>
+      </c>
+      <c r="I186">
         <v>1.4</v>
       </c>
     </row>
-    <row r="187" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="187" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A187">
         <v>43</v>
       </c>
@@ -5594,10 +7500,20 @@
         <v>1</v>
       </c>
       <c r="F187">
+        <v>2</v>
+      </c>
+      <c r="G187">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+      <c r="H187">
+        <v>0</v>
+      </c>
+      <c r="I187">
         <v>1.4</v>
       </c>
     </row>
-    <row r="188" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="188" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A188">
         <v>42</v>
       </c>
@@ -5614,10 +7530,20 @@
         <v>1</v>
       </c>
       <c r="F188">
+        <v>2</v>
+      </c>
+      <c r="G188">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+      <c r="H188">
+        <v>0</v>
+      </c>
+      <c r="I188">
         <v>1.4</v>
       </c>
     </row>
-    <row r="189" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="189" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A189">
         <v>33</v>
       </c>
@@ -5634,13 +7560,23 @@
         <v>1</v>
       </c>
       <c r="F189">
+        <v>2</v>
+      </c>
+      <c r="G189">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+      <c r="H189">
+        <v>0</v>
+      </c>
+      <c r="I189">
         <v>1.4</v>
       </c>
-      <c r="G189" t="s">
+      <c r="J189" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="190" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="190" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A190">
         <v>39</v>
       </c>
@@ -5657,13 +7593,23 @@
         <v>1</v>
       </c>
       <c r="F190">
+        <v>2</v>
+      </c>
+      <c r="G190">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+      <c r="H190">
+        <v>0</v>
+      </c>
+      <c r="I190">
         <v>1.4</v>
       </c>
-      <c r="G190" t="s">
+      <c r="J190" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="191" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="191" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A191">
         <v>47</v>
       </c>
@@ -5680,13 +7626,23 @@
         <v>1</v>
       </c>
       <c r="F191">
+        <v>2</v>
+      </c>
+      <c r="G191">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+      <c r="H191">
+        <v>0</v>
+      </c>
+      <c r="I191">
         <v>1.4</v>
       </c>
-      <c r="G191" t="s">
+      <c r="J191" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="192" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="192" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A192">
         <v>64</v>
       </c>
@@ -5703,13 +7659,23 @@
         <v>1</v>
       </c>
       <c r="F192">
+        <v>2</v>
+      </c>
+      <c r="G192">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+      <c r="H192">
+        <v>0</v>
+      </c>
+      <c r="I192">
         <v>1.6</v>
       </c>
-      <c r="G192" t="s">
+      <c r="J192" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="193" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="193" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A193">
         <v>28</v>
       </c>
@@ -5726,13 +7692,23 @@
         <v>1</v>
       </c>
       <c r="F193">
+        <v>2</v>
+      </c>
+      <c r="G193">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+      <c r="H193">
+        <v>0</v>
+      </c>
+      <c r="I193">
         <v>1.3</v>
       </c>
-      <c r="G193" t="s">
+      <c r="J193" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="194" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="194" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A194">
         <v>106</v>
       </c>
@@ -5749,10 +7725,20 @@
         <v>1</v>
       </c>
       <c r="F194">
+        <v>2</v>
+      </c>
+      <c r="G194">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+      <c r="H194">
+        <v>0</v>
+      </c>
+      <c r="I194">
         <v>2.2000000000000002</v>
       </c>
     </row>
-    <row r="195" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="195" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A195">
         <v>107</v>
       </c>
@@ -5769,10 +7755,20 @@
         <v>1</v>
       </c>
       <c r="F195">
+        <v>2</v>
+      </c>
+      <c r="G195">
+        <f t="shared" ref="G195:G258" si="5">F195-H195</f>
+        <v>2</v>
+      </c>
+      <c r="H195">
+        <v>0</v>
+      </c>
+      <c r="I195">
         <v>2.2000000000000002</v>
       </c>
     </row>
-    <row r="196" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="196" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A196">
         <v>165</v>
       </c>
@@ -5789,13 +7785,23 @@
         <v>1</v>
       </c>
       <c r="F196">
+        <v>2</v>
+      </c>
+      <c r="G196">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="H196">
+        <v>0</v>
+      </c>
+      <c r="I196">
         <v>4.2</v>
       </c>
-      <c r="G196" t="s">
+      <c r="J196" t="s">
         <v>324</v>
       </c>
     </row>
-    <row r="197" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="197" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A197">
         <v>36</v>
       </c>
@@ -5812,10 +7818,20 @@
         <v>1</v>
       </c>
       <c r="F197">
+        <v>2</v>
+      </c>
+      <c r="G197">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="H197">
+        <v>0</v>
+      </c>
+      <c r="I197">
         <v>1.4</v>
       </c>
     </row>
-    <row r="198" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="198" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A198">
         <v>249</v>
       </c>
@@ -5832,13 +7848,23 @@
         <v>1</v>
       </c>
       <c r="F198">
+        <v>2</v>
+      </c>
+      <c r="G198">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="H198">
+        <v>0</v>
+      </c>
+      <c r="I198">
         <v>6.1</v>
       </c>
-      <c r="G198" t="s">
+      <c r="J198" t="s">
         <v>337</v>
       </c>
     </row>
-    <row r="199" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="199" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A199">
         <v>20</v>
       </c>
@@ -5855,13 +7881,23 @@
         <v>1</v>
       </c>
       <c r="F199">
+        <v>2</v>
+      </c>
+      <c r="G199">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="H199">
+        <v>0</v>
+      </c>
+      <c r="I199">
         <v>1.2</v>
       </c>
-      <c r="G199" t="s">
+      <c r="J199" t="s">
         <v>288</v>
       </c>
     </row>
-    <row r="200" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="200" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A200">
         <v>2</v>
       </c>
@@ -5878,13 +7914,23 @@
         <v>1</v>
       </c>
       <c r="F200">
+        <v>2</v>
+      </c>
+      <c r="G200">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="H200">
+        <v>0</v>
+      </c>
+      <c r="I200">
         <v>1.1000000000000001</v>
       </c>
-      <c r="G200" t="s">
+      <c r="J200" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="201" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="201" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A201">
         <v>3</v>
       </c>
@@ -5901,13 +7947,23 @@
         <v>1</v>
       </c>
       <c r="F201">
+        <v>2</v>
+      </c>
+      <c r="G201">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="H201">
+        <v>0</v>
+      </c>
+      <c r="I201">
         <v>1.1000000000000001</v>
       </c>
-      <c r="G201" t="s">
+      <c r="J201" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="202" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="202" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A202">
         <v>12</v>
       </c>
@@ -5924,13 +7980,23 @@
         <v>1</v>
       </c>
       <c r="F202">
+        <v>2</v>
+      </c>
+      <c r="G202">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="H202">
+        <v>0</v>
+      </c>
+      <c r="I202">
         <v>1.1000000000000001</v>
       </c>
-      <c r="G202" t="s">
+      <c r="J202" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="203" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="203" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A203">
         <v>85</v>
       </c>
@@ -5941,13 +8007,23 @@
         <v>1</v>
       </c>
       <c r="F203">
+        <v>2</v>
+      </c>
+      <c r="G203">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="H203">
+        <v>0</v>
+      </c>
+      <c r="I203">
         <v>2.1</v>
       </c>
-      <c r="G203" t="s">
+      <c r="J203" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="204" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="204" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A204">
         <v>86</v>
       </c>
@@ -5958,13 +8034,23 @@
         <v>1</v>
       </c>
       <c r="F204">
+        <v>2</v>
+      </c>
+      <c r="G204">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="H204">
+        <v>0</v>
+      </c>
+      <c r="I204">
         <v>2.1</v>
       </c>
-      <c r="G204" t="s">
+      <c r="J204" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="205" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="205" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A205">
         <v>65</v>
       </c>
@@ -5981,13 +8067,23 @@
         <v>1</v>
       </c>
       <c r="F205">
+        <v>2</v>
+      </c>
+      <c r="G205">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="H205">
+        <v>0</v>
+      </c>
+      <c r="I205">
         <v>1.6</v>
       </c>
-      <c r="G205" t="s">
+      <c r="J205" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="206" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="206" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A206">
         <v>87</v>
       </c>
@@ -5998,13 +8094,23 @@
         <v>1</v>
       </c>
       <c r="F206">
+        <v>2</v>
+      </c>
+      <c r="G206">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="H206">
+        <v>0</v>
+      </c>
+      <c r="I206">
         <v>2.1</v>
       </c>
-      <c r="G206" t="s">
+      <c r="J206" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="207" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="207" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A207">
         <v>88</v>
       </c>
@@ -6015,13 +8121,23 @@
         <v>1</v>
       </c>
       <c r="F207">
+        <v>2</v>
+      </c>
+      <c r="G207">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="H207">
+        <v>0</v>
+      </c>
+      <c r="I207">
         <v>2.1</v>
       </c>
-      <c r="G207" t="s">
+      <c r="J207" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="208" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="208" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A208">
         <v>89</v>
       </c>
@@ -6032,13 +8148,23 @@
         <v>1</v>
       </c>
       <c r="F208">
+        <v>2</v>
+      </c>
+      <c r="G208">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="H208">
+        <v>0</v>
+      </c>
+      <c r="I208">
         <v>2.1</v>
       </c>
-      <c r="G208" t="s">
+      <c r="J208" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="209" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="209" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A209">
         <v>90</v>
       </c>
@@ -6049,13 +8175,23 @@
         <v>1</v>
       </c>
       <c r="F209">
+        <v>2</v>
+      </c>
+      <c r="G209">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="H209">
+        <v>0</v>
+      </c>
+      <c r="I209">
         <v>2.1</v>
       </c>
-      <c r="G209" t="s">
+      <c r="J209" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="210" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="210" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A210">
         <v>91</v>
       </c>
@@ -6066,13 +8202,23 @@
         <v>1</v>
       </c>
       <c r="F210">
+        <v>2</v>
+      </c>
+      <c r="G210">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="H210">
+        <v>0</v>
+      </c>
+      <c r="I210">
         <v>2.1</v>
       </c>
-      <c r="G210" t="s">
+      <c r="J210" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="211" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="211" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A211">
         <v>92</v>
       </c>
@@ -6083,13 +8229,23 @@
         <v>1</v>
       </c>
       <c r="F211">
+        <v>2</v>
+      </c>
+      <c r="G211">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="H211">
+        <v>0</v>
+      </c>
+      <c r="I211">
         <v>2.1</v>
       </c>
-      <c r="G211" t="s">
+      <c r="J211" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="212" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="212" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A212">
         <v>105</v>
       </c>
@@ -6106,10 +8262,20 @@
         <v>1</v>
       </c>
       <c r="F212">
+        <v>2</v>
+      </c>
+      <c r="G212">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="H212">
+        <v>0</v>
+      </c>
+      <c r="I212">
         <v>2.2000000000000002</v>
       </c>
     </row>
-    <row r="213" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="213" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A213">
         <v>114</v>
       </c>
@@ -6126,10 +8292,20 @@
         <v>1</v>
       </c>
       <c r="F213">
+        <v>2</v>
+      </c>
+      <c r="G213">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="H213">
+        <v>0</v>
+      </c>
+      <c r="I213">
         <v>2.4</v>
       </c>
     </row>
-    <row r="214" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="214" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A214">
         <v>115</v>
       </c>
@@ -6146,10 +8322,20 @@
         <v>1</v>
       </c>
       <c r="F214">
+        <v>2</v>
+      </c>
+      <c r="G214">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="H214">
+        <v>0</v>
+      </c>
+      <c r="I214">
         <v>2.4</v>
       </c>
     </row>
-    <row r="215" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="215" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A215">
         <v>116</v>
       </c>
@@ -6166,10 +8352,20 @@
         <v>1</v>
       </c>
       <c r="F215">
+        <v>2</v>
+      </c>
+      <c r="G215">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="H215">
+        <v>0</v>
+      </c>
+      <c r="I215">
         <v>2.4</v>
       </c>
     </row>
-    <row r="216" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="216" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A216">
         <v>66</v>
       </c>
@@ -6186,13 +8382,23 @@
         <v>1</v>
       </c>
       <c r="F216">
+        <v>2</v>
+      </c>
+      <c r="G216">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="H216">
+        <v>0</v>
+      </c>
+      <c r="I216">
         <v>1.6</v>
       </c>
-      <c r="G216" t="s">
+      <c r="J216" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="217" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="217" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A217">
         <v>117</v>
       </c>
@@ -6209,10 +8415,20 @@
         <v>1</v>
       </c>
       <c r="F217">
+        <v>2</v>
+      </c>
+      <c r="G217">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="H217">
+        <v>0</v>
+      </c>
+      <c r="I217">
         <v>2.4</v>
       </c>
     </row>
-    <row r="218" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="218" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A218">
         <v>118</v>
       </c>
@@ -6229,10 +8445,20 @@
         <v>1</v>
       </c>
       <c r="F218">
+        <v>2</v>
+      </c>
+      <c r="G218">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="H218">
+        <v>0</v>
+      </c>
+      <c r="I218">
         <v>2.4</v>
       </c>
     </row>
-    <row r="219" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="219" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A219">
         <v>119</v>
       </c>
@@ -6249,10 +8475,20 @@
         <v>1</v>
       </c>
       <c r="F219">
+        <v>2</v>
+      </c>
+      <c r="G219">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="H219">
+        <v>0</v>
+      </c>
+      <c r="I219">
         <v>2.4</v>
       </c>
     </row>
-    <row r="220" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="220" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A220">
         <v>153</v>
       </c>
@@ -6269,13 +8505,23 @@
         <v>1</v>
       </c>
       <c r="F220">
+        <v>2</v>
+      </c>
+      <c r="G220">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="H220">
+        <v>0</v>
+      </c>
+      <c r="I220">
         <v>4.0999999999999996</v>
       </c>
-      <c r="G220" t="s">
+      <c r="J220" t="s">
         <v>320</v>
       </c>
     </row>
-    <row r="221" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="221" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A221">
         <v>154</v>
       </c>
@@ -6292,13 +8538,23 @@
         <v>1</v>
       </c>
       <c r="F221">
+        <v>2</v>
+      </c>
+      <c r="G221">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="H221">
+        <v>0</v>
+      </c>
+      <c r="I221">
         <v>4.0999999999999996</v>
       </c>
-      <c r="G221" t="s">
+      <c r="J221" t="s">
         <v>320</v>
       </c>
     </row>
-    <row r="222" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="222" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A222">
         <v>155</v>
       </c>
@@ -6315,13 +8571,23 @@
         <v>1</v>
       </c>
       <c r="F222">
+        <v>2</v>
+      </c>
+      <c r="G222">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="H222">
+        <v>0</v>
+      </c>
+      <c r="I222">
         <v>4.0999999999999996</v>
       </c>
-      <c r="G222" t="s">
+      <c r="J222" t="s">
         <v>320</v>
       </c>
     </row>
-    <row r="223" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="223" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A223">
         <v>156</v>
       </c>
@@ -6338,13 +8604,23 @@
         <v>1</v>
       </c>
       <c r="F223">
+        <v>2</v>
+      </c>
+      <c r="G223">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="H223">
+        <v>0</v>
+      </c>
+      <c r="I223">
         <v>4.0999999999999996</v>
       </c>
-      <c r="G223" t="s">
+      <c r="J223" t="s">
         <v>320</v>
       </c>
     </row>
-    <row r="224" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="224" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A224">
         <v>157</v>
       </c>
@@ -6361,13 +8637,23 @@
         <v>1</v>
       </c>
       <c r="F224">
+        <v>2</v>
+      </c>
+      <c r="G224">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="H224">
+        <v>0</v>
+      </c>
+      <c r="I224">
         <v>4.0999999999999996</v>
       </c>
-      <c r="G224" t="s">
+      <c r="J224" t="s">
         <v>320</v>
       </c>
     </row>
-    <row r="225" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="225" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A225">
         <v>158</v>
       </c>
@@ -6384,13 +8670,23 @@
         <v>1</v>
       </c>
       <c r="F225">
+        <v>2</v>
+      </c>
+      <c r="G225">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="H225">
+        <v>0</v>
+      </c>
+      <c r="I225">
         <v>4.0999999999999996</v>
       </c>
-      <c r="G225" t="s">
+      <c r="J225" t="s">
         <v>320</v>
       </c>
     </row>
-    <row r="226" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="226" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A226">
         <v>159</v>
       </c>
@@ -6407,13 +8703,23 @@
         <v>1</v>
       </c>
       <c r="F226">
+        <v>2</v>
+      </c>
+      <c r="G226">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="H226">
+        <v>0</v>
+      </c>
+      <c r="I226">
         <v>4.0999999999999996</v>
       </c>
-      <c r="G226" t="s">
+      <c r="J226" t="s">
         <v>320</v>
       </c>
     </row>
-    <row r="227" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="227" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A227">
         <v>67</v>
       </c>
@@ -6430,13 +8736,23 @@
         <v>1</v>
       </c>
       <c r="F227">
+        <v>2</v>
+      </c>
+      <c r="G227">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="H227">
+        <v>0</v>
+      </c>
+      <c r="I227">
         <v>1.6</v>
       </c>
-      <c r="G227" t="s">
+      <c r="J227" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="228" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="228" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A228">
         <v>160</v>
       </c>
@@ -6453,13 +8769,23 @@
         <v>1</v>
       </c>
       <c r="F228">
+        <v>2</v>
+      </c>
+      <c r="G228">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="H228">
+        <v>0</v>
+      </c>
+      <c r="I228">
         <v>4.0999999999999996</v>
       </c>
-      <c r="G228" t="s">
+      <c r="J228" t="s">
         <v>320</v>
       </c>
     </row>
-    <row r="229" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="229" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A229">
         <v>161</v>
       </c>
@@ -6476,13 +8802,23 @@
         <v>1</v>
       </c>
       <c r="F229">
+        <v>2</v>
+      </c>
+      <c r="G229">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="H229">
+        <v>0</v>
+      </c>
+      <c r="I229">
         <v>4.0999999999999996</v>
       </c>
-      <c r="G229" t="s">
+      <c r="J229" t="s">
         <v>320</v>
       </c>
     </row>
-    <row r="230" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="230" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A230">
         <v>162</v>
       </c>
@@ -6499,13 +8835,23 @@
         <v>1</v>
       </c>
       <c r="F230">
+        <v>2</v>
+      </c>
+      <c r="G230">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="H230">
+        <v>0</v>
+      </c>
+      <c r="I230">
         <v>4.0999999999999996</v>
       </c>
-      <c r="G230" t="s">
+      <c r="J230" t="s">
         <v>320</v>
       </c>
     </row>
-    <row r="231" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="231" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A231">
         <v>176</v>
       </c>
@@ -6522,16 +8868,26 @@
         <v>1</v>
       </c>
       <c r="F231">
+        <v>2</v>
+      </c>
+      <c r="G231">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="H231">
+        <v>0</v>
+      </c>
+      <c r="I231">
         <v>4.2</v>
       </c>
-      <c r="G231" t="s">
+      <c r="J231" t="s">
         <v>328</v>
       </c>
-      <c r="I231" t="s">
+      <c r="L231" t="s">
         <v>424</v>
       </c>
     </row>
-    <row r="232" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="232" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A232">
         <v>196</v>
       </c>
@@ -6548,13 +8904,23 @@
         <v>1</v>
       </c>
       <c r="F232">
+        <v>2</v>
+      </c>
+      <c r="G232">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="H232">
+        <v>0</v>
+      </c>
+      <c r="I232">
         <v>5.2</v>
       </c>
-      <c r="G232" t="s">
+      <c r="J232" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="233" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="233" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A233">
         <v>200</v>
       </c>
@@ -6571,13 +8937,23 @@
         <v>1</v>
       </c>
       <c r="F233">
+        <v>2</v>
+      </c>
+      <c r="G233">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="H233">
+        <v>0</v>
+      </c>
+      <c r="I233">
         <v>5.2</v>
       </c>
-      <c r="G233" t="s">
+      <c r="J233" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="234" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="234" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A234">
         <v>204</v>
       </c>
@@ -6588,13 +8964,23 @@
         <v>1</v>
       </c>
       <c r="F234">
+        <v>2</v>
+      </c>
+      <c r="G234">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="H234">
+        <v>0</v>
+      </c>
+      <c r="I234">
         <v>5.2</v>
       </c>
-      <c r="G234" t="s">
+      <c r="J234" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="235" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="235" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A235">
         <v>207</v>
       </c>
@@ -6605,13 +8991,23 @@
         <v>1</v>
       </c>
       <c r="F235">
+        <v>2</v>
+      </c>
+      <c r="G235">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="H235">
+        <v>0</v>
+      </c>
+      <c r="I235">
         <v>5.2</v>
       </c>
-      <c r="G235" t="s">
+      <c r="J235" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="236" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="236" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A236">
         <v>178</v>
       </c>
@@ -6628,13 +9024,23 @@
         <v>1</v>
       </c>
       <c r="F236">
+        <v>2</v>
+      </c>
+      <c r="G236">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="H236">
+        <v>0</v>
+      </c>
+      <c r="I236">
         <v>4.3</v>
       </c>
-      <c r="G236" t="s">
+      <c r="J236" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="237" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="237" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A237">
         <v>179</v>
       </c>
@@ -6651,13 +9057,23 @@
         <v>1</v>
       </c>
       <c r="F237">
+        <v>2</v>
+      </c>
+      <c r="G237">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="H237">
+        <v>0</v>
+      </c>
+      <c r="I237">
         <v>4.3</v>
       </c>
-      <c r="G237" t="s">
+      <c r="J237" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="238" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="238" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A238">
         <v>230</v>
       </c>
@@ -6674,13 +9090,23 @@
         <v>1</v>
       </c>
       <c r="F238">
+        <v>2</v>
+      </c>
+      <c r="G238">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="H238">
+        <v>0</v>
+      </c>
+      <c r="I238">
         <v>5.4</v>
       </c>
-      <c r="G238" t="s">
+      <c r="J238" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="239" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="239" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A239">
         <v>231</v>
       </c>
@@ -6697,13 +9123,23 @@
         <v>1</v>
       </c>
       <c r="F239">
+        <v>2</v>
+      </c>
+      <c r="G239">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="H239">
+        <v>0</v>
+      </c>
+      <c r="I239">
         <v>5.4</v>
       </c>
-      <c r="G239" t="s">
+      <c r="J239" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="240" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="240" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A240">
         <v>232</v>
       </c>
@@ -6720,13 +9156,23 @@
         <v>1</v>
       </c>
       <c r="F240">
+        <v>2</v>
+      </c>
+      <c r="G240">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="H240">
+        <v>0</v>
+      </c>
+      <c r="I240">
         <v>5.4</v>
       </c>
-      <c r="G240" t="s">
+      <c r="J240" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="241" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="241" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A241">
         <v>233</v>
       </c>
@@ -6743,13 +9189,23 @@
         <v>1</v>
       </c>
       <c r="F241">
+        <v>2</v>
+      </c>
+      <c r="G241">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="H241">
+        <v>0</v>
+      </c>
+      <c r="I241">
         <v>5.4</v>
       </c>
-      <c r="G241" t="s">
+      <c r="J241" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="242" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="242" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A242">
         <v>234</v>
       </c>
@@ -6766,13 +9222,23 @@
         <v>1</v>
       </c>
       <c r="F242">
+        <v>2</v>
+      </c>
+      <c r="G242">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="H242">
+        <v>0</v>
+      </c>
+      <c r="I242">
         <v>5.4</v>
       </c>
-      <c r="G242" t="s">
+      <c r="J242" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="243" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="243" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A243">
         <v>235</v>
       </c>
@@ -6789,13 +9255,23 @@
         <v>1</v>
       </c>
       <c r="F243">
+        <v>2</v>
+      </c>
+      <c r="G243">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="H243">
+        <v>0</v>
+      </c>
+      <c r="I243">
         <v>5.4</v>
       </c>
-      <c r="G243" t="s">
+      <c r="J243" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="244" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="244" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A244">
         <v>236</v>
       </c>
@@ -6812,13 +9288,23 @@
         <v>1</v>
       </c>
       <c r="F244">
+        <v>2</v>
+      </c>
+      <c r="G244">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="H244">
+        <v>0</v>
+      </c>
+      <c r="I244">
         <v>5.4</v>
       </c>
-      <c r="G244" t="s">
+      <c r="J244" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="245" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="245" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A245">
         <v>237</v>
       </c>
@@ -6835,13 +9321,23 @@
         <v>1</v>
       </c>
       <c r="F245">
+        <v>2</v>
+      </c>
+      <c r="G245">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="H245">
+        <v>0</v>
+      </c>
+      <c r="I245">
         <v>5.4</v>
       </c>
-      <c r="G245" t="s">
+      <c r="J245" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="246" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="246" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A246">
         <v>238</v>
       </c>
@@ -6858,13 +9354,23 @@
         <v>1</v>
       </c>
       <c r="F246">
+        <v>2</v>
+      </c>
+      <c r="G246">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="H246">
+        <v>0</v>
+      </c>
+      <c r="I246">
         <v>5.4</v>
       </c>
-      <c r="G246" t="s">
+      <c r="J246" t="s">
         <v>336</v>
       </c>
     </row>
-    <row r="247" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="247" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A247">
         <v>239</v>
       </c>
@@ -6881,13 +9387,23 @@
         <v>1</v>
       </c>
       <c r="F247">
+        <v>2</v>
+      </c>
+      <c r="G247">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="H247">
+        <v>0</v>
+      </c>
+      <c r="I247">
         <v>5.4</v>
       </c>
-      <c r="G247" t="s">
+      <c r="J247" t="s">
         <v>336</v>
       </c>
     </row>
-    <row r="248" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="248" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A248">
         <v>68</v>
       </c>
@@ -6904,13 +9420,23 @@
         <v>1</v>
       </c>
       <c r="F248">
+        <v>2</v>
+      </c>
+      <c r="G248">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="H248">
+        <v>0</v>
+      </c>
+      <c r="I248">
         <v>1.6</v>
       </c>
-      <c r="G248" t="s">
+      <c r="J248" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="249" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="249" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A249">
         <v>240</v>
       </c>
@@ -6927,13 +9453,23 @@
         <v>1</v>
       </c>
       <c r="F249">
+        <v>2</v>
+      </c>
+      <c r="G249">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="H249">
+        <v>0</v>
+      </c>
+      <c r="I249">
         <v>5.4</v>
       </c>
-      <c r="G249" t="s">
+      <c r="J249" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="250" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="250" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A250">
         <v>241</v>
       </c>
@@ -6950,13 +9486,23 @@
         <v>1</v>
       </c>
       <c r="F250">
+        <v>2</v>
+      </c>
+      <c r="G250">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="H250">
+        <v>0</v>
+      </c>
+      <c r="I250">
         <v>5.4</v>
       </c>
-      <c r="G250" t="s">
+      <c r="J250" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="251" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="251" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A251">
         <v>242</v>
       </c>
@@ -6973,13 +9519,23 @@
         <v>1</v>
       </c>
       <c r="F251">
+        <v>2</v>
+      </c>
+      <c r="G251">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="H251">
+        <v>0</v>
+      </c>
+      <c r="I251">
         <v>5.4</v>
       </c>
-      <c r="G251" t="s">
+      <c r="J251" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="252" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="252" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A252">
         <v>243</v>
       </c>
@@ -6996,13 +9552,23 @@
         <v>1</v>
       </c>
       <c r="F252">
+        <v>2</v>
+      </c>
+      <c r="G252">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="H252">
+        <v>0</v>
+      </c>
+      <c r="I252">
         <v>5.4</v>
       </c>
-      <c r="G252" t="s">
+      <c r="J252" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="253" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="253" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A253">
         <v>244</v>
       </c>
@@ -7019,13 +9585,23 @@
         <v>1</v>
       </c>
       <c r="F253">
+        <v>2</v>
+      </c>
+      <c r="G253">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="H253">
+        <v>0</v>
+      </c>
+      <c r="I253">
         <v>5.4</v>
       </c>
-      <c r="G253" t="s">
+      <c r="J253" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="254" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="254" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A254">
         <v>245</v>
       </c>
@@ -7042,13 +9618,23 @@
         <v>1</v>
       </c>
       <c r="F254">
+        <v>2</v>
+      </c>
+      <c r="G254">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="H254">
+        <v>0</v>
+      </c>
+      <c r="I254">
         <v>5.4</v>
       </c>
-      <c r="G254" t="s">
+      <c r="J254" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="255" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="255" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A255">
         <v>246</v>
       </c>
@@ -7065,13 +9651,23 @@
         <v>1</v>
       </c>
       <c r="F255">
+        <v>2</v>
+      </c>
+      <c r="G255">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="H255">
+        <v>0</v>
+      </c>
+      <c r="I255">
         <v>5.4</v>
       </c>
-      <c r="G255" t="s">
+      <c r="J255" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="256" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="256" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A256">
         <v>247</v>
       </c>
@@ -7088,13 +9684,23 @@
         <v>1</v>
       </c>
       <c r="F256">
+        <v>2</v>
+      </c>
+      <c r="G256">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="H256">
+        <v>0</v>
+      </c>
+      <c r="I256">
         <v>5.4</v>
       </c>
-      <c r="G256" t="s">
+      <c r="J256" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="257" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="257" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A257">
         <v>268</v>
       </c>
@@ -7111,13 +9717,23 @@
         <v>1</v>
       </c>
       <c r="F257">
+        <v>2</v>
+      </c>
+      <c r="G257">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="H257">
+        <v>0</v>
+      </c>
+      <c r="I257">
         <v>6.2</v>
       </c>
-      <c r="G257" t="s">
+      <c r="J257" t="s">
         <v>336</v>
       </c>
     </row>
-    <row r="258" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="258" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A258">
         <v>269</v>
       </c>
@@ -7134,13 +9750,23 @@
         <v>1</v>
       </c>
       <c r="F258">
+        <v>2</v>
+      </c>
+      <c r="G258">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="H258">
+        <v>0</v>
+      </c>
+      <c r="I258">
         <v>6.2</v>
       </c>
-      <c r="G258" t="s">
+      <c r="J258" t="s">
         <v>336</v>
       </c>
     </row>
-    <row r="259" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="259" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A259">
         <v>270</v>
       </c>
@@ -7157,13 +9783,23 @@
         <v>1</v>
       </c>
       <c r="F259">
+        <v>2</v>
+      </c>
+      <c r="G259">
+        <f t="shared" ref="G259:G283" si="6">F259-H259</f>
+        <v>2</v>
+      </c>
+      <c r="H259">
+        <v>0</v>
+      </c>
+      <c r="I259">
         <v>6.2</v>
       </c>
-      <c r="G259" t="s">
+      <c r="J259" t="s">
         <v>336</v>
       </c>
     </row>
-    <row r="260" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="260" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A260">
         <v>271</v>
       </c>
@@ -7180,13 +9816,23 @@
         <v>1</v>
       </c>
       <c r="F260">
+        <v>2</v>
+      </c>
+      <c r="G260">
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="H260">
+        <v>0</v>
+      </c>
+      <c r="I260">
         <v>6.2</v>
       </c>
-      <c r="G260" t="s">
+      <c r="J260" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="261" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="261" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A261">
         <v>272</v>
       </c>
@@ -7203,13 +9849,23 @@
         <v>1</v>
       </c>
       <c r="F261">
+        <v>2</v>
+      </c>
+      <c r="G261">
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="H261">
+        <v>0</v>
+      </c>
+      <c r="I261">
         <v>6.2</v>
       </c>
-      <c r="G261" t="s">
+      <c r="J261" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="262" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="262" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A262">
         <v>273</v>
       </c>
@@ -7226,13 +9882,23 @@
         <v>1</v>
       </c>
       <c r="F262">
+        <v>2</v>
+      </c>
+      <c r="G262">
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="H262">
+        <v>0</v>
+      </c>
+      <c r="I262">
         <v>6.2</v>
       </c>
-      <c r="G262" t="s">
+      <c r="J262" t="s">
         <v>336</v>
       </c>
     </row>
-    <row r="263" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="263" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A263">
         <v>274</v>
       </c>
@@ -7249,13 +9915,23 @@
         <v>1</v>
       </c>
       <c r="F263">
+        <v>2</v>
+      </c>
+      <c r="G263">
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="H263">
+        <v>0</v>
+      </c>
+      <c r="I263">
         <v>6.2</v>
       </c>
-      <c r="G263" t="s">
+      <c r="J263" t="s">
         <v>341</v>
       </c>
     </row>
-    <row r="264" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="264" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A264">
         <v>275</v>
       </c>
@@ -7272,13 +9948,23 @@
         <v>1</v>
       </c>
       <c r="F264">
+        <v>2</v>
+      </c>
+      <c r="G264">
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="H264">
+        <v>0</v>
+      </c>
+      <c r="I264">
         <v>6.2</v>
       </c>
-      <c r="G264" t="s">
+      <c r="J264" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="265" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="265" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A265">
         <v>223</v>
       </c>
@@ -7295,10 +9981,20 @@
         <v>1</v>
       </c>
       <c r="F265">
+        <v>2</v>
+      </c>
+      <c r="G265">
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="H265">
+        <v>0</v>
+      </c>
+      <c r="I265">
         <v>5.4</v>
       </c>
     </row>
-    <row r="266" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="266" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A266">
         <v>251</v>
       </c>
@@ -7315,13 +10011,23 @@
         <v>1</v>
       </c>
       <c r="F266">
+        <v>2</v>
+      </c>
+      <c r="G266">
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="H266">
+        <v>0</v>
+      </c>
+      <c r="I266">
         <v>6.1</v>
       </c>
-      <c r="G266" t="s">
+      <c r="J266" t="s">
         <v>338</v>
       </c>
     </row>
-    <row r="267" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="267" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A267">
         <v>252</v>
       </c>
@@ -7338,13 +10044,23 @@
         <v>1</v>
       </c>
       <c r="F267">
+        <v>2</v>
+      </c>
+      <c r="G267">
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="H267">
+        <v>0</v>
+      </c>
+      <c r="I267">
         <v>6.1</v>
       </c>
-      <c r="G267" t="s">
+      <c r="J267" t="s">
         <v>338</v>
       </c>
     </row>
-    <row r="268" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="268" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A268">
         <v>254</v>
       </c>
@@ -7361,10 +10077,20 @@
         <v>1</v>
       </c>
       <c r="F268">
+        <v>2</v>
+      </c>
+      <c r="G268">
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="H268">
+        <v>0</v>
+      </c>
+      <c r="I268">
         <v>6.1</v>
       </c>
     </row>
-    <row r="269" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="269" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A269">
         <v>69</v>
       </c>
@@ -7381,13 +10107,23 @@
         <v>1</v>
       </c>
       <c r="F269">
+        <v>2</v>
+      </c>
+      <c r="G269">
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="H269">
+        <v>0</v>
+      </c>
+      <c r="I269">
         <v>1.6</v>
       </c>
-      <c r="G269" t="s">
+      <c r="J269" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="270" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="270" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A270">
         <v>256</v>
       </c>
@@ -7404,13 +10140,23 @@
         <v>1</v>
       </c>
       <c r="F270">
+        <v>2</v>
+      </c>
+      <c r="G270">
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="H270">
+        <v>0</v>
+      </c>
+      <c r="I270">
         <v>6.1</v>
       </c>
-      <c r="G270" t="s">
+      <c r="J270" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="271" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="271" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A271">
         <v>227</v>
       </c>
@@ -7427,13 +10173,23 @@
         <v>1</v>
       </c>
       <c r="F271">
+        <v>2</v>
+      </c>
+      <c r="G271">
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="H271">
+        <v>0</v>
+      </c>
+      <c r="I271">
         <v>5.4</v>
       </c>
-      <c r="G271" t="s">
+      <c r="J271" t="s">
         <v>336</v>
       </c>
     </row>
-    <row r="272" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="272" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A272">
         <v>197</v>
       </c>
@@ -7450,13 +10206,23 @@
         <v>1</v>
       </c>
       <c r="F272">
+        <v>3</v>
+      </c>
+      <c r="G272">
+        <f t="shared" si="6"/>
+        <v>3</v>
+      </c>
+      <c r="H272">
+        <v>0</v>
+      </c>
+      <c r="I272">
         <v>5.2</v>
       </c>
-      <c r="G272" t="s">
+      <c r="J272" t="s">
         <v>279</v>
       </c>
     </row>
-    <row r="273" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="273" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A273">
         <v>198</v>
       </c>
@@ -7473,13 +10239,23 @@
         <v>1</v>
       </c>
       <c r="F273">
+        <v>3</v>
+      </c>
+      <c r="G273">
+        <f t="shared" si="6"/>
+        <v>3</v>
+      </c>
+      <c r="H273">
+        <v>0</v>
+      </c>
+      <c r="I273">
         <v>5.2</v>
       </c>
-      <c r="G273" t="s">
+      <c r="J273" t="s">
         <v>279</v>
       </c>
     </row>
-    <row r="274" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="274" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A274">
         <v>205</v>
       </c>
@@ -7490,13 +10266,23 @@
         <v>1</v>
       </c>
       <c r="F274">
+        <v>3</v>
+      </c>
+      <c r="G274">
+        <f t="shared" si="6"/>
+        <v>3</v>
+      </c>
+      <c r="H274">
+        <v>0</v>
+      </c>
+      <c r="I274">
         <v>5.2</v>
       </c>
-      <c r="G274" t="s">
+      <c r="J274" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="275" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="275" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A275">
         <v>57</v>
       </c>
@@ -7513,13 +10299,23 @@
         <v>1</v>
       </c>
       <c r="F275">
+        <v>2</v>
+      </c>
+      <c r="G275">
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="H275">
+        <v>0</v>
+      </c>
+      <c r="I275">
         <v>1.5</v>
       </c>
-      <c r="G275" t="s">
+      <c r="J275" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="276" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="276" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A276">
         <v>41</v>
       </c>
@@ -7536,13 +10332,23 @@
         <v>1</v>
       </c>
       <c r="F276">
+        <v>2</v>
+      </c>
+      <c r="G276">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="H276">
+        <v>2</v>
+      </c>
+      <c r="I276">
         <v>1.4</v>
       </c>
-      <c r="G276" t="s">
+      <c r="J276" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="277" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="277" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A277">
         <v>255</v>
       </c>
@@ -7559,10 +10365,20 @@
         <v>1</v>
       </c>
       <c r="F277">
+        <v>2</v>
+      </c>
+      <c r="G277">
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="H277">
+        <v>0</v>
+      </c>
+      <c r="I277">
         <v>6.1</v>
       </c>
     </row>
-    <row r="278" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="278" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A278">
         <v>80</v>
       </c>
@@ -7579,10 +10395,20 @@
         <v>1</v>
       </c>
       <c r="F278">
+        <v>2</v>
+      </c>
+      <c r="G278">
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="H278">
+        <v>0</v>
+      </c>
+      <c r="I278">
         <v>2.1</v>
       </c>
     </row>
-    <row r="279" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="279" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A279">
         <v>81</v>
       </c>
@@ -7599,11 +10425,21 @@
         <v>1</v>
       </c>
       <c r="F279">
+        <v>2</v>
+      </c>
+      <c r="G279">
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="H279">
+        <v>0</v>
+      </c>
+      <c r="I279">
         <v>2.1</v>
       </c>
-      <c r="G279" s="1"/>
-    </row>
-    <row r="280" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="J279" s="1"/>
+    </row>
+    <row r="280" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A280">
         <v>276</v>
       </c>
@@ -7614,13 +10450,23 @@
         <v>1</v>
       </c>
       <c r="F280">
+        <v>6</v>
+      </c>
+      <c r="G280">
+        <f t="shared" si="6"/>
+        <v>6</v>
+      </c>
+      <c r="H280">
+        <v>0</v>
+      </c>
+      <c r="I280">
         <v>6.2</v>
       </c>
-      <c r="G280" t="s">
+      <c r="J280" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="281" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="281" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A281">
         <v>32</v>
       </c>
@@ -7637,13 +10483,23 @@
         <v>1</v>
       </c>
       <c r="F281">
+        <v>2</v>
+      </c>
+      <c r="G281">
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="H281">
+        <v>0</v>
+      </c>
+      <c r="I281">
         <v>1.4</v>
       </c>
-      <c r="G281" t="s">
+      <c r="J281" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="282" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="282" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A282">
         <v>9</v>
       </c>
@@ -7660,13 +10516,23 @@
         <v>1</v>
       </c>
       <c r="F282">
+        <v>2</v>
+      </c>
+      <c r="G282">
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="H282">
+        <v>0</v>
+      </c>
+      <c r="I282">
         <v>1.1000000000000001</v>
       </c>
-      <c r="G282" t="s">
+      <c r="J282" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="283" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="283" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A283">
         <v>164</v>
       </c>
@@ -7683,16 +10549,37 @@
         <v>1</v>
       </c>
       <c r="F283">
+        <v>2</v>
+      </c>
+      <c r="G283">
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="H283">
+        <v>0</v>
+      </c>
+      <c r="I283">
         <v>4.2</v>
       </c>
-      <c r="G283" t="s">
+      <c r="J283" t="s">
         <v>321</v>
       </c>
     </row>
+    <row r="284" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="F284">
+        <f>SUM(F2:F283)</f>
+        <v>2570</v>
+      </c>
+      <c r="G284">
+        <f>SUM(G2:G283)</f>
+        <v>2124</v>
+      </c>
+      <c r="H284">
+        <f>SUM(H2:H283)</f>
+        <v>446</v>
+      </c>
+    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="I1:J285">
-    <sortCondition ref="I1:I285"/>
-  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>

--- a/sch/components.xlsx
+++ b/sch/components.xlsx
@@ -1,20 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26529"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26626"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\miha\Desktop\vezje-idp\kicad\sch\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14C65A4B-2133-462B-A69A-AB3DCDD4AC7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAD4939F-83AF-4359-B689-B441FACF56B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12552" xr2:uid="{6172FD7F-16CD-47D1-A3E4-D63AC8EC044E}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12552" tabRatio="773" xr2:uid="{6172FD7F-16CD-47D1-A3E4-D63AC8EC044E}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="BOM" sheetId="1" r:id="rId1"/>
+    <sheet name="BOM-E-socket" sheetId="2" r:id="rId2"/>
+    <sheet name="BOM-E" sheetId="3" r:id="rId3"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">BOM!$A$1:$K$285</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'BOM-E'!$A$1:$E$244</definedName>
+  </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -25,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="932" uniqueCount="431">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1411" uniqueCount="499">
   <si>
     <t>ID</t>
   </si>
@@ -1011,9 +1017,6 @@
     <t>WD2143-PD 03-15 8706</t>
   </si>
   <si>
-    <t>100 Ω   ±5%</t>
-  </si>
-  <si>
     <t>SN74LS629N</t>
   </si>
   <si>
@@ -1218,9 +1221,6 @@
     <t>150R</t>
   </si>
   <si>
-    <t>LS157</t>
-  </si>
-  <si>
     <t>WD2143-01</t>
   </si>
   <si>
@@ -1239,9 +1239,6 @@
     <t>Z80 PIO (MK 3881)</t>
   </si>
   <si>
-    <t>2n 2 (?)</t>
-  </si>
-  <si>
     <t>390p</t>
   </si>
   <si>
@@ -1260,15 +1257,9 @@
     <t>330p</t>
   </si>
   <si>
-    <t>580n</t>
-  </si>
-  <si>
     <t>1n</t>
   </si>
   <si>
-    <t>10n/10p</t>
-  </si>
-  <si>
     <t>S42</t>
   </si>
   <si>
@@ -1293,21 +1284,12 @@
     <t>Z80 CTC</t>
   </si>
   <si>
-    <t>LS74 / S74</t>
-  </si>
-  <si>
     <t>Notes</t>
   </si>
   <si>
-    <t>Read as black-brown-red. Most likely it is green-brown-red (5K1).</t>
-  </si>
-  <si>
     <t>"E75" (pg. 7)</t>
   </si>
   <si>
-    <t>Value Ref3</t>
-  </si>
-  <si>
     <t>MM2716Q (EPROM)</t>
   </si>
   <si>
@@ -1318,13 +1300,271 @@
   </si>
   <si>
     <t>Square</t>
+  </si>
+  <si>
+    <t>Shop Link</t>
+  </si>
+  <si>
+    <t>https://www.ic-elect.si/ic-74ls374-dip20-flip-flop.html</t>
+  </si>
+  <si>
+    <t>Value Ref 1</t>
+  </si>
+  <si>
+    <t>https://eu.mouser.com/ProductDetail/Texas-Instruments/MC1488N?qs=d9gICRQKuCe4lrnGH3C7Bw%3D%3D</t>
+  </si>
+  <si>
+    <t>https://eu.mouser.com/ProductDetail/Texas-Instruments/MC1489N?qs=d9gICRQKuCdR4s3XhRyFEA%3D%3D</t>
+  </si>
+  <si>
+    <t>https://www.ebay.com/itm/314070811690
+https://www.ebay.com/itm/274950633485</t>
+  </si>
+  <si>
+    <t>https://www.ebay.com/itm/274950610514 (2 pcs)
+https://www.ebay.com/itm/325153953504</t>
+  </si>
+  <si>
+    <t>https://www.ebay.com/itm/172256511559</t>
+  </si>
+  <si>
+    <t>Pcs</t>
+  </si>
+  <si>
+    <t>https://www.ebay.com/itm/354428927179</t>
+  </si>
+  <si>
+    <t>EPROM</t>
+  </si>
+  <si>
+    <t>https://www.ebay.com/itm/325753393829</t>
+  </si>
+  <si>
+    <t>https://eu.mouser.com/ProductDetail/Texas-Instruments/SN74LS04N?qs=spW5eSrOWB4DgGWIHPxzvg%3D%3D
+https://www.ic-elect.si/ic-74ls04-dip14-inverter.html</t>
+  </si>
+  <si>
+    <t>https://eu.mouser.com/ProductDetail/Texas-Instruments/SN74LS05N?qs=spW5eSrOWB5U2y5XHWmnjA%3D%3D
+https://www.ic-elect.si/ic-74ls05-dip14-inverter-pbfree.html</t>
+  </si>
+  <si>
+    <t>https://eu.mouser.com/ProductDetail/Texas-Instruments/SN74LS08N?qs=spW5eSrOWB4y5MjcKVGhlA%3D%3D
+https://www.ic-elect.si/ic-74ls08-dip14-and-gate.html</t>
+  </si>
+  <si>
+    <t>https://eu.mouser.com/ProductDetail/Texas-Instruments/SN74LS10N?qs=sGAEpiMZZMutXGli8Ay4kBELecaPbA6BixFJp4A71TE%3D
+https://www.ic-elect.si/ic-74ls10-dip14-nand-gate.html</t>
+  </si>
+  <si>
+    <t>https://eu.mouser.com/ProductDetail/Texas-Instruments/SN74LS123N?qs=aZHVzqKrScD3CF1KN0ae4Q%3D%3D
+https://www.ic-elect.si/ic-74ls123-dip16-multivibrator.html</t>
+  </si>
+  <si>
+    <t>https://eu.mouser.com/ProductDetail/Texas-Instruments/SN74LS132N?qs=SL3LIuy2dWwicVI9J1F0sw%3D%3D
+https://www.ic-elect.si/ic-74ls132-dip14-schmitt-trigger.html</t>
+  </si>
+  <si>
+    <t>https://eu.mouser.com/ProductDetail/Texas-Instruments/SN74LS138N?qs=j01uVdFEFjG9iU5k7BL8mw%3D%3D
+https://www.ic-elect.si/ic-74ls138-dip16-decoder-demux.html</t>
+  </si>
+  <si>
+    <t>https://eu.mouser.com/ProductDetail/Texas-Instruments/SN74LS14N?qs=sGAEpiMZZMutXGli8Ay4kBELecaPbA6Baz7mo8DTZQo%3D
+https://www.ic-elect.si/ic-74ls14-dip14-schmitt-trigger.html</t>
+  </si>
+  <si>
+    <t>https://eu.mouser.com/ProductDetail/Texas-Instruments/SN74LS157N?qs=LzFo6vGRJ4stINDkpW5nIA%3D%3D
+https://www.ic-elect.si/ic-74ls157-dip16-multiplexer.html</t>
+  </si>
+  <si>
+    <t>https://eu.mouser.com/ProductDetail/Texas-Instruments/SN74LS20N?qs=EIjG%252BN7kn%252BksyasuSGdb8A%3D%3D
+https://www.ic-elect.si/ic-74ls20-dip14-nand-gate-35085.html</t>
+  </si>
+  <si>
+    <t>https://eu.mouser.com/ProductDetail/Texas-Instruments/SN74LS244N?qs=5WY7Uqh921ypecHduhX%252BiA%3D%3D
+https://www.ic-elect.si/ic-74ls244-so20w-driver.html</t>
+  </si>
+  <si>
+    <t>https://eu.mouser.com/ProductDetail/Texas-Instruments/SN74LS27N?qs=sGAEpiMZZMutXGli8Ay4kP28D9wZ8SQIwsPDjIqEADE%3D
+https://www.ic-elect.si/ic-74ls27-dip14-nor-gate.html</t>
+  </si>
+  <si>
+    <t>https://eu.mouser.com/ProductDetail/Texas-Instruments/SN74LS30N?qs=q2XTDbzbm6Bq0XyTd941gw%3D%3D
+https://www.ic-elect.si/ic-74ls30-dip14-nand-gate.html</t>
+  </si>
+  <si>
+    <t>https://eu.mouser.com/ProductDetail/Texas-Instruments/SN74LS32N?qs=q2XTDbzbm6DA9Mnew5GiLA%3D%3D
+https://www.ic-elect.si/ic-74ls32-dip14-or-gate.html</t>
+  </si>
+  <si>
+    <t>https://eu.mouser.com/ProductDetail/Texas-Instruments/SN74LS367AN?qs=SL3LIuy2dWytJLO3%252BW%2Fdvw%3D%3D
+https://www.ic-elect.si/ic-74ls367-dip16-buffer.html</t>
+  </si>
+  <si>
+    <t>https://eu.mouser.com/ProductDetail/Texas-Instruments/SN74LS38N?qs=q2XTDbzbm6CPeB2W6c2jlg%3D%3D
+https://www.ic-elect.si/ic-74ls38-dip14-nand-buffer.html</t>
+  </si>
+  <si>
+    <t>https://eu.mouser.com/ProductDetail/Texas-Instruments/SN74LS393N?qs=Tv815z3GeNTnF1V0GiYITA%3D%3D
+https://www.ic-elect.si/ic-74ls393-dip14-counter.html</t>
+  </si>
+  <si>
+    <t>https://eu.mouser.com/ProductDetail/Texas-Instruments/SN74LS42N?qs=sGAEpiMZZMutXGli8Ay4kHCkCpxTtxgl92ZLS6s4WlY%3D
+https://www.ic-elect.si/ic-74ls42-dip14-decoder.html</t>
+  </si>
+  <si>
+    <t>https://eu.mouser.com/ProductDetail/Texas-Instruments/SN74LS629N?qs=gb35HGp1gQJuZd938Z1iQA%3D%3D
+https://www.ic-elect.si/ic-74ls629-dip16-micsellaneous.html</t>
+  </si>
+  <si>
+    <t>https://eu.mouser.com/ProductDetail/Texas-Instruments/SN74LS74AN?qs=b0gIXGU74fP41yYZQO4%252BKQ%3D%3D
+https://www.ic-elect.si/ic-74ls74-dip14-flip-flop.html</t>
+  </si>
+  <si>
+    <t>https://eu.mouser.com/ProductDetail/Texas-Instruments/SN74LS86AN?qs=mTHRaKC2c7P%2FJtp1i2FCFw%3D%3D
+https://www.ic-elect.si/ic-74ls86-dip14-exor-gate.html</t>
+  </si>
+  <si>
+    <t>74S04 https://eu.mouser.com/ProductDetail/Texas-Instruments/SN74S04N?qs=KaAwwOlwapsheoMb2c1Auw%3D%3D</t>
+  </si>
+  <si>
+    <t>https://www.ebay.com/itm/295313210497</t>
+  </si>
+  <si>
+    <t>https://www.ebay.com/itm/354522453659</t>
+  </si>
+  <si>
+    <t>https://www.ebay.com/itm/311081941531</t>
+  </si>
+  <si>
+    <t>CPU</t>
+  </si>
+  <si>
+    <t>https://www.ebay.com/itm/281532121730</t>
+  </si>
+  <si>
+    <t>https://www.ebay.com/itm/281536070161 (2 pcs)</t>
+  </si>
+  <si>
+    <t>Socket Count</t>
+  </si>
+  <si>
+    <t>https://eu.mouser.com/ProductDetail/TE-Connectivity/1-2199298-4?qs=fK8dlpkaUMvpL10rY9Abiw%3D%3D
+https://www.ic-elect.si/podnozje-16-pin-prof.html</t>
+  </si>
+  <si>
+    <t>https://eu.mouser.com/ProductDetail/TE-Connectivity/1-2199298-5?qs=sGAEpiMZZMvlX3nhDDO4AFokPzkb3saqAYzerZM2mv0%3D
+https://www.ic-elect.si/podnozje-18-pin-prof-pak-26kos.html</t>
+  </si>
+  <si>
+    <t>https://eu.mouser.com/ProductDetail/TE-Connectivity/1-2199298-6?qs=fK8dlpkaUMvuMXpJTs4GlA%3D%3D
+https://www.ic-elect.si/podnozje-20-pin-prof-pak-24kos.html</t>
+  </si>
+  <si>
+    <t>https://eu.mouser.com/ProductDetail/TE-Connectivity/1-2199298-8?qs=fK8dlpkaUMsSY7Gqcrol0Q%3D%3D
+https://www.ic-elect.si/podnozje-24-pin-prof-pak-20kos.html</t>
+  </si>
+  <si>
+    <t>https://eu.mouser.com/ProductDetail/TE-Connectivity/1-2199299-2?qs=fK8dlpkaUMsXyJ%2FBqcw4Fg%3D%3D
+https://www.ic-elect.si/podnozje-28-pin-prof-pak-17kos.html</t>
+  </si>
+  <si>
+    <t>https://eu.mouser.com/ProductDetail/TE-Connectivity/1-2199299-5?qs=fK8dlpkaUMthXjoyadQV1Q%3D%3D
+https://www.ic-elect.si/podnozje-40-pin-prof-pak-12kos.html</t>
+  </si>
+  <si>
+    <t>https://eu.mouser.com/ProductDetail/TE-Connectivity/1-2199298-3?qs=fK8dlpkaUMtBOtVI99wRlQ%3D%3D
+https://www.ic-elect.si/podnozje-14-pin-prof-pak-34kos.html</t>
+  </si>
+  <si>
+    <t>68 Ω   ±5%</t>
+  </si>
+  <si>
+    <t>68 uF 25 V</t>
+  </si>
+  <si>
+    <t>100 uF 40 V</t>
+  </si>
+  <si>
+    <t>VARTA SafeTronic 3.6 V</t>
+  </si>
+  <si>
+    <t>2n2</t>
+  </si>
+  <si>
+    <t>380K Y5P / 390K Y5P</t>
+  </si>
+  <si>
+    <t>390K Y5P</t>
+  </si>
+  <si>
+    <t>684 100V</t>
+  </si>
+  <si>
+    <t>1n0</t>
+  </si>
+  <si>
+    <t>68uF 25V</t>
+  </si>
+  <si>
+    <t>BA 513</t>
+  </si>
+  <si>
+    <t>POT</t>
+  </si>
+  <si>
+    <t>4.7 kΩ   ±5% </t>
+  </si>
+  <si>
+    <t>150 Ω   ±5%</t>
+  </si>
+  <si>
+    <t>390 Ω   ±5%</t>
+  </si>
+  <si>
+    <t>560 Ω   ±5%</t>
+  </si>
+  <si>
+    <t>BZX 2,7</t>
+  </si>
+  <si>
+    <t>Zener diode</t>
+  </si>
+  <si>
+    <t>Blue resistor (tolerance less than 1%)</t>
+  </si>
+  <si>
+    <t>Measured at 9K/43K 52K (Ref 3)</t>
+  </si>
+  <si>
+    <t>Measured at 16K/31K 51K (Ref 3). First value between 1 and 2, second between 2 and 3.</t>
+  </si>
+  <si>
+    <t>Most likely 680 nF.</t>
+  </si>
+  <si>
+    <t>C7 should be read from the board, not from the schema.</t>
+  </si>
+  <si>
+    <t>10n / 10p (?)</t>
+  </si>
+  <si>
+    <t>580n (680n?)</t>
+  </si>
+  <si>
+    <t>5K1   ±5%</t>
+  </si>
+  <si>
+    <t>56 Ω   ±5%</t>
+  </si>
+  <si>
+    <t>220 Ω   ±5%</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1341,6 +1581,14 @@
     </font>
     <font>
       <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1363,10 +1611,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1374,8 +1623,19 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1688,40 +1948,40 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A507EC0B-FECA-46C5-861D-53A4B99CDA9D}">
-  <dimension ref="A1:L284"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:K284"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="3" max="3" width="15.83984375" customWidth="1"/>
     <col min="4" max="4" width="15.5234375" style="2" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="31.3125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="16.15625" customWidth="1"/>
-    <col min="12" max="12" width="53.9453125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="70.3671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
+        <v>342</v>
+      </c>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
         <v>343</v>
       </c>
-      <c r="B1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" t="s">
+      <c r="D1" s="2" t="s">
         <v>344</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>345</v>
-      </c>
       <c r="E1" t="s">
         <v>2</v>
       </c>
       <c r="F1" t="s">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="G1" t="s">
-        <v>429</v>
+        <v>421</v>
       </c>
       <c r="H1" t="s">
-        <v>430</v>
+        <v>422</v>
       </c>
       <c r="I1" t="s">
         <v>1</v>
@@ -1730,13 +1990,10 @@
         <v>125</v>
       </c>
       <c r="K1" t="s">
-        <v>426</v>
-      </c>
-      <c r="L1" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A2">
         <v>79</v>
       </c>
@@ -1747,7 +2004,7 @@
         <v>77</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -1756,7 +2013,7 @@
         <v>3</v>
       </c>
       <c r="G2">
-        <f>F2-H2</f>
+        <f t="shared" ref="G2:G65" si="0">F2-H2</f>
         <v>3</v>
       </c>
       <c r="H2">
@@ -1765,8 +2022,11 @@
       <c r="I2">
         <v>2.1</v>
       </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="J2" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A3">
         <v>71</v>
       </c>
@@ -1780,7 +2040,7 @@
         <v>2</v>
       </c>
       <c r="G3">
-        <f t="shared" ref="G3:G66" si="0">F3-H3</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="H3">
@@ -1789,8 +2049,11 @@
       <c r="I3">
         <v>1.6</v>
       </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="J3" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A4">
         <v>96</v>
       </c>
@@ -1817,7 +2080,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:11" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A5">
         <v>104</v>
       </c>
@@ -1844,7 +2107,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:11" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A6">
         <v>199</v>
       </c>
@@ -1871,7 +2134,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A7">
         <v>121</v>
       </c>
@@ -1882,7 +2145,7 @@
         <v>118</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>404</v>
+        <v>475</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -1900,8 +2163,11 @@
       <c r="I7">
         <v>2.4</v>
       </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="J7" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A8">
         <v>75</v>
       </c>
@@ -1912,7 +2178,7 @@
         <v>73</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -1930,8 +2196,11 @@
       <c r="I8">
         <v>2.1</v>
       </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="J8" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A9">
         <v>97</v>
       </c>
@@ -1958,7 +2227,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A10">
         <v>83</v>
       </c>
@@ -1969,7 +2238,7 @@
         <v>81</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="E10">
         <v>1</v>
@@ -1987,8 +2256,11 @@
       <c r="I10">
         <v>2.1</v>
       </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="J10" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A11">
         <v>98</v>
       </c>
@@ -2015,7 +2287,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:11" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A12">
         <v>99</v>
       </c>
@@ -2042,7 +2314,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:11" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A13">
         <v>100</v>
       </c>
@@ -2069,7 +2341,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:11" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A14">
         <v>101</v>
       </c>
@@ -2096,7 +2368,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:11" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A15">
         <v>102</v>
       </c>
@@ -2123,7 +2395,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A16">
         <v>174</v>
       </c>
@@ -2134,7 +2406,7 @@
         <v>168</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="E16">
         <v>1</v>
@@ -2152,8 +2424,11 @@
       <c r="I16">
         <v>4.2</v>
       </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="J16" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A17">
         <v>175</v>
       </c>
@@ -2164,7 +2439,7 @@
         <v>169</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="E17">
         <v>1</v>
@@ -2182,8 +2457,11 @@
       <c r="I17">
         <v>4.2</v>
       </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="J17" s="2" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A18">
         <v>203</v>
       </c>
@@ -2210,7 +2488,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A19">
         <v>72</v>
       </c>
@@ -2233,8 +2511,11 @@
       <c r="I19">
         <v>1.6</v>
       </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="J19" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A20">
         <v>250</v>
       </c>
@@ -2245,7 +2526,7 @@
         <v>239</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="E20">
         <v>1</v>
@@ -2263,8 +2544,11 @@
       <c r="I20">
         <v>6.1</v>
       </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="J20" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A21">
         <v>10</v>
       </c>
@@ -2275,7 +2559,7 @@
         <v>12</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="E21">
         <v>1</v>
@@ -2297,7 +2581,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A22">
         <v>11</v>
       </c>
@@ -2308,7 +2592,7 @@
         <v>13</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="E22">
         <v>1</v>
@@ -2330,7 +2614,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A23">
         <v>61</v>
       </c>
@@ -2353,8 +2637,11 @@
       <c r="I23">
         <v>1.6</v>
       </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="J23" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A24">
         <v>8</v>
       </c>
@@ -2365,7 +2652,7 @@
         <v>10</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="E24">
         <v>1</v>
@@ -2387,7 +2674,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A25">
         <v>253</v>
       </c>
@@ -2397,8 +2684,8 @@
       <c r="C25" t="s">
         <v>242</v>
       </c>
-      <c r="D25" s="2" t="s">
-        <v>411</v>
+      <c r="D25" s="10" t="s">
+        <v>495</v>
       </c>
       <c r="E25">
         <v>1</v>
@@ -2416,8 +2703,14 @@
       <c r="I25">
         <v>6.1</v>
       </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="J25" t="s">
+        <v>478</v>
+      </c>
+      <c r="K25" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A26">
         <v>62</v>
       </c>
@@ -2440,8 +2733,11 @@
       <c r="I26">
         <v>1.6</v>
       </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="J26" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A27">
         <v>52</v>
       </c>
@@ -2452,7 +2748,7 @@
         <v>51</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="E27">
         <v>1</v>
@@ -2470,8 +2766,11 @@
       <c r="I27">
         <v>1.5</v>
       </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="J27" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A28">
         <v>37</v>
       </c>
@@ -2482,7 +2781,7 @@
         <v>40</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="E28">
         <v>1</v>
@@ -2500,8 +2799,11 @@
       <c r="I28">
         <v>1.4</v>
       </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="J28" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A29">
         <v>34</v>
       </c>
@@ -2511,8 +2813,8 @@
       <c r="C29" t="s">
         <v>38</v>
       </c>
-      <c r="D29" s="2" t="s">
-        <v>413</v>
+      <c r="D29" s="10" t="s">
+        <v>494</v>
       </c>
       <c r="E29">
         <v>1</v>
@@ -2530,8 +2832,14 @@
       <c r="I29">
         <v>1.4</v>
       </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="J29" t="s">
+        <v>475</v>
+      </c>
+      <c r="K29" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A30">
         <v>35</v>
       </c>
@@ -2542,7 +2850,7 @@
         <v>39</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="E30">
         <v>1</v>
@@ -2560,8 +2868,11 @@
       <c r="I30">
         <v>1.4</v>
       </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="J30" s="2" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A31">
         <v>95</v>
       </c>
@@ -2588,29 +2899,29 @@
         <v>286</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A32">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="E32">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F32">
-        <f>E32*2</f>
-        <v>8</v>
+        <f t="shared" ref="F32:F47" si="1">E32*2</f>
+        <v>2</v>
       </c>
       <c r="G32">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H32">
         <v>0</v>
       </c>
       <c r="I32">
-        <v>1.1000000000000001</v>
+        <v>1.3</v>
       </c>
       <c r="J32" t="s">
         <v>283</v>
@@ -2618,27 +2929,27 @@
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A33">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="E33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F33">
-        <f t="shared" ref="F33:F47" si="1">E33*2</f>
-        <v>4</v>
+        <f t="shared" si="1"/>
+        <v>2</v>
       </c>
       <c r="G33">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H33">
         <v>0</v>
       </c>
       <c r="I33">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J33" t="s">
         <v>283</v>
@@ -2646,7 +2957,7 @@
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A34">
-        <v>24</v>
+        <v>108</v>
       </c>
       <c r="B34" s="3" t="s">
         <v>3</v>
@@ -2666,7 +2977,7 @@
         <v>0</v>
       </c>
       <c r="I34">
-        <v>1.3</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="J34" t="s">
         <v>283</v>
@@ -2674,7 +2985,7 @@
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A35">
-        <v>48</v>
+        <v>213</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>3</v>
@@ -2694,7 +3005,7 @@
         <v>0</v>
       </c>
       <c r="I35">
-        <v>1.4</v>
+        <v>5.3</v>
       </c>
       <c r="J35" t="s">
         <v>283</v>
@@ -2702,27 +3013,27 @@
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A36">
-        <v>74</v>
+        <v>221</v>
       </c>
       <c r="B36" s="3" t="s">
         <v>3</v>
       </c>
       <c r="E36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F36">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G36">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H36">
         <v>0</v>
       </c>
       <c r="I36">
-        <v>2.1</v>
+        <v>5.4</v>
       </c>
       <c r="J36" t="s">
         <v>283</v>
@@ -2730,7 +3041,7 @@
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A37">
-        <v>108</v>
+        <v>264</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>3</v>
@@ -2750,7 +3061,7 @@
         <v>0</v>
       </c>
       <c r="I37">
-        <v>2.2999999999999998</v>
+        <v>6.2</v>
       </c>
       <c r="J37" t="s">
         <v>283</v>
@@ -2758,27 +3069,27 @@
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A38">
-        <v>125</v>
+        <v>15</v>
       </c>
       <c r="B38" s="3" t="s">
         <v>3</v>
       </c>
       <c r="E38">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F38">
         <f t="shared" si="1"/>
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G38">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H38">
         <v>0</v>
       </c>
       <c r="I38">
-        <v>3.1</v>
+        <v>1.2</v>
       </c>
       <c r="J38" t="s">
         <v>283</v>
@@ -2786,7 +3097,7 @@
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A39">
-        <v>130</v>
+        <v>74</v>
       </c>
       <c r="B39" s="3" t="s">
         <v>3</v>
@@ -2806,7 +3117,7 @@
         <v>0</v>
       </c>
       <c r="I39">
-        <v>3.2</v>
+        <v>2.1</v>
       </c>
       <c r="J39" t="s">
         <v>283</v>
@@ -2814,27 +3125,27 @@
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A40">
-        <v>144</v>
+        <v>130</v>
       </c>
       <c r="B40" s="3" t="s">
         <v>3</v>
       </c>
       <c r="E40">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F40">
         <f t="shared" si="1"/>
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="G40">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="H40">
         <v>0</v>
       </c>
       <c r="I40">
-        <v>4.0999999999999996</v>
+        <v>3.2</v>
       </c>
       <c r="J40" t="s">
         <v>283</v>
@@ -2870,27 +3181,27 @@
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A42">
-        <v>186</v>
+        <v>248</v>
       </c>
       <c r="B42" s="3" t="s">
         <v>3</v>
       </c>
       <c r="E42">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F42">
         <f t="shared" si="1"/>
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G42">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H42">
         <v>0</v>
       </c>
       <c r="I42">
-        <v>5.0999999999999996</v>
+        <v>6.1</v>
       </c>
       <c r="J42" t="s">
         <v>283</v>
@@ -2898,27 +3209,27 @@
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A43">
-        <v>195</v>
+        <v>1</v>
       </c>
       <c r="B43" s="3" t="s">
         <v>3</v>
       </c>
       <c r="E43">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F43">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G43">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H43">
         <v>0</v>
       </c>
       <c r="I43">
-        <v>5.2</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="J43" t="s">
         <v>283</v>
@@ -2926,27 +3237,27 @@
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A44">
-        <v>213</v>
+        <v>125</v>
       </c>
       <c r="B44" s="3" t="s">
         <v>3</v>
       </c>
       <c r="E44">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F44">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G44">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H44">
         <v>0</v>
       </c>
       <c r="I44">
-        <v>5.3</v>
+        <v>3.1</v>
       </c>
       <c r="J44" t="s">
         <v>283</v>
@@ -2954,27 +3265,27 @@
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A45">
-        <v>221</v>
+        <v>186</v>
       </c>
       <c r="B45" s="3" t="s">
         <v>3</v>
       </c>
       <c r="E45">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F45">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G45">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H45">
         <v>0</v>
       </c>
       <c r="I45">
-        <v>5.4</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="J45" t="s">
         <v>283</v>
@@ -2982,27 +3293,27 @@
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A46">
-        <v>248</v>
+        <v>195</v>
       </c>
       <c r="B46" s="3" t="s">
         <v>3</v>
       </c>
       <c r="E46">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F46">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G46">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="H46">
         <v>0</v>
       </c>
       <c r="I46">
-        <v>6.1</v>
+        <v>5.2</v>
       </c>
       <c r="J46" t="s">
         <v>283</v>
@@ -3010,27 +3321,27 @@
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A47">
-        <v>264</v>
+        <v>144</v>
       </c>
       <c r="B47" s="3" t="s">
         <v>3</v>
       </c>
       <c r="E47">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F47">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="G47">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="H47">
         <v>0</v>
       </c>
       <c r="I47">
-        <v>6.2</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="J47" t="s">
         <v>283</v>
@@ -3047,7 +3358,7 @@
         <v>54</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="E48">
         <v>1</v>
@@ -3080,7 +3391,7 @@
         <v>6</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="E49">
         <v>1</v>
@@ -3179,7 +3490,7 @@
         <v>254</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="E52">
         <v>1</v>
@@ -3198,7 +3509,7 @@
         <v>6.2</v>
       </c>
       <c r="J52" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -3212,7 +3523,7 @@
         <v>247</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="E53">
         <v>1</v>
@@ -3245,7 +3556,7 @@
         <v>248</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="E54">
         <v>1</v>
@@ -3278,7 +3589,7 @@
         <v>249</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="E55">
         <v>1</v>
@@ -3297,7 +3608,7 @@
         <v>6.1</v>
       </c>
       <c r="J55" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -3311,7 +3622,7 @@
         <v>250</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="E56">
         <v>1</v>
@@ -3344,7 +3655,7 @@
         <v>251</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="E57">
         <v>1</v>
@@ -3377,7 +3688,7 @@
         <v>252</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E58">
         <v>1</v>
@@ -3396,7 +3707,7 @@
         <v>6.1</v>
       </c>
       <c r="J58" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -3410,7 +3721,7 @@
         <v>7</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="E59">
         <v>1</v>
@@ -3443,7 +3754,7 @@
         <v>57</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="E60">
         <v>1</v>
@@ -3476,7 +3787,7 @@
         <v>58</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="E61">
         <v>1</v>
@@ -3509,7 +3820,7 @@
         <v>49</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="E62">
         <v>1</v>
@@ -3542,7 +3853,7 @@
         <v>48</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="E63">
         <v>1</v>
@@ -3575,7 +3886,7 @@
         <v>29</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="E64">
         <v>1</v>
@@ -3608,7 +3919,7 @@
         <v>30</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="E65">
         <v>1</v>
@@ -3641,7 +3952,7 @@
         <v>31</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="E66">
         <v>1</v>
@@ -3650,7 +3961,7 @@
         <v>20</v>
       </c>
       <c r="G66">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="G66:G129" si="2">F66-H66</f>
         <v>19</v>
       </c>
       <c r="H66">
@@ -3674,7 +3985,7 @@
         <v>22</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="E67">
         <v>1</v>
@@ -3683,7 +3994,7 @@
         <v>20</v>
       </c>
       <c r="G67">
-        <f t="shared" ref="G67:G130" si="2">F67-H67</f>
+        <f t="shared" si="2"/>
         <v>19</v>
       </c>
       <c r="H67">
@@ -3707,7 +4018,7 @@
         <v>55</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="E68">
         <v>1</v>
@@ -3740,7 +4051,7 @@
         <v>23</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="E69">
         <v>1</v>
@@ -3773,7 +4084,7 @@
         <v>24</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="E70">
         <v>1</v>
@@ -3806,7 +4117,7 @@
         <v>8</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="E71">
         <v>1</v>
@@ -3839,7 +4150,7 @@
         <v>9</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E72">
         <v>1</v>
@@ -3872,7 +4183,7 @@
         <v>15</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E73">
         <v>1</v>
@@ -3905,7 +4216,7 @@
         <v>16</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="E74">
         <v>1</v>
@@ -3938,7 +4249,7 @@
         <v>120</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="E75">
         <v>1</v>
@@ -3971,7 +4282,7 @@
         <v>121</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="E76">
         <v>1</v>
@@ -4004,7 +4315,7 @@
         <v>119</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="E77">
         <v>1</v>
@@ -4037,7 +4348,7 @@
         <v>110</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="E78">
         <v>1</v>
@@ -4070,7 +4381,7 @@
         <v>41</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="E79">
         <v>1</v>
@@ -4103,7 +4414,7 @@
         <v>106</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="E80">
         <v>1</v>
@@ -4125,7 +4436,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="81" spans="1:10" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A81">
         <v>110</v>
       </c>
@@ -4136,7 +4447,7 @@
         <v>107</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="E81">
         <v>1</v>
@@ -4169,7 +4480,7 @@
         <v>108</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="E82">
         <v>1</v>
@@ -4202,7 +4513,7 @@
         <v>109</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="E83">
         <v>1</v>
@@ -4235,7 +4546,7 @@
         <v>92</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="E84">
         <v>1</v>
@@ -4268,7 +4579,7 @@
         <v>91</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="E85">
         <v>1</v>
@@ -4301,7 +4612,7 @@
         <v>74</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="E86">
         <v>1</v>
@@ -4334,7 +4645,7 @@
         <v>101</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="E87">
         <v>1</v>
@@ -4367,7 +4678,7 @@
         <v>75</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="E88">
         <v>1</v>
@@ -4400,7 +4711,7 @@
         <v>82</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="E89">
         <v>1</v>
@@ -4433,7 +4744,7 @@
         <v>25</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="E90">
         <v>1</v>
@@ -4466,7 +4777,7 @@
         <v>80</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="E91">
         <v>1</v>
@@ -4499,7 +4810,7 @@
         <v>76</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="E92">
         <v>1</v>
@@ -4532,7 +4843,7 @@
         <v>117</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="E93">
         <v>1</v>
@@ -4550,6 +4861,9 @@
       <c r="I93">
         <v>2.4</v>
       </c>
+      <c r="J93" t="s">
+        <v>300</v>
+      </c>
     </row>
     <row r="94" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A94">
@@ -4661,7 +4975,7 @@
         <v>132</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="E97">
         <v>1</v>
@@ -4694,7 +5008,7 @@
         <v>133</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E98">
         <v>1</v>
@@ -4727,7 +5041,7 @@
         <v>126</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="E99">
         <v>1</v>
@@ -4760,7 +5074,7 @@
         <v>122</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>397</v>
+        <v>390</v>
       </c>
       <c r="E100">
         <v>1</v>
@@ -4793,7 +5107,7 @@
         <v>26</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="E101">
         <v>1</v>
@@ -4815,7 +5129,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="102" spans="1:11" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A102">
         <v>127</v>
       </c>
@@ -4881,7 +5195,7 @@
         <v>279</v>
       </c>
       <c r="K103" t="s">
-        <v>427</v>
+        <v>419</v>
       </c>
     </row>
     <row r="104" spans="1:11" x14ac:dyDescent="0.55000000000000004">
@@ -4961,7 +5275,7 @@
         <v>129</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="E106">
         <v>1</v>
@@ -4994,7 +5308,7 @@
         <v>128</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="E107">
         <v>1</v>
@@ -5060,7 +5374,7 @@
         <v>166</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="E109">
         <v>1</v>
@@ -5093,7 +5407,7 @@
         <v>167</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="E110">
         <v>1</v>
@@ -5159,7 +5473,7 @@
         <v>27</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="E112">
         <v>1</v>
@@ -5280,7 +5594,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="116" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="116" spans="1:10" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A116">
         <v>183</v>
       </c>
@@ -5291,7 +5605,7 @@
         <v>177</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="E116">
         <v>1</v>
@@ -5324,7 +5638,7 @@
         <v>175</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="E117">
         <v>1</v>
@@ -5343,7 +5657,7 @@
         <v>4.3</v>
       </c>
       <c r="J117" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="118" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -5357,7 +5671,7 @@
         <v>161</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="E118">
         <v>1</v>
@@ -5390,7 +5704,7 @@
         <v>162</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="E119">
         <v>1</v>
@@ -5423,7 +5737,7 @@
         <v>163</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="E120">
         <v>1</v>
@@ -5456,7 +5770,7 @@
         <v>164</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="E121">
         <v>1</v>
@@ -5489,7 +5803,7 @@
         <v>165</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="E122">
         <v>1</v>
@@ -5522,7 +5836,7 @@
         <v>17</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="E123">
         <v>1</v>
@@ -5555,7 +5869,7 @@
         <v>171</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="E124">
         <v>1</v>
@@ -5574,7 +5888,7 @@
         <v>4.2</v>
       </c>
       <c r="J124" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="125" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -5709,7 +6023,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="129" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="129" spans="1:10" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A129">
         <v>228</v>
       </c>
@@ -5720,7 +6034,7 @@
         <v>218</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>417</v>
+        <v>412</v>
       </c>
       <c r="E129">
         <v>1</v>
@@ -5742,7 +6056,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="130" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="130" spans="1:10" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A130">
         <v>225</v>
       </c>
@@ -5753,7 +6067,7 @@
         <v>215</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="E130">
         <v>1</v>
@@ -5762,7 +6076,7 @@
         <v>16</v>
       </c>
       <c r="G130">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="G130:G193" si="3">F130-H130</f>
         <v>15</v>
       </c>
       <c r="H130">
@@ -5786,7 +6100,7 @@
         <v>205</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E131">
         <v>1</v>
@@ -5795,7 +6109,7 @@
         <v>14</v>
       </c>
       <c r="G131">
-        <f t="shared" ref="G131:G194" si="3">F131-H131</f>
+        <f t="shared" si="3"/>
         <v>13</v>
       </c>
       <c r="H131">
@@ -5805,7 +6119,7 @@
         <v>5.3</v>
       </c>
       <c r="J131" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="132" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -5819,7 +6133,7 @@
         <v>206</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="E132">
         <v>1</v>
@@ -5838,7 +6152,7 @@
         <v>5.3</v>
       </c>
       <c r="J132" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="133" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -5852,7 +6166,7 @@
         <v>207</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="E133">
         <v>1</v>
@@ -5885,7 +6199,7 @@
         <v>18</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="E134">
         <v>1</v>
@@ -5915,10 +6229,10 @@
         <v>208</v>
       </c>
       <c r="C135" t="s">
-        <v>425</v>
+        <v>418</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="E135">
         <v>1</v>
@@ -5951,7 +6265,7 @@
         <v>201</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="E136">
         <v>1</v>
@@ -5970,7 +6284,7 @@
         <v>5.2</v>
       </c>
       <c r="J136" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="137" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -5984,7 +6298,7 @@
         <v>199</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="E137">
         <v>1</v>
@@ -6017,7 +6331,7 @@
         <v>193</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>422</v>
+        <v>359</v>
       </c>
       <c r="E138">
         <v>1</v>
@@ -6050,7 +6364,7 @@
         <v>203</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E139">
         <v>1</v>
@@ -6069,7 +6383,7 @@
         <v>5.2</v>
       </c>
       <c r="J139" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="140" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -6204,7 +6518,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="144" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="144" spans="1:10" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A144">
         <v>229</v>
       </c>
@@ -6215,7 +6529,7 @@
         <v>219</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="E144">
         <v>1</v>
@@ -6248,7 +6562,7 @@
         <v>19</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="E145">
         <v>1</v>
@@ -6270,7 +6584,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="146" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="146" spans="1:10" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A146">
         <v>226</v>
       </c>
@@ -6281,7 +6595,7 @@
         <v>216</v>
       </c>
       <c r="D146" s="2" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="E146">
         <v>1</v>
@@ -6314,7 +6628,7 @@
         <v>209</v>
       </c>
       <c r="D147" s="2" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="E147">
         <v>1</v>
@@ -6347,7 +6661,7 @@
         <v>210</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="E148">
         <v>1</v>
@@ -6380,7 +6694,7 @@
         <v>211</v>
       </c>
       <c r="D149" s="2" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="E149">
         <v>1</v>
@@ -6413,7 +6727,7 @@
         <v>202</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="E150">
         <v>1</v>
@@ -6446,7 +6760,7 @@
         <v>200</v>
       </c>
       <c r="D151" s="2" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="E151">
         <v>1</v>
@@ -6465,7 +6779,7 @@
         <v>5.2</v>
       </c>
       <c r="J151" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="152" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -6479,7 +6793,7 @@
         <v>197</v>
       </c>
       <c r="D152" s="2" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E152">
         <v>1</v>
@@ -6498,7 +6812,7 @@
         <v>5.2</v>
       </c>
       <c r="J152" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="153" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -6512,7 +6826,7 @@
         <v>194</v>
       </c>
       <c r="D153" s="2" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="E153">
         <v>1</v>
@@ -6618,7 +6932,7 @@
         <v>0</v>
       </c>
       <c r="H156">
-        <f>F156</f>
+        <f t="shared" ref="H156:H180" si="4">F156</f>
         <v>34</v>
       </c>
       <c r="I156">
@@ -6646,7 +6960,7 @@
         <v>0</v>
       </c>
       <c r="H157">
-        <f t="shared" ref="H157:H180" si="4">F157</f>
+        <f t="shared" si="4"/>
         <v>64</v>
       </c>
       <c r="I157">
@@ -6684,7 +6998,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="159" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="159" spans="1:10" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A159">
         <v>70</v>
       </c>
@@ -6852,7 +7166,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="165" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="165" spans="1:10" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A165">
         <v>277</v>
       </c>
@@ -6908,7 +7222,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="167" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="167" spans="1:10" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A167">
         <v>257</v>
       </c>
@@ -6936,7 +7250,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="168" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="168" spans="1:10" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A168">
         <v>19</v>
       </c>
@@ -6992,7 +7306,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="170" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="170" spans="1:10" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A170">
         <v>224</v>
       </c>
@@ -7020,7 +7334,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="171" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="171" spans="1:10" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A171">
         <v>280</v>
       </c>
@@ -7048,7 +7362,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="172" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="172" spans="1:10" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A172">
         <v>279</v>
       </c>
@@ -7076,7 +7390,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="173" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="173" spans="1:10" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A173">
         <v>267</v>
       </c>
@@ -7104,7 +7418,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="174" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="174" spans="1:10" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A174">
         <v>222</v>
       </c>
@@ -7132,7 +7446,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="175" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="175" spans="1:10" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A175">
         <v>281</v>
       </c>
@@ -7188,7 +7502,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="177" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="177" spans="1:10" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A177">
         <v>282</v>
       </c>
@@ -7311,7 +7625,7 @@
         <v>62</v>
       </c>
       <c r="D181" s="2" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="E181">
         <v>1</v>
@@ -7344,7 +7658,7 @@
         <v>50</v>
       </c>
       <c r="D182" s="2" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="E182">
         <v>1</v>
@@ -7361,6 +7675,9 @@
       </c>
       <c r="I182">
         <v>1.5</v>
+      </c>
+      <c r="J182" t="s">
+        <v>484</v>
       </c>
     </row>
     <row r="183" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -7392,6 +7709,9 @@
       <c r="I183">
         <v>1.4</v>
       </c>
+      <c r="J183" t="s">
+        <v>498</v>
+      </c>
     </row>
     <row r="184" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A184">
@@ -7404,7 +7724,7 @@
         <v>47</v>
       </c>
       <c r="D184" s="2" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="E184">
         <v>1</v>
@@ -7421,6 +7741,9 @@
       </c>
       <c r="I184">
         <v>1.4</v>
+      </c>
+      <c r="J184" t="s">
+        <v>271</v>
       </c>
     </row>
     <row r="185" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -7434,7 +7757,7 @@
         <v>46</v>
       </c>
       <c r="D185" s="2" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="E185">
         <v>1</v>
@@ -7451,6 +7774,9 @@
       </c>
       <c r="I185">
         <v>1.4</v>
+      </c>
+      <c r="J185" t="s">
+        <v>271</v>
       </c>
     </row>
     <row r="186" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -7464,7 +7790,7 @@
         <v>45</v>
       </c>
       <c r="D186" s="2" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E186">
         <v>1</v>
@@ -7481,6 +7807,9 @@
       </c>
       <c r="I186">
         <v>1.4</v>
+      </c>
+      <c r="J186" t="s">
+        <v>294</v>
       </c>
     </row>
     <row r="187" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -7494,7 +7823,7 @@
         <v>44</v>
       </c>
       <c r="D187" s="2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E187">
         <v>1</v>
@@ -7511,6 +7840,9 @@
       </c>
       <c r="I187">
         <v>1.4</v>
+      </c>
+      <c r="J187" t="s">
+        <v>276</v>
       </c>
     </row>
     <row r="188" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -7524,7 +7856,7 @@
         <v>43</v>
       </c>
       <c r="D188" s="2" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="E188">
         <v>1</v>
@@ -7541,6 +7873,9 @@
       </c>
       <c r="I188">
         <v>1.4</v>
+      </c>
+      <c r="J188" t="s">
+        <v>497</v>
       </c>
     </row>
     <row r="189" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -7587,7 +7922,7 @@
         <v>33</v>
       </c>
       <c r="D190" s="2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E190">
         <v>1</v>
@@ -7620,7 +7955,7 @@
         <v>34</v>
       </c>
       <c r="D191" s="2" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E191">
         <v>1</v>
@@ -7653,7 +7988,7 @@
         <v>63</v>
       </c>
       <c r="D192" s="2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E192">
         <v>1</v>
@@ -7675,7 +8010,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="193" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="193" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A193">
         <v>28</v>
       </c>
@@ -7708,7 +8043,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="194" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="194" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A194">
         <v>106</v>
       </c>
@@ -7719,7 +8054,7 @@
         <v>104</v>
       </c>
       <c r="D194" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E194">
         <v>1</v>
@@ -7728,7 +8063,7 @@
         <v>2</v>
       </c>
       <c r="G194">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="G194:G257" si="5">F194-H194</f>
         <v>2</v>
       </c>
       <c r="H194">
@@ -7737,8 +8072,14 @@
       <c r="I194">
         <v>2.2000000000000002</v>
       </c>
-    </row>
-    <row r="195" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="J194" t="s">
+        <v>487</v>
+      </c>
+      <c r="K194" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="195" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A195">
         <v>107</v>
       </c>
@@ -7749,7 +8090,7 @@
         <v>105</v>
       </c>
       <c r="D195" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E195">
         <v>1</v>
@@ -7758,7 +8099,7 @@
         <v>2</v>
       </c>
       <c r="G195">
-        <f t="shared" ref="G195:G258" si="5">F195-H195</f>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="H195">
@@ -7767,8 +8108,11 @@
       <c r="I195">
         <v>2.2000000000000002</v>
       </c>
-    </row>
-    <row r="196" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="J195" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="196" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A196">
         <v>165</v>
       </c>
@@ -7779,7 +8123,7 @@
         <v>159</v>
       </c>
       <c r="D196" s="2" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="E196">
         <v>1</v>
@@ -7800,8 +8144,11 @@
       <c r="J196" t="s">
         <v>324</v>
       </c>
-    </row>
-    <row r="197" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="K196" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="197" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A197">
         <v>36</v>
       </c>
@@ -7830,8 +8177,11 @@
       <c r="I197">
         <v>1.4</v>
       </c>
-    </row>
-    <row r="198" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="J197" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="198" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A198">
         <v>249</v>
       </c>
@@ -7861,10 +8211,10 @@
         <v>6.1</v>
       </c>
       <c r="J198" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="199" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="199" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A199">
         <v>20</v>
       </c>
@@ -7875,7 +8225,7 @@
         <v>21</v>
       </c>
       <c r="D199" s="2" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="E199">
         <v>1</v>
@@ -7897,7 +8247,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="200" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="200" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A200">
         <v>2</v>
       </c>
@@ -7908,7 +8258,7 @@
         <v>4</v>
       </c>
       <c r="D200" s="2" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="E200">
         <v>1</v>
@@ -7930,7 +8280,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="201" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="201" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A201">
         <v>3</v>
       </c>
@@ -7938,10 +8288,10 @@
         <v>5</v>
       </c>
       <c r="C201" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="D201" s="2" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="E201">
         <v>1</v>
@@ -7963,7 +8313,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="202" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="202" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A202">
         <v>12</v>
       </c>
@@ -7974,7 +8324,7 @@
         <v>14</v>
       </c>
       <c r="D202" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E202">
         <v>1</v>
@@ -7996,7 +8346,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="203" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="203" spans="1:11" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A203">
         <v>85</v>
       </c>
@@ -8023,7 +8373,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="204" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="204" spans="1:11" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A204">
         <v>86</v>
       </c>
@@ -8050,7 +8400,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="205" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="205" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A205">
         <v>65</v>
       </c>
@@ -8061,7 +8411,7 @@
         <v>64</v>
       </c>
       <c r="D205" s="2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E205">
         <v>1</v>
@@ -8083,7 +8433,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="206" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="206" spans="1:11" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A206">
         <v>87</v>
       </c>
@@ -8110,7 +8460,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="207" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="207" spans="1:11" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A207">
         <v>88</v>
       </c>
@@ -8137,7 +8487,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="208" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="208" spans="1:11" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A208">
         <v>89</v>
       </c>
@@ -8164,7 +8514,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="209" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="209" spans="1:10" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A209">
         <v>90</v>
       </c>
@@ -8191,7 +8541,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="210" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="210" spans="1:10" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A210">
         <v>91</v>
       </c>
@@ -8218,7 +8568,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="211" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="211" spans="1:10" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A211">
         <v>92</v>
       </c>
@@ -8256,7 +8606,7 @@
         <v>103</v>
       </c>
       <c r="D212" s="2" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="E212">
         <v>1</v>
@@ -8273,6 +8623,9 @@
       </c>
       <c r="I212">
         <v>2.2000000000000002</v>
+      </c>
+      <c r="J212" t="s">
+        <v>271</v>
       </c>
     </row>
     <row r="213" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -8304,6 +8657,9 @@
       <c r="I213">
         <v>2.4</v>
       </c>
+      <c r="J213" t="s">
+        <v>484</v>
+      </c>
     </row>
     <row r="214" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A214">
@@ -8334,6 +8690,9 @@
       <c r="I214">
         <v>2.4</v>
       </c>
+      <c r="J214" t="s">
+        <v>484</v>
+      </c>
     </row>
     <row r="215" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A215">
@@ -8364,6 +8723,9 @@
       <c r="I215">
         <v>2.4</v>
       </c>
+      <c r="J215" t="s">
+        <v>484</v>
+      </c>
     </row>
     <row r="216" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A216">
@@ -8376,7 +8738,7 @@
         <v>65</v>
       </c>
       <c r="D216" s="2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E216">
         <v>1</v>
@@ -8427,6 +8789,9 @@
       <c r="I217">
         <v>2.4</v>
       </c>
+      <c r="J217" t="s">
+        <v>484</v>
+      </c>
     </row>
     <row r="218" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A218">
@@ -8457,6 +8822,9 @@
       <c r="I218">
         <v>2.4</v>
       </c>
+      <c r="J218" t="s">
+        <v>484</v>
+      </c>
     </row>
     <row r="219" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A219">
@@ -8487,6 +8855,9 @@
       <c r="I219">
         <v>2.4</v>
       </c>
+      <c r="J219" t="s">
+        <v>484</v>
+      </c>
     </row>
     <row r="220" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A220">
@@ -8499,7 +8870,7 @@
         <v>148</v>
       </c>
       <c r="D220" s="2" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="E220">
         <v>1</v>
@@ -8532,7 +8903,7 @@
         <v>149</v>
       </c>
       <c r="D221" s="2" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="E221">
         <v>1</v>
@@ -8565,7 +8936,7 @@
         <v>150</v>
       </c>
       <c r="D222" s="2" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="E222">
         <v>1</v>
@@ -8598,7 +8969,7 @@
         <v>151</v>
       </c>
       <c r="D223" s="2" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="E223">
         <v>1</v>
@@ -8631,7 +9002,7 @@
         <v>152</v>
       </c>
       <c r="D224" s="2" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="E224">
         <v>1</v>
@@ -8653,7 +9024,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="225" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+    <row r="225" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A225">
         <v>158</v>
       </c>
@@ -8664,7 +9035,7 @@
         <v>153</v>
       </c>
       <c r="D225" s="2" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="E225">
         <v>1</v>
@@ -8686,7 +9057,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="226" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+    <row r="226" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A226">
         <v>159</v>
       </c>
@@ -8697,7 +9068,7 @@
         <v>154</v>
       </c>
       <c r="D226" s="2" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="E226">
         <v>1</v>
@@ -8719,7 +9090,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="227" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+    <row r="227" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A227">
         <v>67</v>
       </c>
@@ -8730,7 +9101,7 @@
         <v>66</v>
       </c>
       <c r="D227" s="2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E227">
         <v>1</v>
@@ -8752,7 +9123,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="228" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+    <row r="228" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A228">
         <v>160</v>
       </c>
@@ -8763,7 +9134,7 @@
         <v>155</v>
       </c>
       <c r="D228" s="2" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="E228">
         <v>1</v>
@@ -8785,7 +9156,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="229" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+    <row r="229" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A229">
         <v>161</v>
       </c>
@@ -8796,7 +9167,7 @@
         <v>156</v>
       </c>
       <c r="D229" s="2" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="E229">
         <v>1</v>
@@ -8818,7 +9189,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="230" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+    <row r="230" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A230">
         <v>162</v>
       </c>
@@ -8829,7 +9200,7 @@
         <v>157</v>
       </c>
       <c r="D230" s="2" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="E230">
         <v>1</v>
@@ -8851,7 +9222,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="231" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+    <row r="231" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A231">
         <v>176</v>
       </c>
@@ -8862,7 +9233,7 @@
         <v>170</v>
       </c>
       <c r="D231" s="2" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E231">
         <v>1</v>
@@ -8881,13 +9252,10 @@
         <v>4.2</v>
       </c>
       <c r="J231" t="s">
-        <v>328</v>
-      </c>
-      <c r="L231" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="232" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="232" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A232">
         <v>196</v>
       </c>
@@ -8898,7 +9266,7 @@
         <v>188</v>
       </c>
       <c r="D232" s="2" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="E232">
         <v>1</v>
@@ -8920,7 +9288,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="233" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+    <row r="233" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A233">
         <v>200</v>
       </c>
@@ -8931,7 +9299,7 @@
         <v>192</v>
       </c>
       <c r="D233" s="2" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="E233">
         <v>1</v>
@@ -8953,7 +9321,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="234" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+    <row r="234" spans="1:10" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A234">
         <v>204</v>
       </c>
@@ -8980,7 +9348,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="235" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+    <row r="235" spans="1:10" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A235">
         <v>207</v>
       </c>
@@ -9007,7 +9375,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="236" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+    <row r="236" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A236">
         <v>178</v>
       </c>
@@ -9018,7 +9386,7 @@
         <v>172</v>
       </c>
       <c r="D236" s="2" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="E236">
         <v>1</v>
@@ -9040,7 +9408,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="237" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+    <row r="237" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A237">
         <v>179</v>
       </c>
@@ -9051,7 +9419,7 @@
         <v>173</v>
       </c>
       <c r="D237" s="2" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="E237">
         <v>1</v>
@@ -9073,7 +9441,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="238" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+    <row r="238" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A238">
         <v>230</v>
       </c>
@@ -9084,7 +9452,7 @@
         <v>220</v>
       </c>
       <c r="D238" s="2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E238">
         <v>1</v>
@@ -9106,7 +9474,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="239" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+    <row r="239" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A239">
         <v>231</v>
       </c>
@@ -9117,7 +9485,7 @@
         <v>221</v>
       </c>
       <c r="D239" s="2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E239">
         <v>1</v>
@@ -9139,7 +9507,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="240" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+    <row r="240" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A240">
         <v>232</v>
       </c>
@@ -9150,7 +9518,7 @@
         <v>222</v>
       </c>
       <c r="D240" s="2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E240">
         <v>1</v>
@@ -9183,7 +9551,7 @@
         <v>223</v>
       </c>
       <c r="D241" s="2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E241">
         <v>1</v>
@@ -9216,7 +9584,7 @@
         <v>224</v>
       </c>
       <c r="D242" s="2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E242">
         <v>1</v>
@@ -9249,7 +9617,7 @@
         <v>225</v>
       </c>
       <c r="D243" s="2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E243">
         <v>1</v>
@@ -9282,7 +9650,7 @@
         <v>226</v>
       </c>
       <c r="D244" s="2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E244">
         <v>1</v>
@@ -9315,7 +9683,7 @@
         <v>227</v>
       </c>
       <c r="D245" s="2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E245">
         <v>1</v>
@@ -9348,7 +9716,7 @@
         <v>228</v>
       </c>
       <c r="D246" s="2" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="E246">
         <v>1</v>
@@ -9367,7 +9735,7 @@
         <v>5.4</v>
       </c>
       <c r="J246" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="247" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -9381,7 +9749,7 @@
         <v>229</v>
       </c>
       <c r="D247" s="2" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="E247">
         <v>1</v>
@@ -9400,7 +9768,7 @@
         <v>5.4</v>
       </c>
       <c r="J247" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="248" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -9414,7 +9782,7 @@
         <v>67</v>
       </c>
       <c r="D248" s="2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E248">
         <v>1</v>
@@ -9447,7 +9815,7 @@
         <v>230</v>
       </c>
       <c r="D249" s="2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E249">
         <v>1</v>
@@ -9480,7 +9848,7 @@
         <v>231</v>
       </c>
       <c r="D250" s="2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E250">
         <v>1</v>
@@ -9513,7 +9881,7 @@
         <v>232</v>
       </c>
       <c r="D251" s="2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E251">
         <v>1</v>
@@ -9546,7 +9914,7 @@
         <v>233</v>
       </c>
       <c r="D252" s="2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E252">
         <v>1</v>
@@ -9579,7 +9947,7 @@
         <v>234</v>
       </c>
       <c r="D253" s="2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E253">
         <v>1</v>
@@ -9612,7 +9980,7 @@
         <v>235</v>
       </c>
       <c r="D254" s="2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E254">
         <v>1</v>
@@ -9645,7 +10013,7 @@
         <v>236</v>
       </c>
       <c r="D255" s="2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E255">
         <v>1</v>
@@ -9678,7 +10046,7 @@
         <v>237</v>
       </c>
       <c r="D256" s="2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E256">
         <v>1</v>
@@ -9700,7 +10068,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="257" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="257" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A257">
         <v>268</v>
       </c>
@@ -9711,7 +10079,7 @@
         <v>256</v>
       </c>
       <c r="D257" s="2" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="E257">
         <v>1</v>
@@ -9730,10 +10098,10 @@
         <v>6.2</v>
       </c>
       <c r="J257" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="258" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="258" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A258">
         <v>269</v>
       </c>
@@ -9744,7 +10112,7 @@
         <v>257</v>
       </c>
       <c r="D258" s="2" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="E258">
         <v>1</v>
@@ -9753,7 +10121,7 @@
         <v>2</v>
       </c>
       <c r="G258">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="G258:G321" si="6">F258-H258</f>
         <v>2</v>
       </c>
       <c r="H258">
@@ -9763,10 +10131,10 @@
         <v>6.2</v>
       </c>
       <c r="J258" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="259" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="259" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A259">
         <v>270</v>
       </c>
@@ -9777,7 +10145,7 @@
         <v>258</v>
       </c>
       <c r="D259" s="2" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="E259">
         <v>1</v>
@@ -9786,7 +10154,7 @@
         <v>2</v>
       </c>
       <c r="G259">
-        <f t="shared" ref="G259:G283" si="6">F259-H259</f>
+        <f t="shared" si="6"/>
         <v>2</v>
       </c>
       <c r="H259">
@@ -9796,10 +10164,10 @@
         <v>6.2</v>
       </c>
       <c r="J259" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="260" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="260" spans="1:11" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A260">
         <v>271</v>
       </c>
@@ -9810,7 +10178,7 @@
         <v>259</v>
       </c>
       <c r="D260" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="E260">
         <v>1</v>
@@ -9832,7 +10200,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="261" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="261" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A261">
         <v>272</v>
       </c>
@@ -9843,7 +10211,7 @@
         <v>260</v>
       </c>
       <c r="D261" s="2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E261">
         <v>1</v>
@@ -9865,7 +10233,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="262" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="262" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A262">
         <v>273</v>
       </c>
@@ -9876,7 +10244,7 @@
         <v>261</v>
       </c>
       <c r="D262" s="2" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="E262">
         <v>1</v>
@@ -9895,10 +10263,10 @@
         <v>6.2</v>
       </c>
       <c r="J262" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="263" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="263" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A263">
         <v>274</v>
       </c>
@@ -9909,7 +10277,7 @@
         <v>262</v>
       </c>
       <c r="D263" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="E263">
         <v>1</v>
@@ -9928,10 +10296,10 @@
         <v>6.2</v>
       </c>
       <c r="J263" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="264" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="264" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A264">
         <v>275</v>
       </c>
@@ -9942,7 +10310,7 @@
         <v>263</v>
       </c>
       <c r="D264" s="2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E264">
         <v>1</v>
@@ -9964,7 +10332,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="265" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="265" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A265">
         <v>223</v>
       </c>
@@ -9975,7 +10343,7 @@
         <v>213</v>
       </c>
       <c r="D265" s="2" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="E265">
         <v>1</v>
@@ -9993,8 +10361,11 @@
       <c r="I265">
         <v>5.4</v>
       </c>
-    </row>
-    <row r="266" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="J265" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="266" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A266">
         <v>251</v>
       </c>
@@ -10005,7 +10376,7 @@
         <v>240</v>
       </c>
       <c r="D266" s="2" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="E266">
         <v>1</v>
@@ -10024,10 +10395,10 @@
         <v>6.1</v>
       </c>
       <c r="J266" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="267" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="267" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A267">
         <v>252</v>
       </c>
@@ -10038,7 +10409,7 @@
         <v>241</v>
       </c>
       <c r="D267" s="2" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="E267">
         <v>1</v>
@@ -10057,10 +10428,10 @@
         <v>6.1</v>
       </c>
       <c r="J267" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="268" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="268" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A268">
         <v>254</v>
       </c>
@@ -10071,7 +10442,7 @@
         <v>243</v>
       </c>
       <c r="D268" s="2" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E268">
         <v>1</v>
@@ -10089,8 +10460,11 @@
       <c r="I268">
         <v>6.1</v>
       </c>
-    </row>
-    <row r="269" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="J268" s="2" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="269" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A269">
         <v>69</v>
       </c>
@@ -10101,7 +10475,7 @@
         <v>68</v>
       </c>
       <c r="D269" s="2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E269">
         <v>1</v>
@@ -10123,7 +10497,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="270" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="270" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A270">
         <v>256</v>
       </c>
@@ -10134,7 +10508,7 @@
         <v>245</v>
       </c>
       <c r="D270" s="2" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E270">
         <v>1</v>
@@ -10156,7 +10530,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="271" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="271" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A271">
         <v>227</v>
       </c>
@@ -10167,7 +10541,7 @@
         <v>217</v>
       </c>
       <c r="D271" s="2" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="E271">
         <v>1</v>
@@ -10186,10 +10560,10 @@
         <v>5.4</v>
       </c>
       <c r="J271" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="272" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="272" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A272">
         <v>197</v>
       </c>
@@ -10200,7 +10574,7 @@
         <v>189</v>
       </c>
       <c r="D272" s="2" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="E272">
         <v>1</v>
@@ -10219,10 +10593,13 @@
         <v>5.2</v>
       </c>
       <c r="J272" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="273" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+        <v>482</v>
+      </c>
+      <c r="K272" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="273" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A273">
         <v>198</v>
       </c>
@@ -10233,7 +10610,7 @@
         <v>190</v>
       </c>
       <c r="D273" s="2" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="E273">
         <v>1</v>
@@ -10252,10 +10629,13 @@
         <v>5.2</v>
       </c>
       <c r="J273" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="274" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+        <v>482</v>
+      </c>
+      <c r="K273" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="274" spans="1:11" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A274">
         <v>205</v>
       </c>
@@ -10282,7 +10662,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="275" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="275" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A275">
         <v>57</v>
       </c>
@@ -10293,7 +10673,7 @@
         <v>56</v>
       </c>
       <c r="D275" s="2" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E275">
         <v>1</v>
@@ -10315,7 +10695,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="276" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="276" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A276">
         <v>41</v>
       </c>
@@ -10348,7 +10728,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="277" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="277" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A277">
         <v>255</v>
       </c>
@@ -10359,7 +10739,7 @@
         <v>244</v>
       </c>
       <c r="D277" s="2" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="E277">
         <v>1</v>
@@ -10377,8 +10757,11 @@
       <c r="I277">
         <v>6.1</v>
       </c>
-    </row>
-    <row r="278" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="J277" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="278" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A278">
         <v>80</v>
       </c>
@@ -10389,7 +10772,7 @@
         <v>78</v>
       </c>
       <c r="D278" s="2" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="E278">
         <v>1</v>
@@ -10407,8 +10790,11 @@
       <c r="I278">
         <v>2.1</v>
       </c>
-    </row>
-    <row r="279" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="J278" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="279" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A279">
         <v>81</v>
       </c>
@@ -10419,7 +10805,7 @@
         <v>79</v>
       </c>
       <c r="D279" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E279">
         <v>1</v>
@@ -10437,9 +10823,11 @@
       <c r="I279">
         <v>2.1</v>
       </c>
-      <c r="J279" s="1"/>
-    </row>
-    <row r="280" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="J279" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="280" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A280">
         <v>276</v>
       </c>
@@ -10463,10 +10851,10 @@
         <v>6.2</v>
       </c>
       <c r="J280" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="281" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="281" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A281">
         <v>32</v>
       </c>
@@ -10477,7 +10865,7 @@
         <v>32</v>
       </c>
       <c r="D281" s="2" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="E281">
         <v>1</v>
@@ -10499,7 +10887,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="282" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="282" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A282">
         <v>9</v>
       </c>
@@ -10510,7 +10898,7 @@
         <v>11</v>
       </c>
       <c r="D282" s="2" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="E282">
         <v>1</v>
@@ -10532,7 +10920,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="283" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="283" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A283">
         <v>164</v>
       </c>
@@ -10543,7 +10931,7 @@
         <v>158</v>
       </c>
       <c r="D283" s="2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="E283">
         <v>1</v>
@@ -10565,7 +10953,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="284" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="284" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="F284">
         <f>SUM(F2:F283)</f>
         <v>2570</v>
@@ -10580,7 +10968,3258 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:K285" xr:uid="{A507EC0B-FECA-46C5-861D-53A4B99CDA9D}">
+    <filterColumn colId="9">
+      <filters blank="1">
+        <filter val="1 kΩ   ±5%"/>
+        <filter val="1.5 kΩ   ±5%"/>
+        <filter val="10 kΩ   ±5%"/>
+        <filter val="100 Ω   ±5%"/>
+        <filter val="104 50V"/>
+        <filter val="1843 20 kHZ 11034"/>
+        <filter val="20 kΩ   ±5% "/>
+        <filter val="22 pF"/>
+        <filter val="3.3 kΩ   ±5%"/>
+        <filter val="33 Ω   ±5%"/>
+        <filter val="330"/>
+        <filter val="330 Ω   ±5%"/>
+        <filter val="4.7 kΩ   ±5%"/>
+        <filter val="406C MC1489A 75189AN"/>
+        <filter val="47 kΩ   ±5%"/>
+        <filter val="47 Ω   ±5% "/>
+        <filter val="7404PC"/>
+        <filter val="74LS08 PC"/>
+        <filter val="74LS132NB"/>
+        <filter val="74LS14N"/>
+        <filter val="74LS244N"/>
+        <filter val="74LS374N"/>
+        <filter val="8.000 SUNNY 2779"/>
+        <filter val="8624KD D765AC-2"/>
+        <filter val="920 Ω   ±5% / 820 Ω   ±5%"/>
+        <filter val="CR"/>
+        <filter val="CR (15 MΩ   ±0.05% / ±0.02%)"/>
+        <filter val="CR (74LS04 PC)"/>
+        <filter val="CR (SN74LS3…)"/>
+        <filter val="DM7404N"/>
+        <filter val="DM74LS04N"/>
+        <filter val="DM74LS393N"/>
+        <filter val="DM74S74N"/>
+        <filter val="EL74LS10J"/>
+        <filter val="EL74S04"/>
+        <filter val="HD74LS42P"/>
+        <filter val="LED"/>
+        <filter val="M3764A-15 65518"/>
+        <filter val="MC14411 P QR8610"/>
+        <filter val="MC1488P RQ8319"/>
+        <filter val="MC1488P T8444"/>
+        <filter val="MC1489P K8539"/>
+        <filter val="MM58167AN"/>
+        <filter val="MOSTEK TC8639 MK3880N-4 Z80-CPU"/>
+        <filter val="PH"/>
+        <filter val="PWR"/>
+        <filter val="QRT-38 I"/>
+        <filter val="SN54LS367AJ"/>
+        <filter val="SN74LS01N"/>
+        <filter val="SN74LS05J"/>
+        <filter val="SN74LS08N"/>
+        <filter val="SN74LS123N"/>
+        <filter val="SN74LS138N"/>
+        <filter val="SN74LS157N"/>
+        <filter val="SN74LS20N"/>
+        <filter val="SN74LS244N"/>
+        <filter val="SN74LS32N"/>
+        <filter val="SN74LS367AN"/>
+        <filter val="SN74LS629N"/>
+        <filter val="SN74LS74AN"/>
+        <filter val="SN74LS86N"/>
+        <filter val="T74LS244BI"/>
+        <filter val="T74LS27BI"/>
+        <filter val="T74LS30BI"/>
+        <filter val="T74LS38BI"/>
+        <filter val="WD1691PE 8348"/>
+        <filter val="WD2143-PD 03-15 8706"/>
+        <filter val="Z8410AB1 Z80ADMA 28618"/>
+        <filter val="ZILOG Z84??BPS Z80? SIO/1 8338 W"/>
+        <filter val="ZILOG Z8430APE Z80A CTC 8342"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K284">
+    <sortCondition ref="B2:B284"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8D64CAE-8C67-480F-8B07-5B75546A5D0C}">
+  <dimension ref="A1:E102"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="4" max="4" width="11.1015625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="90.05078125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" t="s">
+        <v>342</v>
+      </c>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>420</v>
+      </c>
+      <c r="D1" t="s">
+        <v>463</v>
+      </c>
+      <c r="E1" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2">
+        <v>138</v>
+      </c>
+      <c r="B2" t="s">
+        <v>134</v>
+      </c>
+      <c r="C2">
+        <v>14</v>
+      </c>
+      <c r="D2">
+        <v>50</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3">
+        <v>139</v>
+      </c>
+      <c r="B3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C3">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4">
+        <v>135</v>
+      </c>
+      <c r="B4" t="s">
+        <v>131</v>
+      </c>
+      <c r="C4">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5">
+        <v>141</v>
+      </c>
+      <c r="B5" t="s">
+        <v>137</v>
+      </c>
+      <c r="C5">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6">
+        <v>134</v>
+      </c>
+      <c r="B6" t="s">
+        <v>130</v>
+      </c>
+      <c r="C6">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7">
+        <v>14</v>
+      </c>
+      <c r="B7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8">
+        <v>210</v>
+      </c>
+      <c r="B8" t="s">
+        <v>201</v>
+      </c>
+      <c r="C8">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9">
+        <v>23</v>
+      </c>
+      <c r="B9" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10">
+        <v>6</v>
+      </c>
+      <c r="B10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11">
+        <v>76</v>
+      </c>
+      <c r="B11" t="s">
+        <v>74</v>
+      </c>
+      <c r="C11">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12">
+        <v>103</v>
+      </c>
+      <c r="B12" t="s">
+        <v>101</v>
+      </c>
+      <c r="C12">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13">
+        <v>217</v>
+      </c>
+      <c r="B13" t="s">
+        <v>208</v>
+      </c>
+      <c r="C13">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14">
+        <v>208</v>
+      </c>
+      <c r="B14" t="s">
+        <v>199</v>
+      </c>
+      <c r="C14">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15">
+        <v>211</v>
+      </c>
+      <c r="B15" t="s">
+        <v>202</v>
+      </c>
+      <c r="C15">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16">
+        <v>18</v>
+      </c>
+      <c r="B16" t="s">
+        <v>19</v>
+      </c>
+      <c r="C16">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17">
+        <v>263</v>
+      </c>
+      <c r="B17" t="s">
+        <v>252</v>
+      </c>
+      <c r="C17">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18">
+        <v>7</v>
+      </c>
+      <c r="B18" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A19">
+        <v>13</v>
+      </c>
+      <c r="B19" t="s">
+        <v>15</v>
+      </c>
+      <c r="C19">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A20">
+        <v>137</v>
+      </c>
+      <c r="B20" t="s">
+        <v>133</v>
+      </c>
+      <c r="C20">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A21">
+        <v>214</v>
+      </c>
+      <c r="B21" t="s">
+        <v>205</v>
+      </c>
+      <c r="C21">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A22">
+        <v>212</v>
+      </c>
+      <c r="B22" t="s">
+        <v>203</v>
+      </c>
+      <c r="C22">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A23">
+        <v>215</v>
+      </c>
+      <c r="B23" t="s">
+        <v>206</v>
+      </c>
+      <c r="C23">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A24">
+        <v>209</v>
+      </c>
+      <c r="B24" t="s">
+        <v>200</v>
+      </c>
+      <c r="C24">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A25">
+        <v>56</v>
+      </c>
+      <c r="B25" t="s">
+        <v>55</v>
+      </c>
+      <c r="C25">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A26">
+        <v>120</v>
+      </c>
+      <c r="B26" t="s">
+        <v>117</v>
+      </c>
+      <c r="C26">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A27">
+        <v>132</v>
+      </c>
+      <c r="B27" t="s">
+        <v>128</v>
+      </c>
+      <c r="C27">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A28">
+        <v>260</v>
+      </c>
+      <c r="B28" t="s">
+        <v>249</v>
+      </c>
+      <c r="C28">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A29">
+        <v>4</v>
+      </c>
+      <c r="B29" t="s">
+        <v>6</v>
+      </c>
+      <c r="C29">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A30">
+        <v>216</v>
+      </c>
+      <c r="B30" t="s">
+        <v>207</v>
+      </c>
+      <c r="C30">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A31">
+        <v>219</v>
+      </c>
+      <c r="B31" t="s">
+        <v>210</v>
+      </c>
+      <c r="C31">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A32">
+        <v>220</v>
+      </c>
+      <c r="B32" t="s">
+        <v>211</v>
+      </c>
+      <c r="C32">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A33">
+        <v>94</v>
+      </c>
+      <c r="B33" t="s">
+        <v>92</v>
+      </c>
+      <c r="C33">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A34">
+        <v>77</v>
+      </c>
+      <c r="B34" t="s">
+        <v>75</v>
+      </c>
+      <c r="C34">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A35">
+        <v>78</v>
+      </c>
+      <c r="B35" t="s">
+        <v>76</v>
+      </c>
+      <c r="C35">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A36">
+        <v>136</v>
+      </c>
+      <c r="B36" t="s">
+        <v>132</v>
+      </c>
+      <c r="C36">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A37">
+        <v>133</v>
+      </c>
+      <c r="B37" t="s">
+        <v>129</v>
+      </c>
+      <c r="C37">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A38">
+        <v>218</v>
+      </c>
+      <c r="B38" t="s">
+        <v>209</v>
+      </c>
+      <c r="C38">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A39">
+        <v>123</v>
+      </c>
+      <c r="B39" t="s">
+        <v>120</v>
+      </c>
+      <c r="C39">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A40">
+        <v>124</v>
+      </c>
+      <c r="B40" t="s">
+        <v>121</v>
+      </c>
+      <c r="C40">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A41">
+        <v>122</v>
+      </c>
+      <c r="B41" t="s">
+        <v>119</v>
+      </c>
+      <c r="C41">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A42">
+        <v>206</v>
+      </c>
+      <c r="B42" t="s">
+        <v>197</v>
+      </c>
+      <c r="C42">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A43">
+        <v>258</v>
+      </c>
+      <c r="B43" t="s">
+        <v>247</v>
+      </c>
+      <c r="C43">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A44">
+        <v>259</v>
+      </c>
+      <c r="B44" t="s">
+        <v>248</v>
+      </c>
+      <c r="C44">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A45">
+        <v>261</v>
+      </c>
+      <c r="B45" t="s">
+        <v>250</v>
+      </c>
+      <c r="C45">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A46">
+        <v>262</v>
+      </c>
+      <c r="B46" t="s">
+        <v>251</v>
+      </c>
+      <c r="C46">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A47">
+        <v>5</v>
+      </c>
+      <c r="B47" t="s">
+        <v>7</v>
+      </c>
+      <c r="C47">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A48">
+        <v>40</v>
+      </c>
+      <c r="B48" t="s">
+        <v>41</v>
+      </c>
+      <c r="C48">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A49">
+        <v>201</v>
+      </c>
+      <c r="B49" t="s">
+        <v>193</v>
+      </c>
+      <c r="C49">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A50">
+        <v>266</v>
+      </c>
+      <c r="B50" t="s">
+        <v>254</v>
+      </c>
+      <c r="C50">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A51">
+        <v>25</v>
+      </c>
+      <c r="B51" t="s">
+        <v>25</v>
+      </c>
+      <c r="C51">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A52">
+        <v>193</v>
+      </c>
+      <c r="B52" t="s">
+        <v>186</v>
+      </c>
+      <c r="C52">
+        <v>16</v>
+      </c>
+      <c r="D52">
+        <v>26</v>
+      </c>
+      <c r="E52" s="8" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A53">
+        <v>194</v>
+      </c>
+      <c r="B53" t="s">
+        <v>187</v>
+      </c>
+      <c r="C53">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A54">
+        <v>145</v>
+      </c>
+      <c r="B54" t="s">
+        <v>140</v>
+      </c>
+      <c r="C54">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A55">
+        <v>146</v>
+      </c>
+      <c r="B55" t="s">
+        <v>141</v>
+      </c>
+      <c r="C55">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A56">
+        <v>147</v>
+      </c>
+      <c r="B56" t="s">
+        <v>142</v>
+      </c>
+      <c r="C56">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A57">
+        <v>148</v>
+      </c>
+      <c r="B57" t="s">
+        <v>143</v>
+      </c>
+      <c r="C57">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A58">
+        <v>149</v>
+      </c>
+      <c r="B58" t="s">
+        <v>144</v>
+      </c>
+      <c r="C58">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A59">
+        <v>150</v>
+      </c>
+      <c r="B59" t="s">
+        <v>145</v>
+      </c>
+      <c r="C59">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A60">
+        <v>151</v>
+      </c>
+      <c r="B60" t="s">
+        <v>146</v>
+      </c>
+      <c r="C60">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A61">
+        <v>152</v>
+      </c>
+      <c r="B61" t="s">
+        <v>147</v>
+      </c>
+      <c r="C61">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A62">
+        <v>187</v>
+      </c>
+      <c r="B62" t="s">
+        <v>180</v>
+      </c>
+      <c r="C62">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A63">
+        <v>188</v>
+      </c>
+      <c r="B63" t="s">
+        <v>181</v>
+      </c>
+      <c r="C63">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A64">
+        <v>189</v>
+      </c>
+      <c r="B64" t="s">
+        <v>182</v>
+      </c>
+      <c r="C64">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A65">
+        <v>190</v>
+      </c>
+      <c r="B65" t="s">
+        <v>183</v>
+      </c>
+      <c r="C65">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A66">
+        <v>191</v>
+      </c>
+      <c r="B66" t="s">
+        <v>184</v>
+      </c>
+      <c r="C66">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A67">
+        <v>192</v>
+      </c>
+      <c r="B67" t="s">
+        <v>185</v>
+      </c>
+      <c r="C67">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A68">
+        <v>55</v>
+      </c>
+      <c r="B68" t="s">
+        <v>54</v>
+      </c>
+      <c r="C68">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A69">
+        <v>173</v>
+      </c>
+      <c r="B69" t="s">
+        <v>167</v>
+      </c>
+      <c r="C69">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A70">
+        <v>170</v>
+      </c>
+      <c r="B70" t="s">
+        <v>164</v>
+      </c>
+      <c r="C70">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A71">
+        <v>171</v>
+      </c>
+      <c r="B71" t="s">
+        <v>165</v>
+      </c>
+      <c r="C71">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A72">
+        <v>126</v>
+      </c>
+      <c r="B72" t="s">
+        <v>122</v>
+      </c>
+      <c r="C72">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A73">
+        <v>202</v>
+      </c>
+      <c r="B73" t="s">
+        <v>194</v>
+      </c>
+      <c r="C73">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A74">
+        <v>50</v>
+      </c>
+      <c r="B74" t="s">
+        <v>49</v>
+      </c>
+      <c r="C74">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A75">
+        <v>29</v>
+      </c>
+      <c r="B75" t="s">
+        <v>29</v>
+      </c>
+      <c r="C75">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A76">
+        <v>82</v>
+      </c>
+      <c r="B76" t="s">
+        <v>80</v>
+      </c>
+      <c r="C76">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A77">
+        <v>177</v>
+      </c>
+      <c r="B77" t="s">
+        <v>171</v>
+      </c>
+      <c r="C77">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A78">
+        <v>172</v>
+      </c>
+      <c r="B78" t="s">
+        <v>166</v>
+      </c>
+      <c r="C78">
+        <v>18</v>
+      </c>
+      <c r="D78">
+        <v>1</v>
+      </c>
+      <c r="E78" s="8" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A79">
+        <v>58</v>
+      </c>
+      <c r="B79" t="s">
+        <v>57</v>
+      </c>
+      <c r="C79">
+        <v>20</v>
+      </c>
+      <c r="D79">
+        <v>16</v>
+      </c>
+      <c r="E79" s="8" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A80">
+        <v>59</v>
+      </c>
+      <c r="B80" t="s">
+        <v>58</v>
+      </c>
+      <c r="C80">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A81">
+        <v>49</v>
+      </c>
+      <c r="B81" t="s">
+        <v>48</v>
+      </c>
+      <c r="C81">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A82">
+        <v>30</v>
+      </c>
+      <c r="B82" t="s">
+        <v>30</v>
+      </c>
+      <c r="C82">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A83">
+        <v>31</v>
+      </c>
+      <c r="B83" t="s">
+        <v>31</v>
+      </c>
+      <c r="C83">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A84">
+        <v>21</v>
+      </c>
+      <c r="B84" t="s">
+        <v>22</v>
+      </c>
+      <c r="C84">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A85">
+        <v>22</v>
+      </c>
+      <c r="B85" t="s">
+        <v>23</v>
+      </c>
+      <c r="C85">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A86">
+        <v>113</v>
+      </c>
+      <c r="B86" t="s">
+        <v>110</v>
+      </c>
+      <c r="C86">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A87">
+        <v>84</v>
+      </c>
+      <c r="B87" t="s">
+        <v>82</v>
+      </c>
+      <c r="C87">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A88">
+        <v>26</v>
+      </c>
+      <c r="B88" t="s">
+        <v>26</v>
+      </c>
+      <c r="C88">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A89">
+        <v>27</v>
+      </c>
+      <c r="B89" t="s">
+        <v>27</v>
+      </c>
+      <c r="C89">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A90">
+        <v>168</v>
+      </c>
+      <c r="B90" t="s">
+        <v>162</v>
+      </c>
+      <c r="C90">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A91">
+        <v>16</v>
+      </c>
+      <c r="B91" t="s">
+        <v>17</v>
+      </c>
+      <c r="C91">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A92">
+        <v>17</v>
+      </c>
+      <c r="B92" t="s">
+        <v>18</v>
+      </c>
+      <c r="C92">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A93">
+        <v>167</v>
+      </c>
+      <c r="B93" t="s">
+        <v>161</v>
+      </c>
+      <c r="C93">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A94">
+        <v>129</v>
+      </c>
+      <c r="B94" t="s">
+        <v>126</v>
+      </c>
+      <c r="C94">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A95">
+        <v>128</v>
+      </c>
+      <c r="B95" t="s">
+        <v>124</v>
+      </c>
+      <c r="C95">
+        <v>24</v>
+      </c>
+      <c r="D95">
+        <v>3</v>
+      </c>
+      <c r="E95" s="8" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A96">
+        <v>181</v>
+      </c>
+      <c r="B96" t="s">
+        <v>175</v>
+      </c>
+      <c r="C96">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A97">
+        <v>93</v>
+      </c>
+      <c r="B97" t="s">
+        <v>91</v>
+      </c>
+      <c r="C97">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A98">
+        <v>169</v>
+      </c>
+      <c r="B98" t="s">
+        <v>163</v>
+      </c>
+      <c r="C98">
+        <v>28</v>
+      </c>
+      <c r="D98">
+        <v>1</v>
+      </c>
+      <c r="E98" s="8" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A99">
+        <v>131</v>
+      </c>
+      <c r="B99" t="s">
+        <v>127</v>
+      </c>
+      <c r="C99">
+        <v>40</v>
+      </c>
+      <c r="D99">
+        <v>4</v>
+      </c>
+      <c r="E99" s="8" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A100">
+        <v>112</v>
+      </c>
+      <c r="B100" t="s">
+        <v>109</v>
+      </c>
+      <c r="C100">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A101">
+        <v>109</v>
+      </c>
+      <c r="B101" t="s">
+        <v>106</v>
+      </c>
+      <c r="C101">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A102">
+        <v>111</v>
+      </c>
+      <c r="B102" t="s">
+        <v>108</v>
+      </c>
+      <c r="C102">
+        <v>40</v>
+      </c>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C102">
+    <sortCondition ref="C2:C102"/>
+  </sortState>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A40BA8F-AFFC-4D60-89B3-F498D80C2CF3}">
+  <dimension ref="A1:G102"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="3" max="3" width="12.47265625" style="5" customWidth="1"/>
+    <col min="4" max="4" width="31.3125" style="5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="88" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" t="s">
+        <v>342</v>
+      </c>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>344</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>425</v>
+      </c>
+      <c r="E1" t="s">
+        <v>420</v>
+      </c>
+      <c r="F1" t="s">
+        <v>423</v>
+      </c>
+      <c r="G1" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2">
+        <v>138</v>
+      </c>
+      <c r="B2" t="s">
+        <v>134</v>
+      </c>
+      <c r="C2" s="5">
+        <v>1488</v>
+      </c>
+      <c r="D2" t="s">
+        <v>317</v>
+      </c>
+      <c r="E2">
+        <v>14</v>
+      </c>
+      <c r="F2" t="s">
+        <v>426</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3">
+        <v>139</v>
+      </c>
+      <c r="B3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C3" s="5">
+        <v>1488</v>
+      </c>
+      <c r="D3" t="s">
+        <v>318</v>
+      </c>
+      <c r="E3">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4">
+        <v>135</v>
+      </c>
+      <c r="B4" t="s">
+        <v>131</v>
+      </c>
+      <c r="C4" s="5">
+        <v>1489</v>
+      </c>
+      <c r="D4" t="s">
+        <v>316</v>
+      </c>
+      <c r="E4">
+        <v>14</v>
+      </c>
+      <c r="F4" t="s">
+        <v>427</v>
+      </c>
+      <c r="G4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5">
+        <v>141</v>
+      </c>
+      <c r="B5" t="s">
+        <v>137</v>
+      </c>
+      <c r="C5" s="5">
+        <v>1489</v>
+      </c>
+      <c r="D5" t="s">
+        <v>315</v>
+      </c>
+      <c r="E5">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6">
+        <v>134</v>
+      </c>
+      <c r="B6" t="s">
+        <v>130</v>
+      </c>
+      <c r="C6" s="5">
+        <v>1489</v>
+      </c>
+      <c r="D6" t="s">
+        <v>315</v>
+      </c>
+      <c r="E6">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7">
+        <v>193</v>
+      </c>
+      <c r="B7" t="s">
+        <v>186</v>
+      </c>
+      <c r="C7" s="6">
+        <v>2164</v>
+      </c>
+      <c r="D7" t="s">
+        <v>319</v>
+      </c>
+      <c r="E7">
+        <v>16</v>
+      </c>
+      <c r="F7" t="s">
+        <v>432</v>
+      </c>
+      <c r="G7">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8">
+        <v>194</v>
+      </c>
+      <c r="B8" t="s">
+        <v>187</v>
+      </c>
+      <c r="C8" s="6">
+        <v>2164</v>
+      </c>
+      <c r="D8" t="s">
+        <v>319</v>
+      </c>
+      <c r="E8">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9">
+        <v>145</v>
+      </c>
+      <c r="B9" t="s">
+        <v>140</v>
+      </c>
+      <c r="C9" s="5">
+        <v>2164</v>
+      </c>
+      <c r="D9" t="s">
+        <v>319</v>
+      </c>
+      <c r="E9">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10">
+        <v>146</v>
+      </c>
+      <c r="B10" t="s">
+        <v>141</v>
+      </c>
+      <c r="C10" s="5">
+        <v>2164</v>
+      </c>
+      <c r="D10" t="s">
+        <v>319</v>
+      </c>
+      <c r="E10">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11">
+        <v>147</v>
+      </c>
+      <c r="B11" t="s">
+        <v>142</v>
+      </c>
+      <c r="C11" s="5">
+        <v>2164</v>
+      </c>
+      <c r="D11" t="s">
+        <v>319</v>
+      </c>
+      <c r="E11">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12">
+        <v>148</v>
+      </c>
+      <c r="B12" t="s">
+        <v>143</v>
+      </c>
+      <c r="C12" s="5">
+        <v>2164</v>
+      </c>
+      <c r="D12" t="s">
+        <v>319</v>
+      </c>
+      <c r="E12">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13">
+        <v>149</v>
+      </c>
+      <c r="B13" t="s">
+        <v>144</v>
+      </c>
+      <c r="C13" s="5">
+        <v>2164</v>
+      </c>
+      <c r="D13" t="s">
+        <v>319</v>
+      </c>
+      <c r="E13">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14">
+        <v>150</v>
+      </c>
+      <c r="B14" t="s">
+        <v>145</v>
+      </c>
+      <c r="C14" s="5">
+        <v>2164</v>
+      </c>
+      <c r="D14" t="s">
+        <v>319</v>
+      </c>
+      <c r="E14">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15">
+        <v>151</v>
+      </c>
+      <c r="B15" t="s">
+        <v>146</v>
+      </c>
+      <c r="C15" s="5">
+        <v>2164</v>
+      </c>
+      <c r="D15" t="s">
+        <v>319</v>
+      </c>
+      <c r="E15">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16">
+        <v>152</v>
+      </c>
+      <c r="B16" t="s">
+        <v>147</v>
+      </c>
+      <c r="C16" s="5">
+        <v>2164</v>
+      </c>
+      <c r="D16" t="s">
+        <v>319</v>
+      </c>
+      <c r="E16">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17">
+        <v>187</v>
+      </c>
+      <c r="B17" t="s">
+        <v>180</v>
+      </c>
+      <c r="C17" s="5">
+        <v>2164</v>
+      </c>
+      <c r="D17" t="s">
+        <v>319</v>
+      </c>
+      <c r="E17">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18">
+        <v>188</v>
+      </c>
+      <c r="B18" t="s">
+        <v>181</v>
+      </c>
+      <c r="C18" s="5">
+        <v>2164</v>
+      </c>
+      <c r="D18" t="s">
+        <v>319</v>
+      </c>
+      <c r="E18">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A19">
+        <v>189</v>
+      </c>
+      <c r="B19" t="s">
+        <v>182</v>
+      </c>
+      <c r="C19" s="5">
+        <v>2164</v>
+      </c>
+      <c r="D19" t="s">
+        <v>319</v>
+      </c>
+      <c r="E19">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A20">
+        <v>190</v>
+      </c>
+      <c r="B20" t="s">
+        <v>183</v>
+      </c>
+      <c r="C20" s="5">
+        <v>2164</v>
+      </c>
+      <c r="D20" t="s">
+        <v>319</v>
+      </c>
+      <c r="E20">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A21">
+        <v>191</v>
+      </c>
+      <c r="B21" t="s">
+        <v>184</v>
+      </c>
+      <c r="C21" s="5">
+        <v>2164</v>
+      </c>
+      <c r="D21" t="s">
+        <v>319</v>
+      </c>
+      <c r="E21">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A22">
+        <v>192</v>
+      </c>
+      <c r="B22" t="s">
+        <v>185</v>
+      </c>
+      <c r="C22" s="5">
+        <v>2164</v>
+      </c>
+      <c r="D22" t="s">
+        <v>319</v>
+      </c>
+      <c r="E22">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A23">
+        <v>128</v>
+      </c>
+      <c r="B23" t="s">
+        <v>124</v>
+      </c>
+      <c r="C23" s="5">
+        <v>2716</v>
+      </c>
+      <c r="D23" t="s">
+        <v>279</v>
+      </c>
+      <c r="E23">
+        <v>24</v>
+      </c>
+      <c r="F23" t="s">
+        <v>433</v>
+      </c>
+      <c r="G23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A24">
+        <v>131</v>
+      </c>
+      <c r="B24" t="s">
+        <v>127</v>
+      </c>
+      <c r="C24" s="5">
+        <v>8272</v>
+      </c>
+      <c r="D24" t="s">
+        <v>313</v>
+      </c>
+      <c r="E24">
+        <v>40</v>
+      </c>
+      <c r="F24" t="s">
+        <v>434</v>
+      </c>
+      <c r="G24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A25" s="3">
+        <v>14</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C25" s="9" t="s">
+        <v>362</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="E25" s="3">
+        <v>14</v>
+      </c>
+      <c r="G25" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A26">
+        <v>181</v>
+      </c>
+      <c r="B26" t="s">
+        <v>175</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>364</v>
+      </c>
+      <c r="D26" t="s">
+        <v>329</v>
+      </c>
+      <c r="E26">
+        <v>24</v>
+      </c>
+      <c r="F26" s="8" t="s">
+        <v>428</v>
+      </c>
+      <c r="G26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A27">
+        <v>93</v>
+      </c>
+      <c r="B27" t="s">
+        <v>91</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>373</v>
+      </c>
+      <c r="D27" t="s">
+        <v>305</v>
+      </c>
+      <c r="E27">
+        <v>24</v>
+      </c>
+      <c r="F27" s="8" t="s">
+        <v>429</v>
+      </c>
+      <c r="G27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A28">
+        <v>210</v>
+      </c>
+      <c r="B28" t="s">
+        <v>201</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>387</v>
+      </c>
+      <c r="D28" t="s">
+        <v>332</v>
+      </c>
+      <c r="E28">
+        <v>14</v>
+      </c>
+      <c r="F28" t="s">
+        <v>430</v>
+      </c>
+      <c r="G28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A29">
+        <v>23</v>
+      </c>
+      <c r="B29" t="s">
+        <v>24</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>354</v>
+      </c>
+      <c r="D29" t="s">
+        <v>287</v>
+      </c>
+      <c r="E29">
+        <v>14</v>
+      </c>
+      <c r="F29" s="8" t="s">
+        <v>435</v>
+      </c>
+      <c r="G29">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A30">
+        <v>6</v>
+      </c>
+      <c r="B30" t="s">
+        <v>8</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>354</v>
+      </c>
+      <c r="D30" t="s">
+        <v>274</v>
+      </c>
+      <c r="E30">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A31">
+        <v>76</v>
+      </c>
+      <c r="B31" t="s">
+        <v>74</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>354</v>
+      </c>
+      <c r="D31" t="s">
+        <v>274</v>
+      </c>
+      <c r="E31">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A32">
+        <v>103</v>
+      </c>
+      <c r="B32" t="s">
+        <v>101</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>354</v>
+      </c>
+      <c r="D32" t="s">
+        <v>306</v>
+      </c>
+      <c r="E32">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A33">
+        <v>217</v>
+      </c>
+      <c r="B33" t="s">
+        <v>208</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>354</v>
+      </c>
+      <c r="D33" t="s">
+        <v>274</v>
+      </c>
+      <c r="E33">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A34">
+        <v>208</v>
+      </c>
+      <c r="B34" t="s">
+        <v>199</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>354</v>
+      </c>
+      <c r="D34" t="s">
+        <v>290</v>
+      </c>
+      <c r="E34">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A35">
+        <v>211</v>
+      </c>
+      <c r="B35" t="s">
+        <v>202</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>354</v>
+      </c>
+      <c r="D35" t="s">
+        <v>274</v>
+      </c>
+      <c r="E35">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A36">
+        <v>18</v>
+      </c>
+      <c r="B36" t="s">
+        <v>19</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>375</v>
+      </c>
+      <c r="D36" t="s">
+        <v>285</v>
+      </c>
+      <c r="E36">
+        <v>14</v>
+      </c>
+      <c r="F36" s="8" t="s">
+        <v>436</v>
+      </c>
+      <c r="G36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A37">
+        <v>263</v>
+      </c>
+      <c r="B37" t="s">
+        <v>252</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>356</v>
+      </c>
+      <c r="D37" t="s">
+        <v>333</v>
+      </c>
+      <c r="E37">
+        <v>14</v>
+      </c>
+      <c r="F37" s="8" t="s">
+        <v>437</v>
+      </c>
+      <c r="G37">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A38">
+        <v>7</v>
+      </c>
+      <c r="B38" t="s">
+        <v>9</v>
+      </c>
+      <c r="C38" s="5" t="s">
+        <v>356</v>
+      </c>
+      <c r="D38" t="s">
+        <v>275</v>
+      </c>
+      <c r="E38">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A39">
+        <v>13</v>
+      </c>
+      <c r="B39" t="s">
+        <v>15</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>356</v>
+      </c>
+      <c r="D39" t="s">
+        <v>275</v>
+      </c>
+      <c r="E39">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A40">
+        <v>137</v>
+      </c>
+      <c r="B40" t="s">
+        <v>133</v>
+      </c>
+      <c r="C40" s="5" t="s">
+        <v>356</v>
+      </c>
+      <c r="D40" t="s">
+        <v>275</v>
+      </c>
+      <c r="E40">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A41">
+        <v>214</v>
+      </c>
+      <c r="B41" t="s">
+        <v>205</v>
+      </c>
+      <c r="C41" s="5" t="s">
+        <v>356</v>
+      </c>
+      <c r="D41" t="s">
+        <v>333</v>
+      </c>
+      <c r="E41">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A42">
+        <v>212</v>
+      </c>
+      <c r="B42" t="s">
+        <v>203</v>
+      </c>
+      <c r="C42" s="5" t="s">
+        <v>356</v>
+      </c>
+      <c r="D42" t="s">
+        <v>333</v>
+      </c>
+      <c r="E42">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A43">
+        <v>215</v>
+      </c>
+      <c r="B43" t="s">
+        <v>206</v>
+      </c>
+      <c r="C43" s="5" t="s">
+        <v>384</v>
+      </c>
+      <c r="D43" t="s">
+        <v>334</v>
+      </c>
+      <c r="E43">
+        <v>14</v>
+      </c>
+      <c r="F43" s="8" t="s">
+        <v>438</v>
+      </c>
+      <c r="G43">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A44">
+        <v>55</v>
+      </c>
+      <c r="B44" t="s">
+        <v>54</v>
+      </c>
+      <c r="C44" s="5" t="s">
+        <v>350</v>
+      </c>
+      <c r="D44" t="s">
+        <v>301</v>
+      </c>
+      <c r="E44">
+        <v>16</v>
+      </c>
+      <c r="F44" s="8" t="s">
+        <v>439</v>
+      </c>
+      <c r="G44">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A45">
+        <v>173</v>
+      </c>
+      <c r="B45" t="s">
+        <v>167</v>
+      </c>
+      <c r="C45" s="5" t="s">
+        <v>350</v>
+      </c>
+      <c r="D45" t="s">
+        <v>301</v>
+      </c>
+      <c r="E45">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A46">
+        <v>209</v>
+      </c>
+      <c r="B46" t="s">
+        <v>200</v>
+      </c>
+      <c r="C46" s="5" t="s">
+        <v>349</v>
+      </c>
+      <c r="D46" t="s">
+        <v>331</v>
+      </c>
+      <c r="E46">
+        <v>14</v>
+      </c>
+      <c r="F46" s="8" t="s">
+        <v>440</v>
+      </c>
+      <c r="G46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A47">
+        <v>170</v>
+      </c>
+      <c r="B47" t="s">
+        <v>164</v>
+      </c>
+      <c r="C47" s="5" t="s">
+        <v>360</v>
+      </c>
+      <c r="D47" t="s">
+        <v>325</v>
+      </c>
+      <c r="E47">
+        <v>16</v>
+      </c>
+      <c r="F47" s="8" t="s">
+        <v>441</v>
+      </c>
+      <c r="G47">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A48">
+        <v>171</v>
+      </c>
+      <c r="B48" t="s">
+        <v>165</v>
+      </c>
+      <c r="C48" s="5" t="s">
+        <v>360</v>
+      </c>
+      <c r="D48" t="s">
+        <v>326</v>
+      </c>
+      <c r="E48">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A49">
+        <v>56</v>
+      </c>
+      <c r="B49" t="s">
+        <v>55</v>
+      </c>
+      <c r="C49" s="5" t="s">
+        <v>351</v>
+      </c>
+      <c r="D49" t="s">
+        <v>300</v>
+      </c>
+      <c r="E49">
+        <v>14</v>
+      </c>
+      <c r="F49" s="8" t="s">
+        <v>442</v>
+      </c>
+      <c r="G49">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A50">
+        <v>120</v>
+      </c>
+      <c r="B50" t="s">
+        <v>117</v>
+      </c>
+      <c r="C50" s="5" t="s">
+        <v>351</v>
+      </c>
+      <c r="D50"/>
+      <c r="E50">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A51">
+        <v>126</v>
+      </c>
+      <c r="B51" t="s">
+        <v>122</v>
+      </c>
+      <c r="C51" s="5" t="s">
+        <v>390</v>
+      </c>
+      <c r="D51" t="s">
+        <v>311</v>
+      </c>
+      <c r="E51">
+        <v>16</v>
+      </c>
+      <c r="F51" s="8" t="s">
+        <v>443</v>
+      </c>
+      <c r="G51">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A52">
+        <v>202</v>
+      </c>
+      <c r="B52" t="s">
+        <v>194</v>
+      </c>
+      <c r="C52" s="5" t="s">
+        <v>390</v>
+      </c>
+      <c r="D52" t="s">
+        <v>311</v>
+      </c>
+      <c r="E52">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A53">
+        <v>132</v>
+      </c>
+      <c r="B53" t="s">
+        <v>128</v>
+      </c>
+      <c r="C53" s="5" t="s">
+        <v>372</v>
+      </c>
+      <c r="D53" t="s">
+        <v>314</v>
+      </c>
+      <c r="E53">
+        <v>14</v>
+      </c>
+      <c r="F53" s="8" t="s">
+        <v>444</v>
+      </c>
+      <c r="G53">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A54">
+        <v>58</v>
+      </c>
+      <c r="B54" t="s">
+        <v>57</v>
+      </c>
+      <c r="C54" s="5" t="s">
+        <v>353</v>
+      </c>
+      <c r="D54" t="s">
+        <v>299</v>
+      </c>
+      <c r="E54">
+        <v>20</v>
+      </c>
+      <c r="F54" s="8" t="s">
+        <v>445</v>
+      </c>
+      <c r="G54">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A55">
+        <v>59</v>
+      </c>
+      <c r="B55" t="s">
+        <v>58</v>
+      </c>
+      <c r="C55" s="5" t="s">
+        <v>353</v>
+      </c>
+      <c r="D55" t="s">
+        <v>299</v>
+      </c>
+      <c r="E55">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A56">
+        <v>49</v>
+      </c>
+      <c r="B56" t="s">
+        <v>48</v>
+      </c>
+      <c r="C56" s="5" t="s">
+        <v>353</v>
+      </c>
+      <c r="D56" t="s">
+        <v>289</v>
+      </c>
+      <c r="E56">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A57">
+        <v>30</v>
+      </c>
+      <c r="B57" t="s">
+        <v>30</v>
+      </c>
+      <c r="C57" s="5" t="s">
+        <v>353</v>
+      </c>
+      <c r="D57" t="s">
+        <v>284</v>
+      </c>
+      <c r="E57">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A58">
+        <v>31</v>
+      </c>
+      <c r="B58" t="s">
+        <v>31</v>
+      </c>
+      <c r="C58" s="5" t="s">
+        <v>353</v>
+      </c>
+      <c r="D58" t="s">
+        <v>284</v>
+      </c>
+      <c r="E58">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A59">
+        <v>21</v>
+      </c>
+      <c r="B59" t="s">
+        <v>22</v>
+      </c>
+      <c r="C59" s="5" t="s">
+        <v>353</v>
+      </c>
+      <c r="D59" t="s">
+        <v>289</v>
+      </c>
+      <c r="E59">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A60">
+        <v>22</v>
+      </c>
+      <c r="B60" t="s">
+        <v>23</v>
+      </c>
+      <c r="C60" s="5" t="s">
+        <v>353</v>
+      </c>
+      <c r="D60" t="s">
+        <v>289</v>
+      </c>
+      <c r="E60">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A61">
+        <v>113</v>
+      </c>
+      <c r="B61" t="s">
+        <v>110</v>
+      </c>
+      <c r="C61" s="5" t="s">
+        <v>353</v>
+      </c>
+      <c r="D61" t="s">
+        <v>289</v>
+      </c>
+      <c r="E61">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A62">
+        <v>84</v>
+      </c>
+      <c r="B62" t="s">
+        <v>82</v>
+      </c>
+      <c r="C62" s="5" t="s">
+        <v>353</v>
+      </c>
+      <c r="D62" t="s">
+        <v>289</v>
+      </c>
+      <c r="E62">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A63">
+        <v>26</v>
+      </c>
+      <c r="B63" t="s">
+        <v>26</v>
+      </c>
+      <c r="C63" s="5" t="s">
+        <v>353</v>
+      </c>
+      <c r="D63" t="s">
+        <v>284</v>
+      </c>
+      <c r="E63">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A64">
+        <v>27</v>
+      </c>
+      <c r="B64" t="s">
+        <v>27</v>
+      </c>
+      <c r="C64" s="5" t="s">
+        <v>353</v>
+      </c>
+      <c r="D64" t="s">
+        <v>289</v>
+      </c>
+      <c r="E64">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A65">
+        <v>168</v>
+      </c>
+      <c r="B65" t="s">
+        <v>162</v>
+      </c>
+      <c r="C65" s="5" t="s">
+        <v>353</v>
+      </c>
+      <c r="D65" t="s">
+        <v>289</v>
+      </c>
+      <c r="E65">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A66">
+        <v>16</v>
+      </c>
+      <c r="B66" t="s">
+        <v>17</v>
+      </c>
+      <c r="C66" s="5" t="s">
+        <v>353</v>
+      </c>
+      <c r="D66" t="s">
+        <v>284</v>
+      </c>
+      <c r="E66">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A67">
+        <v>17</v>
+      </c>
+      <c r="B67" t="s">
+        <v>18</v>
+      </c>
+      <c r="C67" s="5" t="s">
+        <v>353</v>
+      </c>
+      <c r="D67" t="s">
+        <v>284</v>
+      </c>
+      <c r="E67">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A68">
+        <v>260</v>
+      </c>
+      <c r="B68" t="s">
+        <v>249</v>
+      </c>
+      <c r="C68" s="5" t="s">
+        <v>385</v>
+      </c>
+      <c r="D68" t="s">
+        <v>338</v>
+      </c>
+      <c r="E68">
+        <v>14</v>
+      </c>
+      <c r="F68" s="8" t="s">
+        <v>446</v>
+      </c>
+      <c r="G68">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A69">
+        <v>4</v>
+      </c>
+      <c r="B69" t="s">
+        <v>6</v>
+      </c>
+      <c r="C69" s="5" t="s">
+        <v>386</v>
+      </c>
+      <c r="D69" t="s">
+        <v>273</v>
+      </c>
+      <c r="E69">
+        <v>14</v>
+      </c>
+      <c r="F69" s="8" t="s">
+        <v>447</v>
+      </c>
+      <c r="G69">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A70">
+        <v>216</v>
+      </c>
+      <c r="B70" t="s">
+        <v>207</v>
+      </c>
+      <c r="C70" s="5" t="s">
+        <v>386</v>
+      </c>
+      <c r="D70" t="s">
+        <v>273</v>
+      </c>
+      <c r="E70">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A71">
+        <v>219</v>
+      </c>
+      <c r="B71" t="s">
+        <v>210</v>
+      </c>
+      <c r="C71" s="5" t="s">
+        <v>386</v>
+      </c>
+      <c r="D71" t="s">
+        <v>273</v>
+      </c>
+      <c r="E71">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A72">
+        <v>220</v>
+      </c>
+      <c r="B72" t="s">
+        <v>211</v>
+      </c>
+      <c r="C72" s="5" t="s">
+        <v>386</v>
+      </c>
+      <c r="D72" t="s">
+        <v>273</v>
+      </c>
+      <c r="E72">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A73">
+        <v>94</v>
+      </c>
+      <c r="B73" t="s">
+        <v>92</v>
+      </c>
+      <c r="C73" s="5" t="s">
+        <v>361</v>
+      </c>
+      <c r="D73" t="s">
+        <v>303</v>
+      </c>
+      <c r="E73">
+        <v>14</v>
+      </c>
+      <c r="F73" s="8" t="s">
+        <v>448</v>
+      </c>
+      <c r="G73">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A74">
+        <v>77</v>
+      </c>
+      <c r="B74" t="s">
+        <v>75</v>
+      </c>
+      <c r="C74" s="5" t="s">
+        <v>361</v>
+      </c>
+      <c r="D74" t="s">
+        <v>302</v>
+      </c>
+      <c r="E74">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A75">
+        <v>78</v>
+      </c>
+      <c r="B75" t="s">
+        <v>76</v>
+      </c>
+      <c r="C75" s="5" t="s">
+        <v>361</v>
+      </c>
+      <c r="D75" t="s">
+        <v>303</v>
+      </c>
+      <c r="E75">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A76">
+        <v>136</v>
+      </c>
+      <c r="B76" t="s">
+        <v>132</v>
+      </c>
+      <c r="C76" s="5" t="s">
+        <v>361</v>
+      </c>
+      <c r="D76" t="s">
+        <v>303</v>
+      </c>
+      <c r="E76">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A77">
+        <v>133</v>
+      </c>
+      <c r="B77" t="s">
+        <v>129</v>
+      </c>
+      <c r="C77" s="5" t="s">
+        <v>361</v>
+      </c>
+      <c r="D77" t="s">
+        <v>303</v>
+      </c>
+      <c r="E77">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A78">
+        <v>218</v>
+      </c>
+      <c r="B78" t="s">
+        <v>209</v>
+      </c>
+      <c r="C78" s="5" t="s">
+        <v>361</v>
+      </c>
+      <c r="D78" t="s">
+        <v>279</v>
+      </c>
+      <c r="E78">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A79">
+        <v>50</v>
+      </c>
+      <c r="B79" t="s">
+        <v>49</v>
+      </c>
+      <c r="C79" s="5" t="s">
+        <v>352</v>
+      </c>
+      <c r="D79" t="s">
+        <v>297</v>
+      </c>
+      <c r="E79">
+        <v>16</v>
+      </c>
+      <c r="F79" s="8" t="s">
+        <v>449</v>
+      </c>
+      <c r="G79">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A80">
+        <v>29</v>
+      </c>
+      <c r="B80" t="s">
+        <v>29</v>
+      </c>
+      <c r="C80" s="5" t="s">
+        <v>352</v>
+      </c>
+      <c r="D80" t="s">
+        <v>291</v>
+      </c>
+      <c r="E80">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A81">
+        <v>167</v>
+      </c>
+      <c r="B81" t="s">
+        <v>161</v>
+      </c>
+      <c r="C81" s="5" t="s">
+        <v>383</v>
+      </c>
+      <c r="D81" t="s">
+        <v>322</v>
+      </c>
+      <c r="E81">
+        <v>20</v>
+      </c>
+      <c r="F81" t="s">
+        <v>424</v>
+      </c>
+      <c r="G81">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A82">
+        <v>123</v>
+      </c>
+      <c r="B82" t="s">
+        <v>120</v>
+      </c>
+      <c r="C82" s="5" t="s">
+        <v>388</v>
+      </c>
+      <c r="D82" t="s">
+        <v>310</v>
+      </c>
+      <c r="E82">
+        <v>14</v>
+      </c>
+      <c r="F82" s="8" t="s">
+        <v>450</v>
+      </c>
+      <c r="G82">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A83">
+        <v>124</v>
+      </c>
+      <c r="B83" t="s">
+        <v>121</v>
+      </c>
+      <c r="C83" s="5" t="s">
+        <v>388</v>
+      </c>
+      <c r="D83" t="s">
+        <v>310</v>
+      </c>
+      <c r="E83">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A84">
+        <v>122</v>
+      </c>
+      <c r="B84" t="s">
+        <v>119</v>
+      </c>
+      <c r="C84" s="5" t="s">
+        <v>388</v>
+      </c>
+      <c r="D84" t="s">
+        <v>310</v>
+      </c>
+      <c r="E84">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A85">
+        <v>206</v>
+      </c>
+      <c r="B85" t="s">
+        <v>197</v>
+      </c>
+      <c r="C85" s="5" t="s">
+        <v>389</v>
+      </c>
+      <c r="D85" t="s">
+        <v>330</v>
+      </c>
+      <c r="E85">
+        <v>14</v>
+      </c>
+      <c r="F85" s="8" t="s">
+        <v>451</v>
+      </c>
+      <c r="G85">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A86">
+        <v>82</v>
+      </c>
+      <c r="B86" t="s">
+        <v>80</v>
+      </c>
+      <c r="C86" s="5" t="s">
+        <v>409</v>
+      </c>
+      <c r="D86" t="s">
+        <v>304</v>
+      </c>
+      <c r="E86">
+        <v>16</v>
+      </c>
+      <c r="F86" s="8" t="s">
+        <v>452</v>
+      </c>
+      <c r="G86">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A87">
+        <v>177</v>
+      </c>
+      <c r="B87" t="s">
+        <v>171</v>
+      </c>
+      <c r="C87" s="5" t="s">
+        <v>415</v>
+      </c>
+      <c r="D87" t="s">
+        <v>328</v>
+      </c>
+      <c r="E87">
+        <v>16</v>
+      </c>
+      <c r="F87" s="8" t="s">
+        <v>453</v>
+      </c>
+      <c r="G87">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A88">
+        <v>258</v>
+      </c>
+      <c r="B88" t="s">
+        <v>247</v>
+      </c>
+      <c r="C88" s="5" t="s">
+        <v>359</v>
+      </c>
+      <c r="D88" t="s">
+        <v>272</v>
+      </c>
+      <c r="E88">
+        <v>14</v>
+      </c>
+      <c r="F88" s="8" t="s">
+        <v>454</v>
+      </c>
+      <c r="G88">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A89">
+        <v>259</v>
+      </c>
+      <c r="B89" t="s">
+        <v>248</v>
+      </c>
+      <c r="C89" s="5" t="s">
+        <v>359</v>
+      </c>
+      <c r="D89" t="s">
+        <v>272</v>
+      </c>
+      <c r="E89">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A90">
+        <v>261</v>
+      </c>
+      <c r="B90" t="s">
+        <v>250</v>
+      </c>
+      <c r="C90" s="5" t="s">
+        <v>359</v>
+      </c>
+      <c r="D90" t="s">
+        <v>272</v>
+      </c>
+      <c r="E90">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A91">
+        <v>262</v>
+      </c>
+      <c r="B91" t="s">
+        <v>251</v>
+      </c>
+      <c r="C91" s="5" t="s">
+        <v>359</v>
+      </c>
+      <c r="D91" t="s">
+        <v>272</v>
+      </c>
+      <c r="E91">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A92">
+        <v>5</v>
+      </c>
+      <c r="B92" t="s">
+        <v>7</v>
+      </c>
+      <c r="C92" s="5" t="s">
+        <v>359</v>
+      </c>
+      <c r="D92" t="s">
+        <v>272</v>
+      </c>
+      <c r="E92">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A93">
+        <v>40</v>
+      </c>
+      <c r="B93" t="s">
+        <v>41</v>
+      </c>
+      <c r="C93" s="5" t="s">
+        <v>359</v>
+      </c>
+      <c r="D93" t="s">
+        <v>296</v>
+      </c>
+      <c r="E93">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A94">
+        <v>201</v>
+      </c>
+      <c r="B94" t="s">
+        <v>193</v>
+      </c>
+      <c r="C94" s="5" t="s">
+        <v>359</v>
+      </c>
+      <c r="D94" t="s">
+        <v>272</v>
+      </c>
+      <c r="E94">
+        <v>14</v>
+      </c>
+      <c r="F94" s="7"/>
+    </row>
+    <row r="95" spans="1:7" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A95">
+        <v>266</v>
+      </c>
+      <c r="B95" t="s">
+        <v>254</v>
+      </c>
+      <c r="C95" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="D95" t="s">
+        <v>341</v>
+      </c>
+      <c r="E95">
+        <v>14</v>
+      </c>
+      <c r="F95" s="8" t="s">
+        <v>455</v>
+      </c>
+      <c r="G95">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A96">
+        <v>25</v>
+      </c>
+      <c r="B96" t="s">
+        <v>25</v>
+      </c>
+      <c r="C96" s="5" t="s">
+        <v>346</v>
+      </c>
+      <c r="D96" t="s">
+        <v>290</v>
+      </c>
+      <c r="E96">
+        <v>14</v>
+      </c>
+      <c r="F96" t="s">
+        <v>456</v>
+      </c>
+      <c r="G96">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A97">
+        <v>129</v>
+      </c>
+      <c r="B97" t="s">
+        <v>126</v>
+      </c>
+      <c r="C97" s="5" t="s">
+        <v>397</v>
+      </c>
+      <c r="D97" t="s">
+        <v>312</v>
+      </c>
+      <c r="E97">
+        <v>20</v>
+      </c>
+      <c r="F97" t="s">
+        <v>457</v>
+      </c>
+      <c r="G97">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A98">
+        <v>172</v>
+      </c>
+      <c r="B98" t="s">
+        <v>166</v>
+      </c>
+      <c r="C98" s="5" t="s">
+        <v>396</v>
+      </c>
+      <c r="D98" t="s">
+        <v>327</v>
+      </c>
+      <c r="E98">
+        <v>18</v>
+      </c>
+      <c r="F98" t="s">
+        <v>458</v>
+      </c>
+      <c r="G98">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A99">
+        <v>169</v>
+      </c>
+      <c r="B99" t="s">
+        <v>163</v>
+      </c>
+      <c r="C99" s="5" t="s">
+        <v>416</v>
+      </c>
+      <c r="D99" t="s">
+        <v>323</v>
+      </c>
+      <c r="E99">
+        <v>28</v>
+      </c>
+      <c r="F99" t="s">
+        <v>462</v>
+      </c>
+      <c r="G99">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A100">
+        <v>112</v>
+      </c>
+      <c r="B100" t="s">
+        <v>109</v>
+      </c>
+      <c r="C100" s="5" t="s">
+        <v>400</v>
+      </c>
+      <c r="D100" t="s">
+        <v>309</v>
+      </c>
+      <c r="E100">
+        <v>40</v>
+      </c>
+      <c r="F100" t="s">
+        <v>459</v>
+      </c>
+      <c r="G100">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A101">
+        <v>109</v>
+      </c>
+      <c r="B101" t="s">
+        <v>106</v>
+      </c>
+      <c r="C101" s="5" t="s">
+        <v>399</v>
+      </c>
+      <c r="D101" t="s">
+        <v>307</v>
+      </c>
+      <c r="E101">
+        <v>40</v>
+      </c>
+      <c r="F101" t="s">
+        <v>461</v>
+      </c>
+      <c r="G101">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A102">
+        <v>111</v>
+      </c>
+      <c r="B102" t="s">
+        <v>108</v>
+      </c>
+      <c r="C102" s="5" t="s">
+        <v>398</v>
+      </c>
+      <c r="D102" t="s">
+        <v>308</v>
+      </c>
+      <c r="E102">
+        <v>40</v>
+      </c>
+      <c r="F102" t="s">
+        <v>460</v>
+      </c>
+      <c r="G102">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:E244" xr:uid="{2A40BA8F-AFFC-4D60-89B3-F498D80C2CF3}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G104">
+    <sortCondition ref="C2:C104"/>
+    <sortCondition ref="E2:E104"/>
+  </sortState>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/sch/components.xlsx
+++ b/sch/components.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\miha\Desktop\vezje-idp\kicad\sch\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A0F370D-7E38-4250-AA97-6BC022227324}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86E4CDBD-65E1-4915-A169-D9BBBF55F73B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12552" tabRatio="773" xr2:uid="{6172FD7F-16CD-47D1-A3E4-D63AC8EC044E}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12552" tabRatio="773" activeTab="3" xr2:uid="{6172FD7F-16CD-47D1-A3E4-D63AC8EC044E}"/>
   </bookViews>
   <sheets>
     <sheet name="BOM" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2153" uniqueCount="577">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2154" uniqueCount="578">
   <si>
     <t>ID</t>
   </si>
@@ -1273,9 +1273,6 @@
   </si>
   <si>
     <t>Shop Link</t>
-  </si>
-  <si>
-    <t>https://www.ic-elect.si/ic-74ls374-dip20-flip-flop.html</t>
   </si>
   <si>
     <t>Value Ref 1</t>
@@ -1704,69 +1701,7 @@
     <t>5.1 K</t>
   </si>
   <si>
-    <t>https://www.ic-elect.si/upor-150r-0207-5-0-25w-cfr-25.html</t>
-  </si>
-  <si>
-    <t>https://www.ic-elect.si/upor-220r-0207-5-0-25w-cfr-25.html</t>
-  </si>
-  <si>
-    <t>https://www.ic-elect.si/upor-330r-0207-5-0-25w-cfr-25.html</t>
-  </si>
-  <si>
-    <t>https://www.ic-elect.si/upor-390r-0207-5-0-25w-cfr-25.html</t>
-  </si>
-  <si>
-    <t>https://www.ic-elect.si/upor-820r-0207-5-0-25w-cfr-25.html</t>
-  </si>
-  <si>
-    <t>https://www.ic-elect.si/upor-10k-0207-5-0-25w-cfr-25.html</t>
-  </si>
-  <si>
-    <t>https://eu.mouser.com/ProductDetail/KOA-Speer/RK1-4DCT52R1505F?qs=FsveJYYILCJecIT90En2dA%3D%3D
-https://eu.mouser.com/ProductDetail/SEI-Stackpole/RNV14FAL15M0?qs=FESYatJ8odI%2FJbrYyfXHXw%3D%3D</t>
-  </si>
-  <si>
-    <t>https://www.ic-elect.si/upor-1k-0207-5-0-25w-cfr-25.html</t>
-  </si>
-  <si>
-    <t>https://www.ic-elect.si/upor-1k5-0207-5-0-25w-cfr-25.html</t>
-  </si>
-  <si>
-    <t>https://www.ic-elect.si/upor-20k-0207-5-0-25w-cfr-25.html</t>
-  </si>
-  <si>
-    <t>https://www.ic-elect.si/upor-33r-0207-5-0-25w-cfr-25.html</t>
-  </si>
-  <si>
-    <t>https://www.ic-elect.si/upor-3k3-0207-5-0-25w-cfr-25.html</t>
-  </si>
-  <si>
-    <t>https://www.ic-elect.si/upor-47r-0207-5-0-25w-cfr-25.html</t>
-  </si>
-  <si>
-    <t>https://www.ic-elect.si/upor-47k-0207-5-0-25w-cfr-25.html</t>
-  </si>
-  <si>
-    <t>https://www.ic-elect.si/upor-4k7-0207-5-0-25w-cfr-25.html</t>
-  </si>
-  <si>
-    <t>https://www.ic-elect.si/upor-560r-0207-5-0-25w-cfr-25.html</t>
-  </si>
-  <si>
-    <t>https://www.ic-elect.si/upor-56r-0207-5-0-25w-cfr-25.html</t>
-  </si>
-  <si>
-    <t>https://www.ic-elect.si/upor-5k1-0207-5-0-25w-cfr-25.html</t>
-  </si>
-  <si>
-    <t>https://www.ic-elect.si/upor-68r-0207-5-0-25w-cfr-25.html</t>
-  </si>
-  <si>
     <t>Zener 2.7 V</t>
-  </si>
-  <si>
-    <t>https://www.ic-elect.si/zener-1-2w-2v7-do-35.html (1/4 W, 3.1-3.9 mm)
-[https://www.ic-elect.si/zener-1-3w-2v7-do-41.html (1.3 W, 4.1 mm)]</t>
   </si>
   <si>
     <t>Blue resistor (tolerance 1 or 2%)</t>
@@ -1799,6 +1734,72 @@
   </si>
   <si>
     <t>https://www.delko.si/sl/industrijska-36v-80-mah-ni-mh-polnilna-gp-baterija.html</t>
+  </si>
+  <si>
+    <t>https://eu.mouser.com/ProductDetail/YAGEO/CFR-25JR-52-68R?qs=gt1LBUVyoHm6An10nuV6tA%3D%3D</t>
+  </si>
+  <si>
+    <t>https://eu.mouser.com/ProductDetail/YAGEO/CFR-25JB-52-5K1?qs=oypCK0zG325u7aO1BrawZA%3D%3D</t>
+  </si>
+  <si>
+    <t>https://eu.mouser.com/ProductDetail/Texas-Instruments/SN74LS374N?qs=5h8QSfodyRhdi57F6aDgtA%3D%3D</t>
+  </si>
+  <si>
+    <t>https://eu.mouser.com/ProductDetail/YAGEO/CFR-25JR-52-150R?qs=19cKSROHwrCg%252Bkk55kO4wg%3D%3D</t>
+  </si>
+  <si>
+    <t>https://eu.mouser.com/ProductDetail/YAGEO/CFR-25JR-52-220R?qs=19cKSROHwrDd9peoB7SMkA%3D%3D</t>
+  </si>
+  <si>
+    <t>https://eu.mouser.com/ProductDetail/YAGEO/CFR-25JR-52-330R?qs=KUIzHt%2Fe91lTLFUOlcnheg%3D%3D</t>
+  </si>
+  <si>
+    <t>https://eu.mouser.com/ProductDetail/YAGEO/CFR-25JR-52-390R?qs=KUIzHt%2Fe91lGSy2ISVMHLA%3D%3D</t>
+  </si>
+  <si>
+    <t>https://eu.mouser.com/ProductDetail/YAGEO/CFR-25JT-52-820R?qs=KUIzHt%2Fe91nf0zePCO9VQg%3D%3D</t>
+  </si>
+  <si>
+    <t>https://eu.mouser.com/ProductDetail/YAGEO/CFR-25JB-52-10R?qs=2kOmHSv6VfRGU0i%252Br6puJQ%3D%3D</t>
+  </si>
+  <si>
+    <t>https://eu.mouser.com/ProductDetail/YAGEO/CFR-25JR-52-1K?qs=FK4oyhsNhknmd5zXOZ4mTQ%3D%3D</t>
+  </si>
+  <si>
+    <t>https://eu.mouser.com/ProductDetail/YAGEO/CFR-25JB-52-1K5?qs=%2F35zJ5USjokhRsfIrdvtSA%3D%3D</t>
+  </si>
+  <si>
+    <t>https://eu.mouser.com/ProductDetail/YAGEO/CFR-25JR-52-20K?qs=19cKSROHwrBYX3RisskriA%3D%3D</t>
+  </si>
+  <si>
+    <t>https://eu.mouser.com/ProductDetail/YAGEO/CFR-25JB-52-33R?qs=oypCK0zG324sJ2xUpnz%2FXg%3D%3D</t>
+  </si>
+  <si>
+    <t>https://eu.mouser.com/ProductDetail/YAGEO/CFR-25JR-52-3K3?qs=19cKSROHwrAt1R6Bf0Zq3Q%3D%3D</t>
+  </si>
+  <si>
+    <t>https://eu.mouser.com/ProductDetail/YAGEO/CFR-25JR-52-47R?qs=b3QwWlrdtsujDBo8o1s8iQ%3D%3D</t>
+  </si>
+  <si>
+    <t>https://eu.mouser.com/ProductDetail/YAGEO/CFR-25JB-52-47K?qs=2kOmHSv6VfThFUpI%252B9lRAg%3D%3D</t>
+  </si>
+  <si>
+    <t>https://eu.mouser.com/ProductDetail/YAGEO/CFR-25JB-52-4K7?qs=oypCK0zG3252T%2FvSUvCH9g%3D%3D</t>
+  </si>
+  <si>
+    <t>https://eu.mouser.com/ProductDetail/YAGEO/CFR-25JT-52-560R?qs=KUIzHt%2Fe91mnjLaCZK7hbg%3D%3D</t>
+  </si>
+  <si>
+    <t>https://eu.mouser.com/ProductDetail/YAGEO/CFR-25JR-52-56R?qs=lfEcNZWccVmso0SeMV07sA%3D%3D</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>https://eu.mouser.com/ProductDetail/Vishay-Semiconductors/TZX2V7C-TR?qs=25SNtymhSqPE5w2ZtavYCQ%3D%3D</t>
+  </si>
+  <si>
+    <t>https://eu.mouser.com/ProductDetail/KOA-Speer/RK1-4DCT52R1505F?qs=FsveJYYILCJecIT90En2dA%3D%3D</t>
   </si>
 </sst>
 </file>
@@ -1862,7 +1863,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1878,6 +1879,14 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2235,13 +2244,13 @@
         <v>1</v>
       </c>
       <c r="J1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="K1" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="L1" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="M1" t="s">
         <v>406</v>
@@ -2277,7 +2286,7 @@
         <v>2.1</v>
       </c>
       <c r="J2" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.55000000000000004">
@@ -2304,7 +2313,7 @@
         <v>1.6</v>
       </c>
       <c r="J3" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="4" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
@@ -2399,7 +2408,7 @@
         <v>118</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -2418,7 +2427,7 @@
         <v>2.4</v>
       </c>
       <c r="J7" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.55000000000000004">
@@ -2451,7 +2460,7 @@
         <v>2.1</v>
       </c>
       <c r="J8" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="9" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
@@ -2511,7 +2520,7 @@
         <v>2.1</v>
       </c>
       <c r="J10" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="11" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
@@ -2767,7 +2776,7 @@
         <v>1.6</v>
       </c>
       <c r="J19" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.55000000000000004">
@@ -2800,7 +2809,7 @@
         <v>6.1</v>
       </c>
       <c r="J20" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.55000000000000004">
@@ -2893,7 +2902,7 @@
         <v>1.6</v>
       </c>
       <c r="J23" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.55000000000000004">
@@ -2941,7 +2950,7 @@
         <v>241</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="E25">
         <v>1</v>
@@ -2960,10 +2969,10 @@
         <v>6.1</v>
       </c>
       <c r="J25" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="M25" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.55000000000000004">
@@ -2990,7 +2999,7 @@
         <v>1.6</v>
       </c>
       <c r="J26" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.55000000000000004">
@@ -3023,7 +3032,7 @@
         <v>1.5</v>
       </c>
       <c r="J27" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.55000000000000004">
@@ -3056,7 +3065,7 @@
         <v>1.4</v>
       </c>
       <c r="J28" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.55000000000000004">
@@ -3070,7 +3079,7 @@
         <v>38</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="E29">
         <v>1</v>
@@ -3089,10 +3098,10 @@
         <v>1.4</v>
       </c>
       <c r="J29" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="M29" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.55000000000000004">
@@ -3125,7 +3134,7 @@
         <v>1.4</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="K30" s="2"/>
     </row>
@@ -3670,10 +3679,10 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="J49" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="K49" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.55000000000000004">
@@ -3781,7 +3790,7 @@
         <v>333</v>
       </c>
       <c r="K52" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.55000000000000004">
@@ -3886,10 +3895,10 @@
         <v>6.1</v>
       </c>
       <c r="J55" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="K55" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="L55" t="b">
         <f t="shared" ref="L55:L79" si="2">OR(ISNUMBER(SEARCH("LS", J55)),ISNUMBER(SEARCH("LS", K55)))</f>
@@ -4089,7 +4098,7 @@
         <v>295</v>
       </c>
       <c r="K60" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="L60" t="b">
         <f t="shared" si="2"/>
@@ -4129,7 +4138,7 @@
         <v>295</v>
       </c>
       <c r="K61" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="L61" t="b">
         <f t="shared" si="2"/>
@@ -4209,7 +4218,7 @@
         <v>285</v>
       </c>
       <c r="K63" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="L63" t="b">
         <f t="shared" si="2"/>
@@ -4286,10 +4295,10 @@
         <v>1.3</v>
       </c>
       <c r="J65" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="K65" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="L65" t="b">
         <f t="shared" si="2"/>
@@ -4326,10 +4335,10 @@
         <v>1.3</v>
       </c>
       <c r="J66" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="K66" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="L66" t="b">
         <f t="shared" si="2"/>
@@ -4369,7 +4378,7 @@
         <v>285</v>
       </c>
       <c r="K67" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="L67" t="b">
         <f t="shared" si="2"/>
@@ -4409,7 +4418,7 @@
         <v>296</v>
       </c>
       <c r="K68" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="L68" t="b">
         <f t="shared" si="2"/>
@@ -4449,7 +4458,7 @@
         <v>285</v>
       </c>
       <c r="K69" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="L69" t="b">
         <f t="shared" si="2"/>
@@ -4486,10 +4495,10 @@
         <v>1.2</v>
       </c>
       <c r="J70" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="K70" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="L70" t="b">
         <f t="shared" si="2"/>
@@ -4529,7 +4538,7 @@
         <v>272</v>
       </c>
       <c r="K71" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="L71" t="b">
         <f t="shared" si="2"/>
@@ -4627,7 +4636,7 @@
         <v>16</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="E74">
         <v>1</v>
@@ -4649,7 +4658,7 @@
         <v>278</v>
       </c>
       <c r="K74" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="L74" t="b">
         <f t="shared" si="2"/>
@@ -4686,10 +4695,10 @@
         <v>2.4</v>
       </c>
       <c r="J75" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="K75" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="L75" t="b">
         <f t="shared" si="2"/>
@@ -4726,10 +4735,10 @@
         <v>2.4</v>
       </c>
       <c r="J76" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="K76" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="L76" t="b">
         <f t="shared" si="2"/>
@@ -4766,10 +4775,10 @@
         <v>2.4</v>
       </c>
       <c r="J77" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="K77" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="L77" t="b">
         <f t="shared" si="2"/>
@@ -4809,7 +4818,7 @@
         <v>285</v>
       </c>
       <c r="K78" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="L78" t="b">
         <f t="shared" si="2"/>
@@ -4889,7 +4898,7 @@
         <v>302</v>
       </c>
       <c r="K80" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
     </row>
     <row r="81" spans="1:12" hidden="1" x14ac:dyDescent="0.55000000000000004">
@@ -4994,7 +5003,7 @@
         <v>304</v>
       </c>
       <c r="K83" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
     </row>
     <row r="84" spans="1:12" x14ac:dyDescent="0.55000000000000004">
@@ -5070,7 +5079,7 @@
         <v>300</v>
       </c>
       <c r="K85" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.55000000000000004">
@@ -5106,7 +5115,7 @@
         <v>272</v>
       </c>
       <c r="K86" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="L86" t="b">
         <f t="shared" ref="L86:L93" si="4">OR(ISNUMBER(SEARCH("LS", J86)),ISNUMBER(SEARCH("LS", K86)))</f>
@@ -5146,7 +5155,7 @@
         <v>301</v>
       </c>
       <c r="K87" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="L87" t="b">
         <f t="shared" si="4"/>
@@ -5183,7 +5192,7 @@
         <v>2.1</v>
       </c>
       <c r="J88" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="K88" t="s">
         <v>298</v>
@@ -5226,7 +5235,7 @@
         <v>285</v>
       </c>
       <c r="K89" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="L89" t="b">
         <f t="shared" si="4"/>
@@ -5266,7 +5275,7 @@
         <v>286</v>
       </c>
       <c r="K90" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="L90" t="b">
         <f t="shared" si="4"/>
@@ -5386,7 +5395,7 @@
         <v>296</v>
       </c>
       <c r="K93" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="L93" t="b">
         <f t="shared" si="4"/>
@@ -5426,7 +5435,7 @@
         <v>311</v>
       </c>
       <c r="K94" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
     </row>
     <row r="95" spans="1:12" x14ac:dyDescent="0.55000000000000004">
@@ -5462,7 +5471,7 @@
         <v>312</v>
       </c>
       <c r="K95" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
     </row>
     <row r="96" spans="1:12" x14ac:dyDescent="0.55000000000000004">
@@ -5614,7 +5623,7 @@
         <v>306</v>
       </c>
       <c r="K99" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="100" spans="1:13" x14ac:dyDescent="0.55000000000000004">
@@ -5687,10 +5696,10 @@
         <v>1.3</v>
       </c>
       <c r="J101" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="K101" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="L101" t="b">
         <f>OR(ISNUMBER(SEARCH("LS", J101)),ISNUMBER(SEARCH("LS", K101)))</f>
@@ -5802,7 +5811,7 @@
         <v>309</v>
       </c>
       <c r="K104" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="105" spans="1:13" x14ac:dyDescent="0.55000000000000004">
@@ -5838,7 +5847,7 @@
         <v>309</v>
       </c>
       <c r="K105" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="106" spans="1:13" x14ac:dyDescent="0.55000000000000004">
@@ -5914,7 +5923,7 @@
         <v>308</v>
       </c>
       <c r="K107" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="L107" t="b">
         <f>OR(ISNUMBER(SEARCH("LS", J107)),ISNUMBER(SEARCH("LS", K107)))</f>
@@ -5954,7 +5963,7 @@
         <v>307</v>
       </c>
       <c r="K108" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="109" spans="1:13" x14ac:dyDescent="0.55000000000000004">
@@ -5990,7 +5999,7 @@
         <v>320</v>
       </c>
       <c r="K109" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="110" spans="1:13" x14ac:dyDescent="0.55000000000000004">
@@ -6066,7 +6075,7 @@
         <v>313</v>
       </c>
       <c r="K111" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="112" spans="1:13" x14ac:dyDescent="0.55000000000000004">
@@ -6102,7 +6111,7 @@
         <v>285</v>
       </c>
       <c r="K112" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="L112" t="b">
         <f>OR(ISNUMBER(SEARCH("LS", J112)),ISNUMBER(SEARCH("LS", K112)))</f>
@@ -6359,7 +6368,7 @@
         <v>285</v>
       </c>
       <c r="K119" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="L119" t="b">
         <f>OR(ISNUMBER(SEARCH("LS", J119)),ISNUMBER(SEARCH("LS", K119)))</f>
@@ -6399,7 +6408,7 @@
         <v>317</v>
       </c>
       <c r="K120" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="121" spans="1:12" x14ac:dyDescent="0.55000000000000004">
@@ -6432,7 +6441,7 @@
         <v>4.2</v>
       </c>
       <c r="J121" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="K121" t="s">
         <v>319</v>
@@ -6475,7 +6484,7 @@
         <v>319</v>
       </c>
       <c r="K122" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="L122" t="b">
         <f>OR(ISNUMBER(SEARCH("LS", J122)),ISNUMBER(SEARCH("LS", K122)))</f>
@@ -6512,10 +6521,10 @@
         <v>1.2</v>
       </c>
       <c r="J123" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="K123" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="L123" t="b">
         <f>OR(ISNUMBER(SEARCH("LS", J123)),ISNUMBER(SEARCH("LS", K123)))</f>
@@ -6595,7 +6604,7 @@
         <v>313</v>
       </c>
       <c r="K125" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="126" spans="1:12" x14ac:dyDescent="0.55000000000000004">
@@ -6882,10 +6891,10 @@
         <v>5.3</v>
       </c>
       <c r="J133" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="K133" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="L133" t="b">
         <f t="shared" si="6"/>
@@ -6922,10 +6931,10 @@
         <v>1.2</v>
       </c>
       <c r="J134" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="K134" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="L134" t="b">
         <f t="shared" si="6"/>
@@ -6965,7 +6974,7 @@
         <v>272</v>
       </c>
       <c r="K135" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="L135" t="b">
         <f t="shared" si="6"/>
@@ -7045,7 +7054,7 @@
         <v>286</v>
       </c>
       <c r="K137" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="L137" t="b">
         <f t="shared" si="6"/>
@@ -7165,7 +7174,7 @@
         <v>313</v>
       </c>
       <c r="K140" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="141" spans="1:12" x14ac:dyDescent="0.55000000000000004">
@@ -7342,7 +7351,7 @@
         <v>282</v>
       </c>
       <c r="K145" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="L145" t="b">
         <f>OR(ISNUMBER(SEARCH("LS", J145)),ISNUMBER(SEARCH("LS", K145)))</f>
@@ -7412,7 +7421,7 @@
         <v>5.3</v>
       </c>
       <c r="J147" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="K147" t="s">
         <v>298</v>
@@ -7452,10 +7461,10 @@
         <v>5.3</v>
       </c>
       <c r="J148" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="K148" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="L148" t="b">
         <f t="shared" si="7"/>
@@ -7492,10 +7501,10 @@
         <v>5.3</v>
       </c>
       <c r="J149" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="K149" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="L149" t="b">
         <f t="shared" si="7"/>
@@ -7535,7 +7544,7 @@
         <v>272</v>
       </c>
       <c r="K150" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="L150" t="b">
         <f t="shared" si="7"/>
@@ -7575,7 +7584,7 @@
         <v>324</v>
       </c>
       <c r="K151" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="L151" t="b">
         <f t="shared" si="7"/>
@@ -7615,7 +7624,7 @@
         <v>323</v>
       </c>
       <c r="K152" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="L152" t="b">
         <f t="shared" si="7"/>
@@ -7695,7 +7704,7 @@
         <v>313</v>
       </c>
       <c r="K154" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="155" spans="1:12" x14ac:dyDescent="0.55000000000000004">
@@ -7731,7 +7740,7 @@
         <v>313</v>
       </c>
       <c r="K155" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="156" spans="1:12" x14ac:dyDescent="0.55000000000000004">
@@ -8497,7 +8506,7 @@
         <v>1.5</v>
       </c>
       <c r="J182" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="183" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -8530,7 +8539,7 @@
         <v>1.4</v>
       </c>
       <c r="J183" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="184" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -8695,7 +8704,7 @@
         <v>1.4</v>
       </c>
       <c r="J188" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="189" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -8893,10 +8902,10 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="J194" t="s">
+        <v>474</v>
+      </c>
+      <c r="M194" t="s">
         <v>475</v>
-      </c>
-      <c r="M194" t="s">
-        <v>476</v>
       </c>
     </row>
     <row r="195" spans="1:13" x14ac:dyDescent="0.55000000000000004">
@@ -8929,7 +8938,7 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="J195" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="196" spans="1:13" x14ac:dyDescent="0.55000000000000004">
@@ -8965,7 +8974,7 @@
         <v>318</v>
       </c>
       <c r="M196" t="s">
-        <v>567</v>
+        <v>546</v>
       </c>
     </row>
     <row r="197" spans="1:13" x14ac:dyDescent="0.55000000000000004">
@@ -8998,7 +9007,7 @@
         <v>1.4</v>
       </c>
       <c r="J197" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="198" spans="1:13" x14ac:dyDescent="0.55000000000000004">
@@ -9478,7 +9487,7 @@
         <v>2.4</v>
       </c>
       <c r="J213" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="214" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -9511,7 +9520,7 @@
         <v>2.4</v>
       </c>
       <c r="J214" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="215" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -9544,7 +9553,7 @@
         <v>2.4</v>
       </c>
       <c r="J215" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="216" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -9610,7 +9619,7 @@
         <v>2.4</v>
       </c>
       <c r="J217" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="218" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -9643,7 +9652,7 @@
         <v>2.4</v>
       </c>
       <c r="J218" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="219" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -9676,7 +9685,7 @@
         <v>2.4</v>
       </c>
       <c r="J219" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="220" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -10072,7 +10081,7 @@
         <v>4.2</v>
       </c>
       <c r="J231" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="232" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -11182,7 +11191,7 @@
         <v>5.4</v>
       </c>
       <c r="J265" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="266" spans="1:13" x14ac:dyDescent="0.55000000000000004">
@@ -11281,7 +11290,7 @@
         <v>6.1</v>
       </c>
       <c r="J268" s="2" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="K268" s="2"/>
     </row>
@@ -11414,10 +11423,10 @@
         <v>5.2</v>
       </c>
       <c r="J272" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="M272" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="273" spans="1:13" x14ac:dyDescent="0.55000000000000004">
@@ -11450,10 +11459,10 @@
         <v>5.2</v>
       </c>
       <c r="J273" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="M273" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="274" spans="1:13" hidden="1" x14ac:dyDescent="0.55000000000000004">
@@ -11579,7 +11588,7 @@
         <v>6.1</v>
       </c>
       <c r="J277" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="278" spans="1:13" x14ac:dyDescent="0.55000000000000004">
@@ -11593,7 +11602,7 @@
         <v>78</v>
       </c>
       <c r="D278" s="2" t="s">
-        <v>568</v>
+        <v>547</v>
       </c>
       <c r="E278">
         <v>1</v>
@@ -11612,7 +11621,7 @@
         <v>2.1</v>
       </c>
       <c r="J278" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="279" spans="1:13" x14ac:dyDescent="0.55000000000000004">
@@ -11626,7 +11635,7 @@
         <v>79</v>
       </c>
       <c r="D279" s="2" t="s">
-        <v>568</v>
+        <v>547</v>
       </c>
       <c r="E279">
         <v>1</v>
@@ -11645,7 +11654,7 @@
         <v>2.1</v>
       </c>
       <c r="J279" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="280" spans="1:13" x14ac:dyDescent="0.55000000000000004">
@@ -11893,7 +11902,7 @@
         <v>409</v>
       </c>
       <c r="D1" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="E1" t="s">
         <v>412</v>
@@ -11913,7 +11922,7 @@
         <v>50</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -12469,7 +12478,7 @@
         <v>26</v>
       </c>
       <c r="E52" s="8" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -12761,7 +12770,7 @@
         <v>1</v>
       </c>
       <c r="E78" s="8" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="79" spans="1:5" ht="28.8" x14ac:dyDescent="0.55000000000000004">
@@ -12778,7 +12787,7 @@
         <v>16</v>
       </c>
       <c r="E79" s="8" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -12960,7 +12969,7 @@
         <v>3</v>
       </c>
       <c r="E95" s="8" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -12999,7 +13008,7 @@
         <v>1</v>
       </c>
       <c r="E98" s="8" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="99" spans="1:5" ht="28.8" x14ac:dyDescent="0.55000000000000004">
@@ -13016,7 +13025,7 @@
         <v>4</v>
       </c>
       <c r="E99" s="8" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -13083,10 +13092,10 @@
         <v>336</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="F1" t="s">
         <v>409</v>
@@ -13095,7 +13104,7 @@
         <v>412</v>
       </c>
       <c r="H1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -13112,13 +13121,13 @@
         <v>311</v>
       </c>
       <c r="E2" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="F2">
         <v>14</v>
       </c>
       <c r="G2" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2">
         <v>2</v>
@@ -13138,7 +13147,7 @@
         <v>312</v>
       </c>
       <c r="E3" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="F3">
         <v>14</v>
@@ -13164,7 +13173,7 @@
         <v>14</v>
       </c>
       <c r="G4" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H4">
         <v>3</v>
@@ -13184,7 +13193,7 @@
         <v>309</v>
       </c>
       <c r="E5" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="F5">
         <v>14</v>
@@ -13204,7 +13213,7 @@
         <v>309</v>
       </c>
       <c r="E6" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="F6">
         <v>14</v>
@@ -13229,8 +13238,8 @@
       <c r="F7">
         <v>16</v>
       </c>
-      <c r="G7" t="s">
-        <v>421</v>
+      <c r="G7" s="3" t="s">
+        <v>420</v>
       </c>
       <c r="H7">
         <v>16</v>
@@ -13270,7 +13279,7 @@
         <v>313</v>
       </c>
       <c r="E9" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="F9">
         <v>16</v>
@@ -13350,7 +13359,7 @@
         <v>313</v>
       </c>
       <c r="E13" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="F13">
         <v>16</v>
@@ -13430,7 +13439,7 @@
         <v>313</v>
       </c>
       <c r="E17" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="F17">
         <v>16</v>
@@ -13510,7 +13519,7 @@
         <v>313</v>
       </c>
       <c r="E21" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="F21">
         <v>16</v>
@@ -13530,7 +13539,7 @@
         <v>313</v>
       </c>
       <c r="E22" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="F22">
         <v>16</v>
@@ -13556,7 +13565,7 @@
         <v>24</v>
       </c>
       <c r="G23" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H23">
         <v>1</v>
@@ -13576,13 +13585,13 @@
         <v>307</v>
       </c>
       <c r="E24" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="F24">
         <v>40</v>
       </c>
-      <c r="G24" t="s">
-        <v>423</v>
+      <c r="G24" s="3" t="s">
+        <v>422</v>
       </c>
       <c r="H24">
         <v>1</v>
@@ -13596,19 +13605,19 @@
         <v>16</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="D25" t="s">
         <v>278</v>
       </c>
       <c r="E25" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="F25">
         <v>14</v>
       </c>
       <c r="G25" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="H25">
         <v>1</v>
@@ -13622,19 +13631,19 @@
         <v>25</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="D26" t="s">
         <v>286</v>
       </c>
       <c r="E26" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="F26">
         <v>14</v>
       </c>
       <c r="G26" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="H26">
         <v>2</v>
@@ -13648,13 +13657,13 @@
         <v>198</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="D27" t="s">
         <v>286</v>
       </c>
       <c r="E27" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="F27">
         <v>14</v>
@@ -13668,7 +13677,7 @@
         <v>41</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="D28" t="s">
         <v>292</v>
@@ -13680,7 +13689,7 @@
         <v>14</v>
       </c>
       <c r="G28" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H28">
         <v>1</v>
@@ -13705,8 +13714,8 @@
       <c r="F29">
         <v>24</v>
       </c>
-      <c r="G29" s="8" t="s">
-        <v>417</v>
+      <c r="G29" s="10" t="s">
+        <v>416</v>
       </c>
       <c r="H29">
         <v>1</v>
@@ -13726,13 +13735,13 @@
         <v>300</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="F30">
         <v>24</v>
       </c>
-      <c r="G30" s="8" t="s">
-        <v>418</v>
+      <c r="G30" s="10" t="s">
+        <v>417</v>
       </c>
       <c r="H30">
         <v>1</v>
@@ -13757,8 +13766,8 @@
       <c r="F31">
         <v>14</v>
       </c>
-      <c r="G31" t="s">
-        <v>419</v>
+      <c r="G31" s="3" t="s">
+        <v>418</v>
       </c>
       <c r="H31">
         <v>1</v>
@@ -13775,16 +13784,16 @@
         <v>346</v>
       </c>
       <c r="D32" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E32" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="F32">
         <v>14</v>
       </c>
       <c r="G32" s="8" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H32">
         <v>6</v>
@@ -13804,7 +13813,7 @@
         <v>272</v>
       </c>
       <c r="E33" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="F33">
         <v>14</v>
@@ -13824,7 +13833,7 @@
         <v>272</v>
       </c>
       <c r="E34" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="F34">
         <v>14</v>
@@ -13844,7 +13853,7 @@
         <v>301</v>
       </c>
       <c r="E35" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="F35">
         <v>14</v>
@@ -13864,7 +13873,7 @@
         <v>272</v>
       </c>
       <c r="E36" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="F36">
         <v>14</v>
@@ -13884,7 +13893,7 @@
         <v>272</v>
       </c>
       <c r="E37" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="F37">
         <v>14</v>
@@ -13904,13 +13913,13 @@
         <v>282</v>
       </c>
       <c r="E38" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="F38">
         <v>14</v>
       </c>
       <c r="G38" s="8" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H38">
         <v>1</v>
@@ -13936,7 +13945,7 @@
         <v>14</v>
       </c>
       <c r="G39" s="8" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H39">
         <v>6</v>
@@ -14062,7 +14071,7 @@
         <v>14</v>
       </c>
       <c r="G45" s="8" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H45">
         <v>1</v>
@@ -14088,7 +14097,7 @@
         <v>16</v>
       </c>
       <c r="G46" s="8" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H46">
         <v>2</v>
@@ -14128,13 +14137,13 @@
         <v>324</v>
       </c>
       <c r="E48" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="F48">
         <v>14</v>
       </c>
       <c r="G48" s="8" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H48">
         <v>1</v>
@@ -14151,7 +14160,7 @@
         <v>352</v>
       </c>
       <c r="D49" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="E49" t="s">
         <v>319</v>
@@ -14160,7 +14169,7 @@
         <v>16</v>
       </c>
       <c r="G49" s="8" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H49">
         <v>2</v>
@@ -14180,7 +14189,7 @@
         <v>319</v>
       </c>
       <c r="E50" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="F50">
         <v>16</v>
@@ -14200,13 +14209,13 @@
         <v>296</v>
       </c>
       <c r="E51" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="F51">
         <v>14</v>
       </c>
       <c r="G51" s="8" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H51">
         <v>2</v>
@@ -14226,7 +14235,7 @@
         <v>296</v>
       </c>
       <c r="E52" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="F52">
         <v>14</v>
@@ -14252,7 +14261,7 @@
         <v>16</v>
       </c>
       <c r="G53" s="8" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H53">
         <v>2</v>
@@ -14292,13 +14301,13 @@
         <v>308</v>
       </c>
       <c r="E55" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="F55">
         <v>14</v>
       </c>
       <c r="G55" s="8" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H55">
         <v>1</v>
@@ -14318,13 +14327,13 @@
         <v>295</v>
       </c>
       <c r="E56" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="F56">
         <v>20</v>
       </c>
       <c r="G56" s="8" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H56">
         <v>14</v>
@@ -14344,7 +14353,7 @@
         <v>295</v>
       </c>
       <c r="E57" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="F57">
         <v>20</v>
@@ -14364,7 +14373,7 @@
         <v>285</v>
       </c>
       <c r="E58" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="F58">
         <v>20</v>
@@ -14381,10 +14390,10 @@
         <v>345</v>
       </c>
       <c r="D59" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="E59" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="F59">
         <v>20</v>
@@ -14401,10 +14410,10 @@
         <v>345</v>
       </c>
       <c r="D60" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="E60" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="F60">
         <v>20</v>
@@ -14424,7 +14433,7 @@
         <v>285</v>
       </c>
       <c r="E61" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="F61">
         <v>20</v>
@@ -14444,7 +14453,7 @@
         <v>285</v>
       </c>
       <c r="E62" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="F62">
         <v>20</v>
@@ -14464,7 +14473,7 @@
         <v>285</v>
       </c>
       <c r="E63" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="F63">
         <v>20</v>
@@ -14484,7 +14493,7 @@
         <v>285</v>
       </c>
       <c r="E64" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="F64">
         <v>20</v>
@@ -14501,10 +14510,10 @@
         <v>345</v>
       </c>
       <c r="D65" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="E65" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="F65">
         <v>20</v>
@@ -14524,7 +14533,7 @@
         <v>285</v>
       </c>
       <c r="E66" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="F66">
         <v>20</v>
@@ -14544,7 +14553,7 @@
         <v>285</v>
       </c>
       <c r="E67" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="F67">
         <v>20</v>
@@ -14561,10 +14570,10 @@
         <v>345</v>
       </c>
       <c r="D68" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="E68" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="F68">
         <v>20</v>
@@ -14581,10 +14590,10 @@
         <v>345</v>
       </c>
       <c r="D69" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="E69" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="F69">
         <v>20</v>
@@ -14601,16 +14610,16 @@
         <v>374</v>
       </c>
       <c r="D70" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="E70" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="F70">
         <v>14</v>
       </c>
       <c r="G70" s="8" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H70">
         <v>1</v>
@@ -14627,16 +14636,16 @@
         <v>375</v>
       </c>
       <c r="D71" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="E71" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="F71">
         <v>14</v>
       </c>
       <c r="G71" s="8" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H71">
         <v>4</v>
@@ -14653,10 +14662,10 @@
         <v>375</v>
       </c>
       <c r="D72" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="E72" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="F72">
         <v>14</v>
@@ -14673,10 +14682,10 @@
         <v>375</v>
       </c>
       <c r="D73" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="E73" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="F73">
         <v>14</v>
@@ -14693,10 +14702,10 @@
         <v>375</v>
       </c>
       <c r="D74" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="E74" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="F74">
         <v>14</v>
@@ -14722,7 +14731,7 @@
         <v>14</v>
       </c>
       <c r="G75" s="8" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H75">
         <v>6</v>
@@ -14739,7 +14748,7 @@
         <v>353</v>
       </c>
       <c r="D76" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="E76" t="s">
         <v>298</v>
@@ -14819,7 +14828,7 @@
         <v>353</v>
       </c>
       <c r="D80" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="E80" t="s">
         <v>298</v>
@@ -14848,7 +14857,7 @@
         <v>16</v>
       </c>
       <c r="G81" s="8" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="H81">
         <v>2</v>
@@ -14894,7 +14903,7 @@
         <v>20</v>
       </c>
       <c r="G83" t="s">
-        <v>413</v>
+        <v>558</v>
       </c>
       <c r="H83">
         <v>1</v>
@@ -14911,16 +14920,16 @@
         <v>377</v>
       </c>
       <c r="D84" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="E84" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="F84">
         <v>14</v>
       </c>
       <c r="G84" s="8" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H84">
         <v>3</v>
@@ -14937,10 +14946,10 @@
         <v>377</v>
       </c>
       <c r="D85" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="E85" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="F85">
         <v>14</v>
@@ -14957,10 +14966,10 @@
         <v>377</v>
       </c>
       <c r="D86" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="E86" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="F86">
         <v>14</v>
@@ -14980,13 +14989,13 @@
         <v>323</v>
       </c>
       <c r="E87" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="F87">
         <v>14</v>
       </c>
       <c r="G87" s="8" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H87">
         <v>1</v>
@@ -15012,7 +15021,7 @@
         <v>16</v>
       </c>
       <c r="G88" s="8" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H88">
         <v>1</v>
@@ -15038,7 +15047,7 @@
         <v>16</v>
       </c>
       <c r="G89" s="8" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="H89">
         <v>1</v>
@@ -15064,7 +15073,7 @@
         <v>14</v>
       </c>
       <c r="G90" s="8" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="H90">
         <v>6</v>
@@ -15185,13 +15194,13 @@
         <v>333</v>
       </c>
       <c r="E96" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="F96">
         <v>14</v>
       </c>
       <c r="G96" s="8" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="H96">
         <v>1</v>
@@ -15211,13 +15220,13 @@
         <v>306</v>
       </c>
       <c r="E97" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="F97">
         <v>20</v>
       </c>
-      <c r="G97" t="s">
-        <v>445</v>
+      <c r="G97" s="3" t="s">
+        <v>444</v>
       </c>
       <c r="H97">
         <v>1</v>
@@ -15237,13 +15246,13 @@
         <v>320</v>
       </c>
       <c r="E98" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="F98">
         <v>18</v>
       </c>
-      <c r="G98" t="s">
-        <v>446</v>
+      <c r="G98" s="3" t="s">
+        <v>445</v>
       </c>
       <c r="H98">
         <v>1</v>
@@ -15263,13 +15272,13 @@
         <v>317</v>
       </c>
       <c r="E99" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="F99">
         <v>28</v>
       </c>
-      <c r="G99" t="s">
-        <v>450</v>
+      <c r="G99" s="3" t="s">
+        <v>449</v>
       </c>
       <c r="H99">
         <v>1</v>
@@ -15289,13 +15298,13 @@
         <v>304</v>
       </c>
       <c r="E100" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="F100">
         <v>40</v>
       </c>
-      <c r="G100" t="s">
-        <v>447</v>
+      <c r="G100" s="3" t="s">
+        <v>446</v>
       </c>
       <c r="H100">
         <v>1</v>
@@ -15315,13 +15324,13 @@
         <v>302</v>
       </c>
       <c r="E101" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="F101">
         <v>40</v>
       </c>
-      <c r="G101" t="s">
-        <v>449</v>
+      <c r="G101" s="3" t="s">
+        <v>448</v>
       </c>
       <c r="H101">
         <v>1</v>
@@ -15346,8 +15355,8 @@
       <c r="F102">
         <v>40</v>
       </c>
-      <c r="G102" t="s">
-        <v>448</v>
+      <c r="G102" s="3" t="s">
+        <v>447</v>
       </c>
       <c r="H102">
         <v>1</v>
@@ -15373,7 +15382,7 @@
     <col min="10" max="10" width="25.1015625" customWidth="1"/>
     <col min="11" max="11" width="10" customWidth="1"/>
     <col min="12" max="12" width="7.1015625" customWidth="1"/>
-    <col min="13" max="13" width="58.47265625" customWidth="1"/>
+    <col min="13" max="13" width="58.47265625" style="5" customWidth="1"/>
     <col min="14" max="14" width="10.7890625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -15406,13 +15415,16 @@
         <v>1</v>
       </c>
       <c r="J1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="K1" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="L1" t="s">
-        <v>420</v>
+        <v>419</v>
+      </c>
+      <c r="M1" s="5" t="s">
+        <v>575</v>
       </c>
       <c r="N1" t="s">
         <v>406</v>
@@ -15447,16 +15459,16 @@
         <v>2.4</v>
       </c>
       <c r="J2" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="K2" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="L2">
         <v>6</v>
       </c>
-      <c r="M2" t="s">
-        <v>546</v>
+      <c r="M2" s="11" t="s">
+        <v>559</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.55000000000000004">
@@ -15488,7 +15500,7 @@
         <v>2.4</v>
       </c>
       <c r="J3" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.55000000000000004">
@@ -15520,7 +15532,7 @@
         <v>2.4</v>
       </c>
       <c r="J4" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.55000000000000004">
@@ -15552,7 +15564,7 @@
         <v>2.4</v>
       </c>
       <c r="J5" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.55000000000000004">
@@ -15584,7 +15596,7 @@
         <v>2.4</v>
       </c>
       <c r="J6" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.55000000000000004">
@@ -15616,7 +15628,7 @@
         <v>2.4</v>
       </c>
       <c r="J7" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.55000000000000004">
@@ -15648,16 +15660,16 @@
         <v>1.4</v>
       </c>
       <c r="J8" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="K8" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="L8">
         <v>1</v>
       </c>
-      <c r="M8" t="s">
-        <v>547</v>
+      <c r="M8" s="11" t="s">
+        <v>560</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.55000000000000004">
@@ -15692,13 +15704,13 @@
         <v>329</v>
       </c>
       <c r="K9" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="L9">
         <v>1</v>
       </c>
-      <c r="M9" t="s">
-        <v>548</v>
+      <c r="M9" s="12" t="s">
+        <v>561</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.55000000000000004">
@@ -15730,16 +15742,16 @@
         <v>1.4</v>
       </c>
       <c r="J10" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="K10" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="L10">
         <v>1</v>
       </c>
-      <c r="M10" t="s">
-        <v>549</v>
+      <c r="M10" s="11" t="s">
+        <v>562</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.55000000000000004">
@@ -15774,13 +15786,13 @@
         <v>289</v>
       </c>
       <c r="K11" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="L11">
         <v>2</v>
       </c>
-      <c r="M11" t="s">
-        <v>550</v>
+      <c r="M11" s="11" t="s">
+        <v>563</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.55000000000000004">
@@ -15847,13 +15859,13 @@
         <v>290</v>
       </c>
       <c r="K13" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="L13">
         <v>4</v>
       </c>
-      <c r="M13" t="s">
-        <v>551</v>
+      <c r="M13" s="11" t="s">
+        <v>564</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.55000000000000004">
@@ -15981,19 +15993,19 @@
         <v>1.5</v>
       </c>
       <c r="J17" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="K17" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="L17">
         <v>1</v>
       </c>
-      <c r="M17" t="s">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14" ht="57.6" x14ac:dyDescent="0.55000000000000004">
+      <c r="M17" s="11" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A18">
         <v>165</v>
       </c>
@@ -16025,16 +16037,16 @@
         <v>318</v>
       </c>
       <c r="K18" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="L18">
         <v>1</v>
       </c>
-      <c r="M18" s="8" t="s">
-        <v>552</v>
+      <c r="M18" s="13" t="s">
+        <v>577</v>
       </c>
       <c r="N18" t="s">
-        <v>567</v>
+        <v>546</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.55000000000000004">
@@ -16069,13 +16081,13 @@
         <v>274</v>
       </c>
       <c r="K19" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="L19">
         <v>26</v>
       </c>
-      <c r="M19" t="s">
-        <v>553</v>
+      <c r="M19" s="11" t="s">
+        <v>565</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.55000000000000004">
@@ -16910,16 +16922,16 @@
         <v>276</v>
       </c>
       <c r="K45" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="L45">
         <v>1</v>
       </c>
-      <c r="M45" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="46" spans="1:14" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="M45" s="11" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14" ht="35.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A46">
         <v>106</v>
       </c>
@@ -16948,19 +16960,19 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="J46" t="s">
+        <v>474</v>
+      </c>
+      <c r="K46" t="s">
+        <v>545</v>
+      </c>
+      <c r="L46">
+        <v>1</v>
+      </c>
+      <c r="M46" s="13" t="s">
+        <v>576</v>
+      </c>
+      <c r="N46" t="s">
         <v>475</v>
-      </c>
-      <c r="K46" t="s">
-        <v>565</v>
-      </c>
-      <c r="L46">
-        <v>1</v>
-      </c>
-      <c r="M46" s="8" t="s">
-        <v>566</v>
-      </c>
-      <c r="N46" t="s">
-        <v>476</v>
       </c>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.55000000000000004">
@@ -16995,13 +17007,13 @@
         <v>284</v>
       </c>
       <c r="K47" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="L47">
         <v>1</v>
       </c>
-      <c r="M47" t="s">
-        <v>555</v>
+      <c r="M47" s="11" t="s">
+        <v>567</v>
       </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.55000000000000004">
@@ -17036,13 +17048,13 @@
         <v>314</v>
       </c>
       <c r="K48" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="L48">
         <v>10</v>
       </c>
-      <c r="M48" t="s">
-        <v>556</v>
+      <c r="M48" s="11" t="s">
+        <v>568</v>
       </c>
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.55000000000000004">
@@ -17365,13 +17377,13 @@
         <v>270</v>
       </c>
       <c r="K58" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="L58">
         <v>10</v>
       </c>
-      <c r="M58" t="s">
-        <v>557</v>
+      <c r="M58" s="11" t="s">
+        <v>569</v>
       </c>
     </row>
     <row r="59" spans="1:13" x14ac:dyDescent="0.55000000000000004">
@@ -17694,13 +17706,13 @@
         <v>332</v>
       </c>
       <c r="K68" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="L68">
         <v>1</v>
       </c>
-      <c r="M68" t="s">
-        <v>558</v>
+      <c r="M68" s="11" t="s">
+        <v>570</v>
       </c>
     </row>
     <row r="69" spans="1:13" x14ac:dyDescent="0.55000000000000004">
@@ -17735,13 +17747,13 @@
         <v>330</v>
       </c>
       <c r="K69" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="L69">
         <v>2</v>
       </c>
-      <c r="M69" t="s">
-        <v>559</v>
+      <c r="M69" s="11" t="s">
+        <v>571</v>
       </c>
     </row>
     <row r="70" spans="1:13" x14ac:dyDescent="0.55000000000000004">
@@ -17808,13 +17820,13 @@
         <v>328</v>
       </c>
       <c r="K71" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="L71">
         <v>8</v>
       </c>
-      <c r="M71" t="s">
-        <v>560</v>
+      <c r="M71" s="11" t="s">
+        <v>572</v>
       </c>
     </row>
     <row r="72" spans="1:13" x14ac:dyDescent="0.55000000000000004">
@@ -18006,7 +18018,7 @@
         <v>5.4</v>
       </c>
       <c r="J77" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="78" spans="1:13" x14ac:dyDescent="0.55000000000000004">
@@ -18070,16 +18082,16 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="J79" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="K79" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="L79">
         <v>1</v>
       </c>
-      <c r="M79" t="s">
-        <v>561</v>
+      <c r="M79" s="11" t="s">
+        <v>573</v>
       </c>
     </row>
     <row r="80" spans="1:13" x14ac:dyDescent="0.55000000000000004">
@@ -18111,16 +18123,16 @@
         <v>1.4</v>
       </c>
       <c r="J80" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="K80" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="L80">
         <v>1</v>
       </c>
-      <c r="M80" t="s">
-        <v>562</v>
+      <c r="M80" s="11" t="s">
+        <v>574</v>
       </c>
     </row>
     <row r="81" spans="1:13" x14ac:dyDescent="0.55000000000000004">
@@ -18152,16 +18164,16 @@
         <v>4.2</v>
       </c>
       <c r="J81" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="K81" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="L81">
         <v>1</v>
       </c>
-      <c r="M81" t="s">
-        <v>563</v>
+      <c r="M81" s="11" t="s">
+        <v>557</v>
       </c>
     </row>
     <row r="82" spans="1:13" x14ac:dyDescent="0.55000000000000004">
@@ -18193,16 +18205,16 @@
         <v>6.1</v>
       </c>
       <c r="J82" s="2" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="K82" s="2" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="L82">
         <v>1</v>
       </c>
-      <c r="M82" t="s">
-        <v>564</v>
+      <c r="M82" s="12" t="s">
+        <v>556</v>
       </c>
     </row>
   </sheetData>
@@ -18210,6 +18222,29 @@
     <sortCondition ref="D2:D82"/>
     <sortCondition ref="B2:B82"/>
   </sortState>
+  <hyperlinks>
+    <hyperlink ref="M2" r:id="rId1" xr:uid="{42E0DCFC-8871-4E95-B6CC-43A277B8DEB2}"/>
+    <hyperlink ref="M9" r:id="rId2" xr:uid="{E3217A02-A8C4-4F9F-878A-6B87BF51C928}"/>
+    <hyperlink ref="M8" r:id="rId3" xr:uid="{2471DA2A-9163-413F-A79A-ADF19832513A}"/>
+    <hyperlink ref="M10" r:id="rId4" xr:uid="{C55ED55E-4938-4B12-B9D3-6FBEA40FC5AF}"/>
+    <hyperlink ref="M11" r:id="rId5" xr:uid="{A7988052-A8F5-4AAF-8E7C-86566731AC5A}"/>
+    <hyperlink ref="M13" r:id="rId6" xr:uid="{37C9658B-C285-457A-B181-E67E5CC86AE1}"/>
+    <hyperlink ref="M17" r:id="rId7" xr:uid="{06C8AC6D-DB8B-4E2E-8DAD-C4612D8E2ACD}"/>
+    <hyperlink ref="M19" r:id="rId8" xr:uid="{117312FF-492B-4C8E-8C13-EA15DD01A670}"/>
+    <hyperlink ref="M45" r:id="rId9" xr:uid="{12C82AE4-7AE4-41EF-8544-661452760378}"/>
+    <hyperlink ref="M47" r:id="rId10" xr:uid="{56701756-22AC-47DA-946B-118E758F8232}"/>
+    <hyperlink ref="M48" r:id="rId11" xr:uid="{6301D18A-3336-490F-AC1A-3D1EEAAC3A29}"/>
+    <hyperlink ref="M58" r:id="rId12" xr:uid="{6A975214-3D65-46F5-B6ED-936E279CAD1E}"/>
+    <hyperlink ref="M68" r:id="rId13" xr:uid="{4B4B0154-690E-4A78-A5DA-DCA3D50679A2}"/>
+    <hyperlink ref="M69" r:id="rId14" xr:uid="{51C00003-98D8-4FA2-8DFD-9E6571F9B1E8}"/>
+    <hyperlink ref="M71" r:id="rId15" xr:uid="{55D0241C-5879-40FC-A259-1FA739439842}"/>
+    <hyperlink ref="M79" r:id="rId16" xr:uid="{B440E0BF-AA4D-467C-8E13-1016EBB9FB67}"/>
+    <hyperlink ref="M80" r:id="rId17" xr:uid="{B864F5C8-47B8-4660-9ED2-01E13FDB6F35}"/>
+    <hyperlink ref="M81" r:id="rId18" xr:uid="{80209C7C-D54D-4B24-86C0-25B62FBD4B66}"/>
+    <hyperlink ref="M82" r:id="rId19" xr:uid="{621AF746-F6B2-4A0D-BB11-1BAD00092CCD}"/>
+    <hyperlink ref="M46" r:id="rId20" xr:uid="{6918D5BB-6DB2-405C-96C5-E749BC01A39E}"/>
+    <hyperlink ref="M18" r:id="rId21" xr:uid="{FEE61E9B-E15C-4B2C-A0C6-991187CEE277}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -18253,10 +18288,10 @@
         <v>1</v>
       </c>
       <c r="J1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="K1" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="L1" t="s">
         <v>406</v>
@@ -18286,7 +18321,7 @@
         <v>1.6</v>
       </c>
       <c r="J2" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.55000000000000004">
@@ -18300,7 +18335,7 @@
         <v>118</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -18318,7 +18353,7 @@
         <v>2.4</v>
       </c>
       <c r="J3" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.55000000000000004">
@@ -18350,7 +18385,7 @@
         <v>2.1</v>
       </c>
       <c r="J4" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.55000000000000004">
@@ -18382,7 +18417,7 @@
         <v>2.1</v>
       </c>
       <c r="J5" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.55000000000000004">
@@ -18474,7 +18509,7 @@
         <v>1.6</v>
       </c>
       <c r="J8" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.55000000000000004">
@@ -18506,7 +18541,7 @@
         <v>6.1</v>
       </c>
       <c r="J9" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.55000000000000004">
@@ -18597,7 +18632,7 @@
         <v>1.6</v>
       </c>
       <c r="J12" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.55000000000000004">
@@ -18644,7 +18679,7 @@
         <v>241</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="E14">
         <v>1</v>
@@ -18662,10 +18697,10 @@
         <v>6.1</v>
       </c>
       <c r="J14" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="L14" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.55000000000000004">
@@ -18692,7 +18727,7 @@
         <v>1.6</v>
       </c>
       <c r="J15" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.55000000000000004">
@@ -18724,7 +18759,7 @@
         <v>1.5</v>
       </c>
       <c r="J16" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.55000000000000004">
@@ -18756,7 +18791,7 @@
         <v>1.4</v>
       </c>
       <c r="J17" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.55000000000000004">
@@ -18770,7 +18805,7 @@
         <v>38</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="E18">
         <v>1</v>
@@ -18788,10 +18823,10 @@
         <v>1.4</v>
       </c>
       <c r="J18" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="L18" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.55000000000000004">
@@ -18823,7 +18858,7 @@
         <v>1.4</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="K19" s="2"/>
     </row>
@@ -19302,7 +19337,7 @@
         <v>1</v>
       </c>
       <c r="J1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.55000000000000004">
@@ -19371,13 +19406,13 @@
         <v>6.1</v>
       </c>
       <c r="J3" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="K3" s="8" t="s">
-        <v>570</v>
+        <v>549</v>
       </c>
       <c r="L3" t="s">
-        <v>569</v>
+        <v>548</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.55000000000000004">
@@ -19391,7 +19426,7 @@
         <v>78</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>568</v>
+        <v>547</v>
       </c>
       <c r="E4">
         <v>1</v>
@@ -19410,13 +19445,13 @@
         <v>2.1</v>
       </c>
       <c r="J4" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="K4" t="s">
-        <v>571</v>
+        <v>550</v>
       </c>
       <c r="L4" t="s">
-        <v>572</v>
+        <v>551</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.55000000000000004">
@@ -19430,7 +19465,7 @@
         <v>79</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>568</v>
+        <v>547</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -19449,10 +19484,10 @@
         <v>2.1</v>
       </c>
       <c r="J5" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="K5" t="s">
-        <v>571</v>
+        <v>550</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.55000000000000004">
@@ -19516,7 +19551,7 @@
         <v>288</v>
       </c>
       <c r="K7" t="s">
-        <v>574</v>
+        <v>553</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="115.2" x14ac:dyDescent="0.55000000000000004">
@@ -19552,7 +19587,7 @@
         <v>275</v>
       </c>
       <c r="K8" s="8" t="s">
-        <v>575</v>
+        <v>554</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.55000000000000004">
@@ -19588,7 +19623,7 @@
         <v>315</v>
       </c>
       <c r="K9" t="s">
-        <v>573</v>
+        <v>552</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.55000000000000004">
@@ -19621,10 +19656,10 @@
         <v>2.1</v>
       </c>
       <c r="J10" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="K10" t="s">
-        <v>576</v>
+        <v>555</v>
       </c>
     </row>
   </sheetData>
